--- a/data/DPDP_Rules_Tracker.xlsx
+++ b/data/DPDP_Rules_Tracker.xlsx
@@ -2153,7 +2153,7 @@
       </c>
       <c r="J16" s="11" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="K16" s="11" t="inlineStr">
@@ -2183,7 +2183,7 @@
       </c>
       <c r="R16" s="11" t="inlineStr">
         <is>
-          <t>In force eighteen months after notification (G.S.R. 843(E), group (c)) — not yet operative.</t>
+          <t>In force eighteen months after notification (G.S.R. 843(E), group (c)) — not yet operative. Text corrected 2026-09-23 against the official Act PDF (SHA-256 4deb2398...7d15), independently verified twice (two PDF extraction methods, two review passes) — see docs/act_table_audit_2026-09-23.md.</t>
         </is>
       </c>
       <c r="S16" s="13">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="E36" s="11" t="inlineStr">
         <is>
-          <t>Sets broad exemptions from most of the Act's obligations — for legal-right enforcement, judicial/regulatory processing, crime prevention/investigation, foreign-contract processing of non-Indian data, M&amp;A restructuring, and defaulter financial-information processing — plus government-notified exemptions for security instrumentalities, research/statistics, and startups.</t>
+          <t>Sets broad exemptions from most of the Act's obligations — for legal-right enforcement, judicial/regulatory processing, crime prevention/investigation, foreign-contract processing of non-Indian data, M&amp;A restructuring, and defaulter financial-information processing — plus a notified security-instrumentality exemption, a self-executing research/archiving/statistical exemption, notified exemptions for specific Data Fiduciaries (including startups) from listed sections, a conditional State-processing exemption from parts of Sections 8 and 12, and a five-year sunset power to exempt any Data Fiduciary from any provision by notification.</t>
         </is>
       </c>
       <c r="F36" s="12" t="inlineStr">
@@ -3873,7 +3873,7 @@
       </c>
       <c r="J36" s="11" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="K36" s="11" t="inlineStr">
@@ -3903,7 +3903,7 @@
       </c>
       <c r="R36" s="11" t="inlineStr">
         <is>
-          <t>In force eighteen months after notification (G.S.R. 843(E), group (c)) — not yet operative.</t>
+          <t>In force eighteen months after notification (G.S.R. 843(E), group (c)) — not yet operative. Text corrected 2026-09-23 against the official Act PDF (SHA-256 4deb2398...7d15), independently verified twice (two PDF extraction methods, two review passes) — see docs/act_table_audit_2026-09-23.md.</t>
         </is>
       </c>
       <c r="S36" s="13">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="E54" s="11" t="inlineStr">
         <is>
-          <t>Gives the Chairperson general superintendence over Board administrative matters, and the power to delegate scrutiny/functions/proceedings to individual Members or groups of Members.</t>
+          <t>Gives the Chairperson general superintendence over Board administrative matters, the power to authorise any officer to scrutinise matters addressed to the Board, and the power to delegate specific functions and proceedings to an individual Member or groups of Members.</t>
         </is>
       </c>
       <c r="F54" s="12" t="inlineStr">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="J54" s="11" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="K54" s="11" t="inlineStr">
@@ -5451,7 +5451,7 @@
       </c>
       <c r="R54" s="11" t="inlineStr">
         <is>
-          <t>Currently in force.</t>
+          <t>Currently in force. Text corrected 2026-09-23 against the official Act PDF (SHA-256 4deb2398...7d15), independently verified twice (two PDF extraction methods, two review passes) — see docs/act_table_audit_2026-09-23.md.</t>
         </is>
       </c>
       <c r="S54" s="13">
@@ -5937,7 +5937,7 @@
       </c>
       <c r="J60" s="11" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="K60" s="11" t="inlineStr">
@@ -5967,7 +5967,7 @@
       </c>
       <c r="R60" s="11" t="inlineStr">
         <is>
-          <t>In force eighteen months after notification (G.S.R. 843(E), group (c)) — not yet operative.</t>
+          <t>In force eighteen months after notification (G.S.R. 843(E), group (c)) — not yet operative. Text corrected 2026-09-23 against the official Act PDF (SHA-256 4deb2398...7d15), independently verified twice (two PDF extraction methods, two review passes) — see docs/act_table_audit_2026-09-23.md.</t>
         </is>
       </c>
       <c r="S60" s="13">
@@ -7313,7 +7313,7 @@
       </c>
       <c r="J76" s="11" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="K76" s="11" t="inlineStr">
@@ -7343,7 +7343,7 @@
       </c>
       <c r="R76" s="11" t="inlineStr">
         <is>
-          <t>Currently in force.</t>
+          <t>Currently in force. Text corrected 2026-09-23 against the official Act PDF (SHA-256 4deb2398...7d15), independently verified twice (two PDF extraction methods, two review passes) — see docs/act_table_audit_2026-09-23.md.</t>
         </is>
       </c>
       <c r="S76" s="13">
@@ -7460,7 +7460,7 @@
       </c>
       <c r="E78" s="11" t="inlineStr">
         <is>
-          <t>Amends the TRAI Act, 1997 to fold in the DPDP Appellate Tribunal, and amends the RTI Act, 2005 to redefine what counts as exempt 'personal information' by reference to this Act.</t>
+          <t>Amends the TRAI Act, 1997 to replace its Appellate Tribunal list with the IT Act, Airports Economic Regulatory Authority Act, and DPDP Act Appellate Tribunals, and amends the RTI Act, 2005 to add a standalone exemption for 'information which relates to personal information'.</t>
         </is>
       </c>
       <c r="F78" s="12" t="inlineStr">
@@ -7485,7 +7485,7 @@
       </c>
       <c r="J78" s="11" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="K78" s="11" t="inlineStr">
@@ -7515,7 +7515,7 @@
       </c>
       <c r="R78" s="11" t="inlineStr">
         <is>
-          <t>Currently in force.</t>
+          <t>Currently in force. Text corrected 2026-09-23 against the official Act PDF (SHA-256 4deb2398...7d15), independently verified twice (two PDF extraction methods, two review passes) — see docs/act_table_audit_2026-09-23.md.</t>
         </is>
       </c>
       <c r="S78" s="13">
@@ -7546,7 +7546,7 @@
       </c>
       <c r="E79" s="11" t="inlineStr">
         <is>
-          <t>Amends the Information Technology Act, 2000 — removes the old compensation-for-data-breach provision (Section 43A, since this Act now governs that), and cross-references this Act in two other IT Act provisions.</t>
+          <t>Amends the Information Technology Act, 2000 — removes the old compensation-for-data-breach provision (Section 43A, since this Act now governs that), inserts a cross-reference to this Act into Section 81's proviso, and omits a now-redundant RTI-exemption clause (Section 87(2)(ob)).</t>
         </is>
       </c>
       <c r="F79" s="12" t="inlineStr">
@@ -7571,7 +7571,7 @@
       </c>
       <c r="J79" s="11" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="K79" s="11" t="inlineStr">
@@ -7601,7 +7601,7 @@
       </c>
       <c r="R79" s="11" t="inlineStr">
         <is>
-          <t>In force eighteen months after notification (G.S.R. 843(E), group (c)) — not yet operative.</t>
+          <t>In force eighteen months after notification (G.S.R. 843(E), group (c)) — not yet operative. Text corrected 2026-09-23 against the official Act PDF (SHA-256 4deb2398...7d15), independently verified twice (two PDF extraction methods, two review passes) — see docs/act_table_audit_2026-09-23.md.</t>
         </is>
       </c>
       <c r="S79" s="13">
@@ -7801,7 +7801,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O80"/>
+  <dimension ref="A1:O87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -12872,6 +12872,475 @@
       <c r="O80" s="11" t="inlineStr">
         <is>
           <t>Initial baseline load from Act text; commencement per G.S.R. 843(E). In force eighteen months after notification (G.S.R. 843(E), group (c)) — not yet operative.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="11" t="inlineStr">
+        <is>
+          <t>CHG-0033</t>
+        </is>
+      </c>
+      <c r="B81" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-23T01:45:00</t>
+        </is>
+      </c>
+      <c r="C81" s="11" t="inlineStr">
+        <is>
+          <t>DPDPA-S7</t>
+        </is>
+      </c>
+      <c r="D81" s="11" t="inlineStr">
+        <is>
+          <t>Correction</t>
+        </is>
+      </c>
+      <c r="E81" s="11" t="inlineStr">
+        <is>
+          <t>Lists nine 'certain legitimate uses' that permit processing without consent — voluntary data-sharing for an obvious purpose, State benefit delivery, State legal functions, legal disclosure obligations, court orders, medical emergencies, public health measures, disaster response, and employment-related purposes.</t>
+        </is>
+      </c>
+      <c r="F81" s="11" t="inlineStr">
+        <is>
+          <t>Lists nine 'certain legitimate uses' that permit processing without consent — voluntary data-sharing for an obvious purpose, State benefit delivery, State legal functions, legal disclosure obligations, court orders, medical emergencies, public health measures, disaster response, and employment-related purposes.</t>
+        </is>
+      </c>
+      <c r="G81" s="11" t="inlineStr">
+        <is>
+          <t>Digital Personal Data Protection Act, 2023 (Act No. 22 of 2023)</t>
+        </is>
+      </c>
+      <c r="H81" s="11" t="inlineStr">
+        <is>
+          <t>https://www.meity.gov.in/static/uploads/2024/06/2bf1f0e9f04e6fb4f8fef35e82c42aa5.pdf</t>
+        </is>
+      </c>
+      <c r="I81" s="11" t="inlineStr">
+        <is>
+          <t>cowork:claude-sonnet-5 + claude-opus (manual re-verification against official PDF)</t>
+        </is>
+      </c>
+      <c r="J81" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K81" s="11" t="inlineStr">
+        <is>
+          <t>Pending Review</t>
+        </is>
+      </c>
+      <c r="L81" s="11" t="n"/>
+      <c r="M81" s="11" t="n"/>
+      <c r="N81" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O81" s="11" t="inlineStr">
+        <is>
+          <t>One-time manual data-quality correction (not a detected regulatory change): DB text diverged from the enacted Act at seeding time. Corrected against a freshly downloaded, hash-verified copy of the official PDF, independently checked with a second extraction tool and a second review pass. review_status left 'Pending Review' since no human has read the literal corrected text line-by-line yet — see docs/act_table_audit_2026-09-23.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="11" t="inlineStr">
+        <is>
+          <t>CHG-0034</t>
+        </is>
+      </c>
+      <c r="B82" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-23T01:45:00</t>
+        </is>
+      </c>
+      <c r="C82" s="11" t="inlineStr">
+        <is>
+          <t>DPDPA-S26</t>
+        </is>
+      </c>
+      <c r="D82" s="11" t="inlineStr">
+        <is>
+          <t>Correction</t>
+        </is>
+      </c>
+      <c r="E82" s="11" t="inlineStr">
+        <is>
+          <t>Gives the Chairperson general superintendence over Board administrative matters, and the power to delegate scrutiny/functions/proceedings to individual Members or groups of Members.</t>
+        </is>
+      </c>
+      <c r="F82" s="11" t="inlineStr">
+        <is>
+          <t>Gives the Chairperson general superintendence over Board administrative matters, the power to authorise any officer to scrutinise matters addressed to the Board, and the power to delegate specific functions and proceedings to an individual Member or groups of Members.</t>
+        </is>
+      </c>
+      <c r="G82" s="11" t="inlineStr">
+        <is>
+          <t>Digital Personal Data Protection Act, 2023 (Act No. 22 of 2023)</t>
+        </is>
+      </c>
+      <c r="H82" s="11" t="inlineStr">
+        <is>
+          <t>https://www.meity.gov.in/static/uploads/2024/06/2bf1f0e9f04e6fb4f8fef35e82c42aa5.pdf</t>
+        </is>
+      </c>
+      <c r="I82" s="11" t="inlineStr">
+        <is>
+          <t>cowork:claude-sonnet-5 + claude-opus (manual re-verification against official PDF)</t>
+        </is>
+      </c>
+      <c r="J82" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K82" s="11" t="inlineStr">
+        <is>
+          <t>Pending Review</t>
+        </is>
+      </c>
+      <c r="L82" s="11" t="n"/>
+      <c r="M82" s="11" t="n"/>
+      <c r="N82" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O82" s="11" t="inlineStr">
+        <is>
+          <t>One-time manual data-quality correction (not a detected regulatory change): DB text diverged from the enacted Act at seeding time. Corrected against a freshly downloaded, hash-verified copy of the official PDF, independently checked with a second extraction tool and a second review pass. review_status left 'Pending Review' since no human has read the literal corrected text line-by-line yet — see docs/act_table_audit_2026-09-23.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="11" t="inlineStr">
+        <is>
+          <t>CHG-0035</t>
+        </is>
+      </c>
+      <c r="B83" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-23T01:45:00</t>
+        </is>
+      </c>
+      <c r="C83" s="11" t="inlineStr">
+        <is>
+          <t>DPDPA-S17</t>
+        </is>
+      </c>
+      <c r="D83" s="11" t="inlineStr">
+        <is>
+          <t>Correction</t>
+        </is>
+      </c>
+      <c r="E83" s="11" t="inlineStr">
+        <is>
+          <t>Sets broad exemptions from most of the Act's obligations — for legal-right enforcement, judicial/regulatory processing, crime prevention/investigation, foreign-contract processing of non-Indian data, M&amp;A restructuring, and defaulter financial-information processing — plus government-notified exemptions for security instrumentalities, research/statistics, and startups.</t>
+        </is>
+      </c>
+      <c r="F83" s="11" t="inlineStr">
+        <is>
+          <t>Sets broad exemptions from most of the Act's obligations — for legal-right enforcement, judicial/regulatory processing, crime prevention/investigation, foreign-contract processing of non-Indian data, M&amp;A restructuring, and defaulter financial-information processing — plus a notified security-instrumentality exemption, a self-executing research/archiving/statistical exemption, notified exemptions for specific Data Fiduciaries (including startups) from listed sections, a conditional State-processing exemption from parts of Sections 8 and 12, and a five-year sunset power to exempt any Data Fiduciary from any provision by notification.</t>
+        </is>
+      </c>
+      <c r="G83" s="11" t="inlineStr">
+        <is>
+          <t>Digital Personal Data Protection Act, 2023 (Act No. 22 of 2023)</t>
+        </is>
+      </c>
+      <c r="H83" s="11" t="inlineStr">
+        <is>
+          <t>https://www.meity.gov.in/static/uploads/2024/06/2bf1f0e9f04e6fb4f8fef35e82c42aa5.pdf</t>
+        </is>
+      </c>
+      <c r="I83" s="11" t="inlineStr">
+        <is>
+          <t>cowork:claude-sonnet-5 + claude-opus (manual re-verification against official PDF)</t>
+        </is>
+      </c>
+      <c r="J83" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K83" s="11" t="inlineStr">
+        <is>
+          <t>Pending Review</t>
+        </is>
+      </c>
+      <c r="L83" s="11" t="n"/>
+      <c r="M83" s="11" t="n"/>
+      <c r="N83" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O83" s="11" t="inlineStr">
+        <is>
+          <t>One-time manual data-quality correction (not a detected regulatory change): DB text diverged from the enacted Act at seeding time. Corrected against a freshly downloaded, hash-verified copy of the official PDF, independently checked with a second extraction tool and a second review pass. review_status left 'Pending Review' since no human has read the literal corrected text line-by-line yet — see docs/act_table_audit_2026-09-23.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="11" t="inlineStr">
+        <is>
+          <t>CHG-0036</t>
+        </is>
+      </c>
+      <c r="B84" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-23T01:45:00</t>
+        </is>
+      </c>
+      <c r="C84" s="11" t="inlineStr">
+        <is>
+          <t>DPDPA-S28</t>
+        </is>
+      </c>
+      <c r="D84" s="11" t="inlineStr">
+        <is>
+          <t>Correction</t>
+        </is>
+      </c>
+      <c r="E84" s="11" t="inlineStr">
+        <is>
+          <t>Sets the Board's inquiry procedure as an independent, digital-by-design body — determining if grounds exist to proceed, natural-justice-based inquiries, civil-court-equivalent evidentiary powers, and the ability to close/warn/cost frivolous complaints.</t>
+        </is>
+      </c>
+      <c r="F84" s="11" t="inlineStr">
+        <is>
+          <t>Sets the Board's inquiry procedure as an independent, digital-by-design body — determining if grounds exist to proceed, natural-justice-based inquiries, civil-court-equivalent evidentiary powers, and the ability to close/warn/cost frivolous complaints.</t>
+        </is>
+      </c>
+      <c r="G84" s="11" t="inlineStr">
+        <is>
+          <t>Digital Personal Data Protection Act, 2023 (Act No. 22 of 2023)</t>
+        </is>
+      </c>
+      <c r="H84" s="11" t="inlineStr">
+        <is>
+          <t>https://www.meity.gov.in/static/uploads/2024/06/2bf1f0e9f04e6fb4f8fef35e82c42aa5.pdf</t>
+        </is>
+      </c>
+      <c r="I84" s="11" t="inlineStr">
+        <is>
+          <t>cowork:claude-sonnet-5 + claude-opus (manual re-verification against official PDF)</t>
+        </is>
+      </c>
+      <c r="J84" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K84" s="11" t="inlineStr">
+        <is>
+          <t>Pending Review</t>
+        </is>
+      </c>
+      <c r="L84" s="11" t="n"/>
+      <c r="M84" s="11" t="n"/>
+      <c r="N84" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O84" s="11" t="inlineStr">
+        <is>
+          <t>One-time manual data-quality correction (not a detected regulatory change): DB text diverged from the enacted Act at seeding time. Corrected against a freshly downloaded, hash-verified copy of the official PDF, independently checked with a second extraction tool and a second review pass. review_status left 'Pending Review' since no human has read the literal corrected text line-by-line yet — see docs/act_table_audit_2026-09-23.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="11" t="inlineStr">
+        <is>
+          <t>CHG-0037</t>
+        </is>
+      </c>
+      <c r="B85" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-23T01:45:00</t>
+        </is>
+      </c>
+      <c r="C85" s="11" t="inlineStr">
+        <is>
+          <t>DPDPA-S42</t>
+        </is>
+      </c>
+      <c r="D85" s="11" t="inlineStr">
+        <is>
+          <t>Correction</t>
+        </is>
+      </c>
+      <c r="E85" s="11" t="inlineStr">
+        <is>
+          <t>Allows the Central Government to amend the penalty Schedule by notification, capped at no more than double the originally enacted penalty amounts; amendments take effect as if enacted, from the notification date.</t>
+        </is>
+      </c>
+      <c r="F85" s="11" t="inlineStr">
+        <is>
+          <t>Allows the Central Government to amend the penalty Schedule by notification, capped at no more than double the originally enacted penalty amounts; amendments take effect as if enacted, from the notification date.</t>
+        </is>
+      </c>
+      <c r="G85" s="11" t="inlineStr">
+        <is>
+          <t>Digital Personal Data Protection Act, 2023 (Act No. 22 of 2023)</t>
+        </is>
+      </c>
+      <c r="H85" s="11" t="inlineStr">
+        <is>
+          <t>https://www.meity.gov.in/static/uploads/2024/06/2bf1f0e9f04e6fb4f8fef35e82c42aa5.pdf</t>
+        </is>
+      </c>
+      <c r="I85" s="11" t="inlineStr">
+        <is>
+          <t>cowork:claude-sonnet-5 + claude-opus (manual re-verification against official PDF)</t>
+        </is>
+      </c>
+      <c r="J85" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K85" s="11" t="inlineStr">
+        <is>
+          <t>Pending Review</t>
+        </is>
+      </c>
+      <c r="L85" s="11" t="n"/>
+      <c r="M85" s="11" t="n"/>
+      <c r="N85" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O85" s="11" t="inlineStr">
+        <is>
+          <t>One-time manual data-quality correction (not a detected regulatory change): DB text diverged from the enacted Act at seeding time. Corrected against a freshly downloaded, hash-verified copy of the official PDF, independently checked with a second extraction tool and a second review pass. review_status left 'Pending Review' since no human has read the literal corrected text line-by-line yet — see docs/act_table_audit_2026-09-23.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="11" t="inlineStr">
+        <is>
+          <t>CHG-0038</t>
+        </is>
+      </c>
+      <c r="B86" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-23T01:45:00</t>
+        </is>
+      </c>
+      <c r="C86" s="11" t="inlineStr">
+        <is>
+          <t>DPDPA-S44.1_3</t>
+        </is>
+      </c>
+      <c r="D86" s="11" t="inlineStr">
+        <is>
+          <t>Correction</t>
+        </is>
+      </c>
+      <c r="E86" s="11" t="inlineStr">
+        <is>
+          <t>Amends the TRAI Act, 1997 to fold in the DPDP Appellate Tribunal, and amends the RTI Act, 2005 to redefine what counts as exempt 'personal information' by reference to this Act.</t>
+        </is>
+      </c>
+      <c r="F86" s="11" t="inlineStr">
+        <is>
+          <t>Amends the TRAI Act, 1997 to replace its Appellate Tribunal list with the IT Act, Airports Economic Regulatory Authority Act, and DPDP Act Appellate Tribunals, and amends the RTI Act, 2005 to add a standalone exemption for 'information which relates to personal information'.</t>
+        </is>
+      </c>
+      <c r="G86" s="11" t="inlineStr">
+        <is>
+          <t>Digital Personal Data Protection Act, 2023 (Act No. 22 of 2023)</t>
+        </is>
+      </c>
+      <c r="H86" s="11" t="inlineStr">
+        <is>
+          <t>https://www.meity.gov.in/static/uploads/2024/06/2bf1f0e9f04e6fb4f8fef35e82c42aa5.pdf</t>
+        </is>
+      </c>
+      <c r="I86" s="11" t="inlineStr">
+        <is>
+          <t>cowork:claude-sonnet-5 + claude-opus (manual re-verification against official PDF)</t>
+        </is>
+      </c>
+      <c r="J86" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K86" s="11" t="inlineStr">
+        <is>
+          <t>Pending Review</t>
+        </is>
+      </c>
+      <c r="L86" s="11" t="n"/>
+      <c r="M86" s="11" t="n"/>
+      <c r="N86" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O86" s="11" t="inlineStr">
+        <is>
+          <t>One-time manual data-quality correction (not a detected regulatory change): DB text diverged from the enacted Act at seeding time. Corrected against a freshly downloaded, hash-verified copy of the official PDF, independently checked with a second extraction tool and a second review pass. review_status left 'Pending Review' since no human has read the literal corrected text line-by-line yet — see docs/act_table_audit_2026-09-23.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="11" t="inlineStr">
+        <is>
+          <t>CHG-0039</t>
+        </is>
+      </c>
+      <c r="B87" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-23T01:45:00</t>
+        </is>
+      </c>
+      <c r="C87" s="11" t="inlineStr">
+        <is>
+          <t>DPDPA-S44.2</t>
+        </is>
+      </c>
+      <c r="D87" s="11" t="inlineStr">
+        <is>
+          <t>Correction</t>
+        </is>
+      </c>
+      <c r="E87" s="11" t="inlineStr">
+        <is>
+          <t>Amends the Information Technology Act, 2000 — removes the old compensation-for-data-breach provision (Section 43A, since this Act now governs that), and cross-references this Act in two other IT Act provisions.</t>
+        </is>
+      </c>
+      <c r="F87" s="11" t="inlineStr">
+        <is>
+          <t>Amends the Information Technology Act, 2000 — removes the old compensation-for-data-breach provision (Section 43A, since this Act now governs that), inserts a cross-reference to this Act into Section 81's proviso, and omits a now-redundant RTI-exemption clause (Section 87(2)(ob)).</t>
+        </is>
+      </c>
+      <c r="G87" s="11" t="inlineStr">
+        <is>
+          <t>Digital Personal Data Protection Act, 2023 (Act No. 22 of 2023)</t>
+        </is>
+      </c>
+      <c r="H87" s="11" t="inlineStr">
+        <is>
+          <t>https://www.meity.gov.in/static/uploads/2024/06/2bf1f0e9f04e6fb4f8fef35e82c42aa5.pdf</t>
+        </is>
+      </c>
+      <c r="I87" s="11" t="inlineStr">
+        <is>
+          <t>cowork:claude-sonnet-5 + claude-opus (manual re-verification against official PDF)</t>
+        </is>
+      </c>
+      <c r="J87" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K87" s="11" t="inlineStr">
+        <is>
+          <t>Pending Review</t>
+        </is>
+      </c>
+      <c r="L87" s="11" t="n"/>
+      <c r="M87" s="11" t="n"/>
+      <c r="N87" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O87" s="11" t="inlineStr">
+        <is>
+          <t>One-time manual data-quality correction (not a detected regulatory change): DB text diverged from the enacted Act at seeding time. Corrected against a freshly downloaded, hash-verified copy of the official PDF, independently checked with a second extraction tool and a second review pass. review_status left 'Pending Review' since no human has read the literal corrected text line-by-line yet — see docs/act_table_audit_2026-09-23.md.</t>
         </is>
       </c>
     </row>
@@ -12897,7 +13366,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -12961,7 +13430,7 @@
     <row r="2">
       <c r="A2" s="11" t="inlineStr">
         <is>
-          <t>SRC-0001</t>
+          <t>SRC-0003</t>
         </is>
       </c>
       <c r="B2" s="11" t="inlineStr">
@@ -12971,12 +13440,12 @@
       </c>
       <c r="C2" s="11" t="inlineStr">
         <is>
-          <t>Digital Personal Data Protection Rules, 2025 — Gazette Notification G.S.R. 846(E)</t>
+          <t>Gazette Notification G.S.R. 843(E), 13 Nov 2025 (Act commencement schedule)</t>
         </is>
       </c>
       <c r="D2" s="11" t="inlineStr">
         <is>
-          <t>https://www.meity.gov.in/static/uploads/2025/11/53450e6e5dc0bfa85ebd78686cadad39.pdf</t>
+          <t>user-upload:Timelines_for_enforcement_of_DPDPA.pdf</t>
         </is>
       </c>
       <c r="E2" s="11" t="inlineStr">
@@ -13001,14 +13470,14 @@
       </c>
       <c r="I2" s="11" t="inlineStr">
         <is>
-          <t>CHG-0002,CHG-0003,CHG-0004,CHG-0005,CHG-0006,CHG-0007,CHG-0008,CHG-0009,CHG-0010,CHG-0011,CHG-0012,CHG-0013,CHG-0014,CHG-0015,CHG-0016,CHG-0017,CHG-0018,CHG-0019,CHG-0020,CHG-0021,CHG-0022,CHG-0023,CHG-0024,CHG-0025,CHG-0026,CHG-0027,CHG-0028,CHG-0029,CHG-0030,CHG-0031,CHG-0032</t>
+          <t>CHG-A0001,CHG-A0002,CHG-A0003,CHG-A0004,CHG-A0005,CHG-A0006,CHG-A0007,CHG-A0008,CHG-A0009,CHG-A0010,CHG-A0011,CHG-A0012,CHG-A0013,CHG-A0014,CHG-A0015,CHG-A0016,CHG-A0017,CHG-A0018,CHG-A0019,CHG-A0020,CHG-A0021,CHG-A0022,CHG-A0023,CHG-A0024,CHG-A0025,CHG-A0026,CHG-A0027,CHG-A0028,CHG-A0029,CHG-A0030,CHG-A0031,CHG-A0032,CHG-A0033,CHG-A0034,CHG-A0035,CHG-A0036,CHG-A0037,CHG-A0038,CHG-A0039,CHG-A0040,CHG-A0041,CHG-A0042,CHG-A0043,CHG-A0044,CHG-A0045,CHG-A0046,CHG-A0047,CHG-A0048</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
         <is>
-          <t>SRC-0002</t>
+          <t>SRC-0001</t>
         </is>
       </c>
       <c r="B3" s="11" t="inlineStr">
@@ -13018,86 +13487,156 @@
       </c>
       <c r="C3" s="11" t="inlineStr">
         <is>
-          <t>Digital Personal Data Protection Act, 2023 (Act No. 22 of 2023)</t>
+          <t>DPDP Rules, 2025 — MeitY PDF (G.S.R. 846(E))</t>
         </is>
       </c>
       <c r="D3" s="11" t="inlineStr">
         <is>
-          <t>https://www.meity.gov.in/static/uploads/2024/06/2bf1f0e9f04e6fb4f8fef35e82c42aa5.pdf</t>
-        </is>
-      </c>
-      <c r="E3" s="11" t="inlineStr">
-        <is>
-          <t>2023-08-11</t>
-        </is>
-      </c>
+          <t>https://www.meity.gov.in/static/uploads/2025/11/53450e6e5dc0bfa85ebd78686cadad39.pdf</t>
+        </is>
+      </c>
+      <c r="E3" s="11" t="n"/>
       <c r="F3" s="11" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G3" s="11" t="inlineStr">
         <is>
-          <t>manual-seed-not-hashed</t>
+          <t>76094c7228c8dbff357281552fa2b052fe363303eb8b2c33ee5361d38883070d</t>
         </is>
       </c>
       <c r="H3" s="11" t="inlineStr">
         <is>
-          <t>Processed</t>
+          <t>No Change Detected</t>
         </is>
       </c>
       <c r="I3" s="11" t="inlineStr">
         <is>
-          <t>CHG-A0001,CHG-A0002,CHG-A0003,CHG-A0004,CHG-A0005,CHG-A0006,CHG-A0007,CHG-A0008,CHG-A0009,CHG-A0010,CHG-A0011,CHG-A0012,CHG-A0013,CHG-A0014,CHG-A0015,CHG-A0016,CHG-A0017,CHG-A0018,CHG-A0019,CHG-A0020,CHG-A0021,CHG-A0022,CHG-A0023,CHG-A0024,CHG-A0025,CHG-A0026,CHG-A0027,CHG-A0028,CHG-A0029,CHG-A0030,CHG-A0031,CHG-A0032,CHG-A0033,CHG-A0034,CHG-A0035,CHG-A0036,CHG-A0037,CHG-A0038,CHG-A0039,CHG-A0040,CHG-A0041,CHG-A0042,CHG-A0043,CHG-A0044,CHG-A0045,CHG-A0046,CHG-A0047,CHG-A0048</t>
+          <t>CHG-0002,CHG-0003,CHG-0004,CHG-0005,CHG-0006,CHG-0007,CHG-0008,CHG-0009,CHG-0010,CHG-0011,CHG-0012,CHG-0013,CHG-0014,CHG-0015,CHG-0016,CHG-0017,CHG-0018,CHG-0019,CHG-0020,CHG-0021,CHG-0022,CHG-0023,CHG-0024,CHG-0025,CHG-0026,CHG-0027,CHG-0028,CHG-0029,CHG-0030,CHG-0031,CHG-0032</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
-          <t>SRC-0003</t>
+          <t>SRC-0002</t>
         </is>
       </c>
       <c r="B4" s="11" t="inlineStr">
         <is>
+          <t>MeitY</t>
+        </is>
+      </c>
+      <c r="C4" s="11" t="inlineStr">
+        <is>
+          <t>DPDP Act, 2023 — MeitY PDF</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="inlineStr">
+        <is>
+          <t>https://www.meity.gov.in/static/uploads/2024/06/2bf1f0e9f04e6fb4f8fef35e82c42aa5.pdf</t>
+        </is>
+      </c>
+      <c r="E4" s="11" t="n"/>
+      <c r="F4" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G4" s="11" t="inlineStr">
+        <is>
+          <t>f15bda1ff8065c68f8e1cc57c50616264afeb49d72cfc48d1e92a2a3c473c1d2</t>
+        </is>
+      </c>
+      <c r="H4" s="11" t="inlineStr">
+        <is>
+          <t>No Change Detected</t>
+        </is>
+      </c>
+      <c r="I4" s="11" t="inlineStr">
+        <is>
+          <t>CHG-A0001,CHG-A0002,CHG-A0003,CHG-A0004,CHG-A0005,CHG-A0006,CHG-A0007,CHG-A0008,CHG-A0009,CHG-A0010,CHG-A0011,CHG-A0012,CHG-A0013,CHG-A0014,CHG-A0015,CHG-A0016,CHG-A0017,CHG-A0018,CHG-A0019,CHG-A0020,CHG-A0021,CHG-A0022,CHG-A0023,CHG-A0024,CHG-A0025,CHG-A0026,CHG-A0027,CHG-A0028,CHG-A0029,CHG-A0030,CHG-A0031,CHG-A0032,CHG-A0033,CHG-A0034,CHG-A0035,CHG-A0036,CHG-A0037,CHG-A0038,CHG-A0039,CHG-A0040,CHG-A0041,CHG-A0042,CHG-A0043,CHG-A0044,CHG-A0045,CHG-A0046,CHG-A0047,CHG-A0048</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>SRC-0004</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>PIB</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>PIB — All Press Releases (English)</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t>https://www.pib.gov.in/allRel.aspx</t>
+        </is>
+      </c>
+      <c r="E5" s="11" t="n"/>
+      <c r="F5" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G5" s="11" t="inlineStr">
+        <is>
+          <t>d38842055f43a4f6ee39929156a2c93772a0b128ba3ab14f887a64fcf1c77e89</t>
+        </is>
+      </c>
+      <c r="H5" s="11" t="inlineStr">
+        <is>
+          <t>No Change Detected</t>
+        </is>
+      </c>
+      <c r="I5" s="11" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>SRC-0005</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
           <t>eGazette</t>
         </is>
       </c>
-      <c r="C4" s="11" t="inlineStr">
-        <is>
-          <t>Gazette Notification G.S.R. 843(E), 13 Nov 2025 (Act commencement schedule)</t>
-        </is>
-      </c>
-      <c r="D4" s="11" t="inlineStr">
-        <is>
-          <t>user-upload:Timelines_for_enforcement_of_DPDPA.pdf</t>
-        </is>
-      </c>
-      <c r="E4" s="11" t="inlineStr">
-        <is>
-          <t>2025-11-13</t>
-        </is>
-      </c>
-      <c r="F4" s="11" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="G4" s="11" t="inlineStr">
-        <is>
-          <t>manual-seed-not-hashed</t>
-        </is>
-      </c>
-      <c r="H4" s="11" t="inlineStr">
-        <is>
-          <t>Processed</t>
-        </is>
-      </c>
-      <c r="I4" s="11" t="inlineStr">
-        <is>
-          <t>CHG-A0001,CHG-A0002,CHG-A0003,CHG-A0004,CHG-A0005,CHG-A0006,CHG-A0007,CHG-A0008,CHG-A0009,CHG-A0010,CHG-A0011,CHG-A0012,CHG-A0013,CHG-A0014,CHG-A0015,CHG-A0016,CHG-A0017,CHG-A0018,CHG-A0019,CHG-A0020,CHG-A0021,CHG-A0022,CHG-A0023,CHG-A0024,CHG-A0025,CHG-A0026,CHG-A0027,CHG-A0028,CHG-A0029,CHG-A0030,CHG-A0031,CHG-A0032,CHG-A0033,CHG-A0034,CHG-A0035,CHG-A0036,CHG-A0037,CHG-A0038,CHG-A0039,CHG-A0040,CHG-A0041,CHG-A0042,CHG-A0043,CHG-A0044,CHG-A0045,CHG-A0046,CHG-A0047,CHG-A0048</t>
-        </is>
-      </c>
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t>eGazette — Home (best-effort; no stable search endpoint confirmed)</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>https://egazette.gov.in/</t>
+        </is>
+      </c>
+      <c r="E6" s="11" t="n"/>
+      <c r="F6" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G6" s="11" t="inlineStr">
+        <is>
+          <t>ca96805449aa0e1eb65ff8f302650b129a742ad9902372ad6409b3dd18248582</t>
+        </is>
+      </c>
+      <c r="H6" s="11" t="inlineStr">
+        <is>
+          <t>No Change Detected</t>
+        </is>
+      </c>
+      <c r="I6" s="11" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="2">

--- a/data/DPDP_Rules_Tracker.xlsx
+++ b/data/DPDP_Rules_Tracker.xlsx
@@ -126,7 +126,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -163,6 +163,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1069,7 +1075,7 @@
       </c>
       <c r="J3" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="K3" s="12" t="inlineStr">
@@ -1094,7 +1100,7 @@
       <c r="P3" s="12" t="n"/>
       <c r="Q3" s="12" t="inlineStr">
         <is>
-          <t>CHG-0002</t>
+          <t>CHG-0086</t>
         </is>
       </c>
       <c r="R3" s="12" t="inlineStr">
@@ -1106,7 +1112,11 @@
         <f>IF(I3="","",IF(TODAY()&gt;=DATEVALUE(I3),"Yes","No"))</f>
         <v/>
       </c>
-      <c r="T3" s="14" t="n"/>
+      <c r="T3" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-23 (CHG-0086)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="12" t="inlineStr">
@@ -1156,7 +1166,7 @@
       </c>
       <c r="J4" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="K4" s="12" t="inlineStr">
@@ -1186,7 +1196,7 @@
       </c>
       <c r="R4" s="12" t="inlineStr">
         <is>
-          <t>Currently in force.</t>
+          <t>Currently in force. Text rebuilt verbatim 2026-09-23 from the official Act PDF (SHA-256 4deb2398...7d15) -- see docs/act_verbatim_rebuild_2026-09-23.md.</t>
         </is>
       </c>
       <c r="S4" s="14">
@@ -1330,7 +1340,7 @@
       </c>
       <c r="J6" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="K6" s="12" t="inlineStr">
@@ -1360,7 +1370,7 @@
       </c>
       <c r="R6" s="12" t="inlineStr">
         <is>
-          <t>In force eighteen months after notification (G.S.R. 843(E), group (c)) — not yet operative.</t>
+          <t>In force eighteen months after notification (G.S.R. 843(E), group (c)) — not yet operative. Text rebuilt verbatim 2026-09-23 from the official Act PDF (SHA-256 4deb2398...7d15) -- see docs/act_verbatim_rebuild_2026-09-23.md.</t>
         </is>
       </c>
       <c r="S6" s="14">
@@ -1504,7 +1514,7 @@
       </c>
       <c r="J8" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="K8" s="12" t="inlineStr">
@@ -1534,7 +1544,7 @@
       </c>
       <c r="R8" s="12" t="inlineStr">
         <is>
-          <t>In force eighteen months after notification (G.S.R. 843(E), group (c)) — not yet operative.</t>
+          <t>In force eighteen months after notification (G.S.R. 843(E), group (c)) — not yet operative. Text rebuilt verbatim 2026-09-23 from the official Act PDF (SHA-256 4deb2398...7d15) -- see docs/act_verbatim_rebuild_2026-09-23.md.</t>
         </is>
       </c>
       <c r="S8" s="14">
@@ -1678,7 +1688,7 @@
       </c>
       <c r="J10" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="K10" s="12" t="inlineStr">
@@ -1708,7 +1718,7 @@
       </c>
       <c r="R10" s="12" t="inlineStr">
         <is>
-          <t>In force eighteen months after notification (G.S.R. 843(E), group (c)) — not yet operative.</t>
+          <t>In force eighteen months after notification (G.S.R. 843(E), group (c)) — not yet operative. Text rebuilt verbatim 2026-09-23 from the official Act PDF (SHA-256 4deb2398...7d15) -- see docs/act_verbatim_rebuild_2026-09-23.md.</t>
         </is>
       </c>
       <c r="S10" s="14">
@@ -1852,7 +1862,7 @@
       </c>
       <c r="J12" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="K12" s="12" t="inlineStr">
@@ -1882,7 +1892,7 @@
       </c>
       <c r="R12" s="12" t="inlineStr">
         <is>
-          <t>In force eighteen months after notification (G.S.R. 843(E), group (c)) — not yet operative.</t>
+          <t>In force eighteen months after notification (G.S.R. 843(E), group (c)) — not yet operative. Text rebuilt verbatim 2026-09-23 from the official Act PDF (SHA-256 4deb2398...7d15) -- see docs/act_verbatim_rebuild_2026-09-23.md.</t>
         </is>
       </c>
       <c r="S12" s="14">
@@ -2026,7 +2036,7 @@
       </c>
       <c r="J14" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="K14" s="12" t="inlineStr">
@@ -2056,7 +2066,7 @@
       </c>
       <c r="R14" s="12" t="inlineStr">
         <is>
-          <t>In force one year after notification (G.S.R. 843(E), group (b)).</t>
+          <t>In force one year after notification (G.S.R. 843(E), group (b)). Text rebuilt verbatim 2026-09-23 from the official Act PDF (SHA-256 4deb2398...7d15) -- see docs/act_verbatim_rebuild_2026-09-23.md.</t>
         </is>
       </c>
       <c r="S14" s="14">
@@ -2230,7 +2240,7 @@
       </c>
       <c r="R16" s="12" t="inlineStr">
         <is>
-          <t>In force eighteen months after notification (G.S.R. 843(E), group (c)) — not yet operative. Text corrected 2026-09-23 against the official Act PDF (SHA-256 4deb2398...7d15), re-verified against a hash-confirmed copy of the source PDF (second extraction pass; Sonnet+Opus review) — see docs/act_table_audit_2026-09-23.md.</t>
+          <t>In force eighteen months after notification (G.S.R. 843(E), group (c)) — not yet operative. Text rebuilt verbatim 2026-09-23 from the official Act PDF (SHA-256 4deb2398...7d15) -- see docs/act_verbatim_rebuild_2026-09-23.md.</t>
         </is>
       </c>
       <c r="S16" s="14">
@@ -2374,7 +2384,7 @@
       </c>
       <c r="J18" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="K18" s="12" t="inlineStr">
@@ -2404,7 +2414,7 @@
       </c>
       <c r="R18" s="12" t="inlineStr">
         <is>
-          <t>In force eighteen months after notification (G.S.R. 843(E), group (c)) — not yet operative.</t>
+          <t>In force eighteen months after notification (G.S.R. 843(E), group (c)) — not yet operative. Text rebuilt verbatim 2026-09-23 from the official Act PDF (SHA-256 4deb2398...7d15) -- see docs/act_verbatim_rebuild_2026-09-23.md.</t>
         </is>
       </c>
       <c r="S18" s="14">
@@ -2548,7 +2558,7 @@
       </c>
       <c r="J20" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="K20" s="12" t="inlineStr">
@@ -2578,7 +2588,7 @@
       </c>
       <c r="R20" s="12" t="inlineStr">
         <is>
-          <t>In force eighteen months after notification (G.S.R. 843(E), group (c)) — not yet operative.</t>
+          <t>In force eighteen months after notification (G.S.R. 843(E), group (c)) — not yet operative. Text rebuilt verbatim 2026-09-23 from the official Act PDF (SHA-256 4deb2398...7d15) -- see docs/act_verbatim_rebuild_2026-09-23.md.</t>
         </is>
       </c>
       <c r="S20" s="14">
@@ -2722,7 +2732,7 @@
       </c>
       <c r="J22" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="K22" s="12" t="inlineStr">
@@ -2752,7 +2762,7 @@
       </c>
       <c r="R22" s="12" t="inlineStr">
         <is>
-          <t>In force eighteen months after notification (G.S.R. 843(E), group (c)) — not yet operative.</t>
+          <t>In force eighteen months after notification (G.S.R. 843(E), group (c)) — not yet operative. Text rebuilt verbatim 2026-09-23 from the official Act PDF (SHA-256 4deb2398...7d15) -- see docs/act_verbatim_rebuild_2026-09-23.md.</t>
         </is>
       </c>
       <c r="S22" s="14">
@@ -2896,7 +2906,7 @@
       </c>
       <c r="J24" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="K24" s="12" t="inlineStr">
@@ -2926,7 +2936,7 @@
       </c>
       <c r="R24" s="12" t="inlineStr">
         <is>
-          <t>In force eighteen months after notification (G.S.R. 843(E), group (c)) — not yet operative.</t>
+          <t>In force eighteen months after notification (G.S.R. 843(E), group (c)) — not yet operative. Text rebuilt verbatim 2026-09-23 from the official Act PDF (SHA-256 4deb2398...7d15) -- see docs/act_verbatim_rebuild_2026-09-23.md.</t>
         </is>
       </c>
       <c r="S24" s="14">
@@ -3070,7 +3080,7 @@
       </c>
       <c r="J26" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="K26" s="12" t="inlineStr">
@@ -3100,7 +3110,7 @@
       </c>
       <c r="R26" s="12" t="inlineStr">
         <is>
-          <t>In force eighteen months after notification (G.S.R. 843(E), group (c)) — not yet operative.</t>
+          <t>In force eighteen months after notification (G.S.R. 843(E), group (c)) — not yet operative. Text rebuilt verbatim 2026-09-23 from the official Act PDF (SHA-256 4deb2398...7d15) -- see docs/act_verbatim_rebuild_2026-09-23.md.</t>
         </is>
       </c>
       <c r="S26" s="14">
@@ -3244,7 +3254,7 @@
       </c>
       <c r="J28" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="K28" s="12" t="inlineStr">
@@ -3274,7 +3284,7 @@
       </c>
       <c r="R28" s="12" t="inlineStr">
         <is>
-          <t>In force eighteen months after notification (G.S.R. 843(E), group (c)) — not yet operative.</t>
+          <t>In force eighteen months after notification (G.S.R. 843(E), group (c)) — not yet operative. Text rebuilt verbatim 2026-09-23 from the official Act PDF (SHA-256 4deb2398...7d15) -- see docs/act_verbatim_rebuild_2026-09-23.md.</t>
         </is>
       </c>
       <c r="S28" s="14">
@@ -3331,7 +3341,7 @@
       </c>
       <c r="J29" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="K29" s="12" t="inlineStr">
@@ -3356,7 +3366,7 @@
       <c r="P29" s="12" t="n"/>
       <c r="Q29" s="12" t="inlineStr">
         <is>
-          <t>CHG-0015</t>
+          <t>CHG-0087</t>
         </is>
       </c>
       <c r="R29" s="12" t="inlineStr">
@@ -3368,7 +3378,11 @@
         <f>IF(I29="","",IF(TODAY()&gt;=DATEVALUE(I29),"Yes","No"))</f>
         <v/>
       </c>
-      <c r="T29" s="14" t="n"/>
+      <c r="T29" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-23 (CHG-0087)</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="12" t="inlineStr">
@@ -3418,7 +3432,7 @@
       </c>
       <c r="J30" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="K30" s="12" t="inlineStr">
@@ -3448,7 +3462,7 @@
       </c>
       <c r="R30" s="12" t="inlineStr">
         <is>
-          <t>In force eighteen months after notification (G.S.R. 843(E), group (c)) — not yet operative.</t>
+          <t>In force eighteen months after notification (G.S.R. 843(E), group (c)) — not yet operative. Text rebuilt verbatim 2026-09-23 from the official Act PDF (SHA-256 4deb2398...7d15) -- see docs/act_verbatim_rebuild_2026-09-23.md.</t>
         </is>
       </c>
       <c r="S30" s="14">
@@ -3592,7 +3606,7 @@
       </c>
       <c r="J32" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="K32" s="12" t="inlineStr">
@@ -3622,7 +3636,7 @@
       </c>
       <c r="R32" s="12" t="inlineStr">
         <is>
-          <t>In force eighteen months after notification (G.S.R. 843(E), group (c)) — not yet operative.</t>
+          <t>In force eighteen months after notification (G.S.R. 843(E), group (c)) — not yet operative. Text rebuilt verbatim 2026-09-23 from the official Act PDF (SHA-256 4deb2398...7d15) -- see docs/act_verbatim_rebuild_2026-09-23.md.</t>
         </is>
       </c>
       <c r="S32" s="14">
@@ -3766,7 +3780,7 @@
       </c>
       <c r="J34" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="K34" s="12" t="inlineStr">
@@ -3796,7 +3810,7 @@
       </c>
       <c r="R34" s="12" t="inlineStr">
         <is>
-          <t>In force eighteen months after notification (G.S.R. 843(E), group (c)) — not yet operative.</t>
+          <t>In force eighteen months after notification (G.S.R. 843(E), group (c)) — not yet operative. Text rebuilt verbatim 2026-09-23 from the official Act PDF (SHA-256 4deb2398...7d15) -- see docs/act_verbatim_rebuild_2026-09-23.md.</t>
         </is>
       </c>
       <c r="S34" s="14">
@@ -3915,7 +3929,7 @@
       </c>
       <c r="E36" s="12" t="inlineStr">
         <is>
-          <t>Sets broad exemptions from most of the Act's obligations — for legal-right enforcement, judicial/regulatory processing, crime prevention/investigation, foreign-contract processing of non-Indian data, M&amp;A restructuring, and defaulter financial-information processing — plus a notified security-instrumentality exemption, a self-executing research/archiving/statistical exemption, notified exemptions for specific Data Fiduciaries (including startups) from listed sections, a conditional State-processing exemption from parts of Sections 8 and 12, and a five-year sunset power to exempt any Data Fiduciary from any provision by notification.</t>
+          <t>Sets broad exemptions from most of the Act's obligations — for legal-right enforcement, judicial/regulatory processing, crime prevention/investigation, foreign-contract processing of non-Indian data, M&amp;A restructuring, and defaulter financial-information processing — plus government-notified exemptions for security instrumentalities, research/statistics, and startups.</t>
         </is>
       </c>
       <c r="F36" s="13" t="inlineStr">
@@ -3970,7 +3984,7 @@
       </c>
       <c r="R36" s="12" t="inlineStr">
         <is>
-          <t>In force eighteen months after notification (G.S.R. 843(E), group (c)) — not yet operative. Text corrected 2026-09-23 against the official Act PDF (SHA-256 4deb2398...7d15), re-verified against a hash-confirmed copy of the source PDF (second extraction pass; Sonnet+Opus review) — see docs/act_table_audit_2026-09-23.md.</t>
+          <t>In force eighteen months after notification (G.S.R. 843(E), group (c)) — not yet operative. Text rebuilt verbatim 2026-09-23 from the official Act PDF (SHA-256 4deb2398...7d15) -- see docs/act_verbatim_rebuild_2026-09-23.md.</t>
         </is>
       </c>
       <c r="S36" s="14">
@@ -4114,7 +4128,7 @@
       </c>
       <c r="J38" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="K38" s="12" t="inlineStr">
@@ -4144,7 +4158,7 @@
       </c>
       <c r="R38" s="12" t="inlineStr">
         <is>
-          <t>Currently in force.</t>
+          <t>Currently in force. Text rebuilt verbatim 2026-09-23 from the official Act PDF (SHA-256 4deb2398...7d15) -- see docs/act_verbatim_rebuild_2026-09-23.md.</t>
         </is>
       </c>
       <c r="S38" s="14">
@@ -4288,7 +4302,7 @@
       </c>
       <c r="J40" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="K40" s="12" t="inlineStr">
@@ -4318,7 +4332,7 @@
       </c>
       <c r="R40" s="12" t="inlineStr">
         <is>
-          <t>Currently in force.</t>
+          <t>Currently in force. Text rebuilt verbatim 2026-09-23 from the official Act PDF (SHA-256 4deb2398...7d15) -- see docs/act_verbatim_rebuild_2026-09-23.md.</t>
         </is>
       </c>
       <c r="S40" s="14">
@@ -4462,7 +4476,7 @@
       </c>
       <c r="J42" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="K42" s="12" t="inlineStr">
@@ -4492,7 +4506,7 @@
       </c>
       <c r="R42" s="12" t="inlineStr">
         <is>
-          <t>Currently in force.</t>
+          <t>Currently in force. Text rebuilt verbatim 2026-09-23 from the official Act PDF (SHA-256 4deb2398...7d15) -- see docs/act_verbatim_rebuild_2026-09-23.md.</t>
         </is>
       </c>
       <c r="S42" s="14">
@@ -4636,7 +4650,7 @@
       </c>
       <c r="J44" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="K44" s="12" t="inlineStr">
@@ -4666,7 +4680,7 @@
       </c>
       <c r="R44" s="12" t="inlineStr">
         <is>
-          <t>Currently in force.</t>
+          <t>Currently in force. Text rebuilt verbatim 2026-09-23 from the official Act PDF (SHA-256 4deb2398...7d15) -- see docs/act_verbatim_rebuild_2026-09-23.md.</t>
         </is>
       </c>
       <c r="S44" s="14">
@@ -4810,7 +4824,7 @@
       </c>
       <c r="J46" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="K46" s="12" t="inlineStr">
@@ -4840,7 +4854,7 @@
       </c>
       <c r="R46" s="12" t="inlineStr">
         <is>
-          <t>Currently in force.</t>
+          <t>Currently in force. Text rebuilt verbatim 2026-09-23 from the official Act PDF (SHA-256 4deb2398...7d15) -- see docs/act_verbatim_rebuild_2026-09-23.md.</t>
         </is>
       </c>
       <c r="S46" s="14">
@@ -4984,7 +4998,7 @@
       </c>
       <c r="J48" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="K48" s="12" t="inlineStr">
@@ -5014,7 +5028,7 @@
       </c>
       <c r="R48" s="12" t="inlineStr">
         <is>
-          <t>Currently in force.</t>
+          <t>Currently in force. Text rebuilt verbatim 2026-09-23 from the official Act PDF (SHA-256 4deb2398...7d15) -- see docs/act_verbatim_rebuild_2026-09-23.md.</t>
         </is>
       </c>
       <c r="S48" s="14">
@@ -5071,7 +5085,7 @@
       </c>
       <c r="J49" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="K49" s="12" t="inlineStr">
@@ -5096,7 +5110,7 @@
       <c r="P49" s="12" t="n"/>
       <c r="Q49" s="12" t="inlineStr">
         <is>
-          <t>CHG-0025</t>
+          <t>CHG-0088</t>
         </is>
       </c>
       <c r="R49" s="12" t="inlineStr">
@@ -5108,7 +5122,11 @@
         <f>IF(I49="","",IF(TODAY()&gt;=DATEVALUE(I49),"Yes","No"))</f>
         <v/>
       </c>
-      <c r="T49" s="14" t="n"/>
+      <c r="T49" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-23 (CHG-0088)</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="12" t="inlineStr">
@@ -5158,7 +5176,7 @@
       </c>
       <c r="J50" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="K50" s="12" t="inlineStr">
@@ -5188,7 +5206,7 @@
       </c>
       <c r="R50" s="12" t="inlineStr">
         <is>
-          <t>Currently in force.</t>
+          <t>Currently in force. Text rebuilt verbatim 2026-09-23 from the official Act PDF (SHA-256 4deb2398...7d15) -- see docs/act_verbatim_rebuild_2026-09-23.md.</t>
         </is>
       </c>
       <c r="S50" s="14">
@@ -5332,7 +5350,7 @@
       </c>
       <c r="J52" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="K52" s="12" t="inlineStr">
@@ -5362,7 +5380,7 @@
       </c>
       <c r="R52" s="12" t="inlineStr">
         <is>
-          <t>Currently in force.</t>
+          <t>Currently in force. Text rebuilt verbatim 2026-09-23 from the official Act PDF (SHA-256 4deb2398...7d15) -- see docs/act_verbatim_rebuild_2026-09-23.md.</t>
         </is>
       </c>
       <c r="S52" s="14">
@@ -5481,7 +5499,7 @@
       </c>
       <c r="E54" s="12" t="inlineStr">
         <is>
-          <t>Gives the Chairperson general superintendence over Board administrative matters, the power to authorise any officer to scrutinise matters addressed to the Board, and the power to delegate specific functions and proceedings to an individual Member or groups of Members.</t>
+          <t>Gives the Chairperson general superintendence over Board administrative matters, and the power to delegate scrutiny/functions/proceedings to individual Members or groups of Members.</t>
         </is>
       </c>
       <c r="F54" s="13" t="inlineStr">
@@ -5536,7 +5554,7 @@
       </c>
       <c r="R54" s="12" t="inlineStr">
         <is>
-          <t>Currently in force. Text corrected 2026-09-23 against the official Act PDF (SHA-256 4deb2398...7d15), re-verified against a hash-confirmed copy of the source PDF (second extraction pass; Sonnet+Opus review) — see docs/act_table_audit_2026-09-23.md.</t>
+          <t>Currently in force. Text rebuilt verbatim 2026-09-23 from the official Act PDF (SHA-256 4deb2398...7d15) -- see docs/act_verbatim_rebuild_2026-09-23.md.</t>
         </is>
       </c>
       <c r="S54" s="14">
@@ -5680,7 +5698,7 @@
       </c>
       <c r="J56" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="K56" s="12" t="inlineStr">
@@ -5710,7 +5728,7 @@
       </c>
       <c r="R56" s="12" t="inlineStr">
         <is>
-          <t>In force eighteen months after notification (G.S.R. 843(E), group (c)) — not yet operative.</t>
+          <t>In force eighteen months after notification (G.S.R. 843(E), group (c)) — not yet operative. Text rebuilt verbatim 2026-09-23 from the official Act PDF (SHA-256 4deb2398...7d15) -- see docs/act_verbatim_rebuild_2026-09-23.md.</t>
         </is>
       </c>
       <c r="S56" s="14">
@@ -5854,7 +5872,7 @@
       </c>
       <c r="J58" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="K58" s="12" t="inlineStr">
@@ -5884,7 +5902,7 @@
       </c>
       <c r="R58" s="12" t="inlineStr">
         <is>
-          <t>In force one year after notification (G.S.R. 843(E), group (b)).</t>
+          <t>In force one year after notification (G.S.R. 843(E), group (b)). Text rebuilt verbatim 2026-09-23 from the official Act PDF (SHA-256 4deb2398...7d15) -- see docs/act_verbatim_rebuild_2026-09-23.md.</t>
         </is>
       </c>
       <c r="S58" s="14">
@@ -6058,7 +6076,7 @@
       </c>
       <c r="R60" s="12" t="inlineStr">
         <is>
-          <t>In force eighteen months after notification (G.S.R. 843(E), group (c)) — not yet operative. Text corrected 2026-09-23 against the official Act PDF (SHA-256 4deb2398...7d15), re-verified against a hash-confirmed copy of the source PDF (second extraction pass; Sonnet+Opus review) — see docs/act_table_audit_2026-09-23.md.</t>
+          <t>In force eighteen months after notification (G.S.R. 843(E), group (c)) — not yet operative. Text rebuilt verbatim 2026-09-23 from the official Act PDF (SHA-256 4deb2398...7d15) -- see docs/act_verbatim_rebuild_2026-09-23.md.</t>
         </is>
       </c>
       <c r="S60" s="14">
@@ -6202,7 +6220,7 @@
       </c>
       <c r="J62" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="K62" s="12" t="inlineStr">
@@ -6232,7 +6250,7 @@
       </c>
       <c r="R62" s="12" t="inlineStr">
         <is>
-          <t>In force eighteen months after notification (G.S.R. 843(E), group (c)) — not yet operative.</t>
+          <t>In force eighteen months after notification (G.S.R. 843(E), group (c)) — not yet operative. Text rebuilt verbatim 2026-09-23 from the official Act PDF (SHA-256 4deb2398...7d15) -- see docs/act_verbatim_rebuild_2026-09-23.md.</t>
         </is>
       </c>
       <c r="S62" s="14">
@@ -6376,7 +6394,7 @@
       </c>
       <c r="J64" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="K64" s="12" t="inlineStr">
@@ -6406,7 +6424,7 @@
       </c>
       <c r="R64" s="12" t="inlineStr">
         <is>
-          <t>In force eighteen months after notification (G.S.R. 843(E), group (c)) — not yet operative.</t>
+          <t>In force eighteen months after notification (G.S.R. 843(E), group (c)) — not yet operative. Text rebuilt verbatim 2026-09-23 from the official Act PDF (SHA-256 4deb2398...7d15) -- see docs/act_verbatim_rebuild_2026-09-23.md.</t>
         </is>
       </c>
       <c r="S64" s="14">
@@ -6463,7 +6481,7 @@
       </c>
       <c r="J65" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="K65" s="12" t="inlineStr">
@@ -6493,7 +6511,7 @@
       </c>
       <c r="R65" s="12" t="inlineStr">
         <is>
-          <t>In force eighteen months after notification (G.S.R. 843(E), group (c)) — not yet operative.</t>
+          <t>In force eighteen months after notification (G.S.R. 843(E), group (c)) — not yet operative. Text rebuilt verbatim 2026-09-23 from the official Act PDF (SHA-256 4deb2398...7d15) -- see docs/act_verbatim_rebuild_2026-09-23.md.</t>
         </is>
       </c>
       <c r="S65" s="14">
@@ -6550,7 +6568,7 @@
       </c>
       <c r="J66" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="K66" s="12" t="inlineStr">
@@ -6580,7 +6598,7 @@
       </c>
       <c r="R66" s="12" t="inlineStr">
         <is>
-          <t>In force eighteen months after notification (G.S.R. 843(E), group (c)) — not yet operative.</t>
+          <t>In force eighteen months after notification (G.S.R. 843(E), group (c)) — not yet operative. Text rebuilt verbatim 2026-09-23 from the official Act PDF (SHA-256 4deb2398...7d15) -- see docs/act_verbatim_rebuild_2026-09-23.md.</t>
         </is>
       </c>
       <c r="S66" s="14">
@@ -6637,7 +6655,7 @@
       </c>
       <c r="J67" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="K67" s="12" t="inlineStr">
@@ -6667,7 +6685,7 @@
       </c>
       <c r="R67" s="12" t="inlineStr">
         <is>
-          <t>In force eighteen months after notification (G.S.R. 843(E), group (c)) — not yet operative.</t>
+          <t>In force eighteen months after notification (G.S.R. 843(E), group (c)) — not yet operative. Text rebuilt verbatim 2026-09-23 from the official Act PDF (SHA-256 4deb2398...7d15) -- see docs/act_verbatim_rebuild_2026-09-23.md.</t>
         </is>
       </c>
       <c r="S67" s="14">
@@ -6724,7 +6742,7 @@
       </c>
       <c r="J68" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="K68" s="12" t="inlineStr">
@@ -6754,7 +6772,7 @@
       </c>
       <c r="R68" s="12" t="inlineStr">
         <is>
-          <t>In force eighteen months after notification (G.S.R. 843(E), group (c)) — not yet operative.</t>
+          <t>In force eighteen months after notification (G.S.R. 843(E), group (c)) — not yet operative. Text rebuilt verbatim 2026-09-23 from the official Act PDF (SHA-256 4deb2398...7d15) -- see docs/act_verbatim_rebuild_2026-09-23.md.</t>
         </is>
       </c>
       <c r="S68" s="14">
@@ -6811,7 +6829,7 @@
       </c>
       <c r="J69" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="K69" s="12" t="inlineStr">
@@ -6841,7 +6859,7 @@
       </c>
       <c r="R69" s="12" t="inlineStr">
         <is>
-          <t>Currently in force.</t>
+          <t>Currently in force. Text rebuilt verbatim 2026-09-23 from the official Act PDF (SHA-256 4deb2398...7d15) -- see docs/act_verbatim_rebuild_2026-09-23.md.</t>
         </is>
       </c>
       <c r="S69" s="14">
@@ -6898,7 +6916,7 @@
       </c>
       <c r="J70" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="K70" s="12" t="inlineStr">
@@ -6928,7 +6946,7 @@
       </c>
       <c r="R70" s="12" t="inlineStr">
         <is>
-          <t>In force eighteen months after notification (G.S.R. 843(E), group (c)) — not yet operative.</t>
+          <t>In force eighteen months after notification (G.S.R. 843(E), group (c)) — not yet operative. Text rebuilt verbatim 2026-09-23 from the official Act PDF (SHA-256 4deb2398...7d15) -- see docs/act_verbatim_rebuild_2026-09-23.md.</t>
         </is>
       </c>
       <c r="S70" s="14">
@@ -6985,7 +7003,7 @@
       </c>
       <c r="J71" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="K71" s="12" t="inlineStr">
@@ -7015,7 +7033,7 @@
       </c>
       <c r="R71" s="12" t="inlineStr">
         <is>
-          <t>In force eighteen months after notification (G.S.R. 843(E), group (c)) — not yet operative.</t>
+          <t>In force eighteen months after notification (G.S.R. 843(E), group (c)) — not yet operative. Text rebuilt verbatim 2026-09-23 from the official Act PDF (SHA-256 4deb2398...7d15) -- see docs/act_verbatim_rebuild_2026-09-23.md.</t>
         </is>
       </c>
       <c r="S71" s="14">
@@ -7072,7 +7090,7 @@
       </c>
       <c r="J72" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="K72" s="12" t="inlineStr">
@@ -7102,7 +7120,7 @@
       </c>
       <c r="R72" s="12" t="inlineStr">
         <is>
-          <t>Currently in force.</t>
+          <t>Currently in force. Text rebuilt verbatim 2026-09-23 from the official Act PDF (SHA-256 4deb2398...7d15) -- see docs/act_verbatim_rebuild_2026-09-23.md.</t>
         </is>
       </c>
       <c r="S72" s="14">
@@ -7159,7 +7177,7 @@
       </c>
       <c r="J73" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="K73" s="12" t="inlineStr">
@@ -7189,7 +7207,7 @@
       </c>
       <c r="R73" s="12" t="inlineStr">
         <is>
-          <t>Currently in force.</t>
+          <t>Currently in force. Text rebuilt verbatim 2026-09-23 from the official Act PDF (SHA-256 4deb2398...7d15) -- see docs/act_verbatim_rebuild_2026-09-23.md.</t>
         </is>
       </c>
       <c r="S73" s="14">
@@ -7246,7 +7264,7 @@
       </c>
       <c r="J74" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="K74" s="12" t="inlineStr">
@@ -7276,7 +7294,7 @@
       </c>
       <c r="R74" s="12" t="inlineStr">
         <is>
-          <t>Currently in force.</t>
+          <t>Currently in force. Text rebuilt verbatim 2026-09-23 from the official Act PDF (SHA-256 4deb2398...7d15) -- see docs/act_verbatim_rebuild_2026-09-23.md.</t>
         </is>
       </c>
       <c r="S74" s="14">
@@ -7333,7 +7351,7 @@
       </c>
       <c r="J75" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="K75" s="12" t="inlineStr">
@@ -7363,7 +7381,7 @@
       </c>
       <c r="R75" s="12" t="inlineStr">
         <is>
-          <t>Currently in force.</t>
+          <t>Currently in force. Text rebuilt verbatim 2026-09-23 from the official Act PDF (SHA-256 4deb2398...7d15) -- see docs/act_verbatim_rebuild_2026-09-23.md.</t>
         </is>
       </c>
       <c r="S75" s="14">
@@ -7420,7 +7438,7 @@
       </c>
       <c r="J76" s="12" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="K76" s="12" t="inlineStr">
@@ -7450,7 +7468,7 @@
       </c>
       <c r="R76" s="12" t="inlineStr">
         <is>
-          <t>Currently in force. Text corrected 2026-09-23 against the official Act PDF (SHA-256 4deb2398...7d15), re-verified against a hash-confirmed copy of the source PDF (second extraction pass; Sonnet+Opus review) — see docs/act_table_audit_2026-09-23.md.</t>
+          <t>Currently in force.</t>
         </is>
       </c>
       <c r="S76" s="14">
@@ -7507,7 +7525,7 @@
       </c>
       <c r="J77" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="K77" s="12" t="inlineStr">
@@ -7537,7 +7555,7 @@
       </c>
       <c r="R77" s="12" t="inlineStr">
         <is>
-          <t>Currently in force.</t>
+          <t>Currently in force. Text rebuilt verbatim 2026-09-23 from the official Act PDF (SHA-256 4deb2398...7d15) -- see docs/act_verbatim_rebuild_2026-09-23.md.</t>
         </is>
       </c>
       <c r="S77" s="14">
@@ -7569,7 +7587,7 @@
       </c>
       <c r="E78" s="12" t="inlineStr">
         <is>
-          <t>Amends the TRAI Act, 1997 to replace its Appellate Tribunal list with the IT Act, Airports Economic Regulatory Authority Act, and DPDP Act Appellate Tribunals, and amends the RTI Act, 2005 to add a standalone exemption for 'information which relates to personal information'.</t>
+          <t>Amends the TRAI Act, 1997 to fold in the DPDP Appellate Tribunal, and amends the RTI Act, 2005 to redefine what counts as exempt 'personal information' by reference to this Act.</t>
         </is>
       </c>
       <c r="F78" s="13" t="inlineStr">
@@ -7624,7 +7642,7 @@
       </c>
       <c r="R78" s="12" t="inlineStr">
         <is>
-          <t>Currently in force. Text corrected 2026-09-23 against the official Act PDF (SHA-256 4deb2398...7d15), re-verified against a hash-confirmed copy of the source PDF (second extraction pass; Sonnet+Opus review) — see docs/act_table_audit_2026-09-23.md.</t>
+          <t>Currently in force. Text rebuilt verbatim 2026-09-23 from the official Act PDF (SHA-256 4deb2398...7d15) -- see docs/act_verbatim_rebuild_2026-09-23.md.</t>
         </is>
       </c>
       <c r="S78" s="14">
@@ -7656,7 +7674,7 @@
       </c>
       <c r="E79" s="12" t="inlineStr">
         <is>
-          <t>Amends the Information Technology Act, 2000 — removes the old compensation-for-data-breach provision (Section 43A, since this Act now governs that), inserts a cross-reference to this Act into Section 81's proviso, and omits a now-redundant RTI-exemption clause (Section 87(2)(ob)).</t>
+          <t>Amends the Information Technology Act, 2000 — removes the old compensation-for-data-breach provision (Section 43A, since this Act now governs that), and cross-references this Act in two other IT Act provisions.</t>
         </is>
       </c>
       <c r="F79" s="13" t="inlineStr">
@@ -7711,7 +7729,7 @@
       </c>
       <c r="R79" s="12" t="inlineStr">
         <is>
-          <t>In force eighteen months after notification (G.S.R. 843(E), group (c)) — not yet operative. Text corrected 2026-09-23 against the official Act PDF (SHA-256 4deb2398...7d15), re-verified against a hash-confirmed copy of the source PDF (second extraction pass; Sonnet+Opus review) — see docs/act_table_audit_2026-09-23.md.</t>
+          <t>In force eighteen months after notification (G.S.R. 843(E), group (c)) — not yet operative. Text rebuilt verbatim 2026-09-23 from the official Act PDF (SHA-256 4deb2398...7d15) -- see docs/act_verbatim_rebuild_2026-09-23.md.</t>
         </is>
       </c>
       <c r="S79" s="14">
@@ -7768,7 +7786,7 @@
       </c>
       <c r="J80" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="K80" s="12" t="inlineStr">
@@ -7798,7 +7816,7 @@
       </c>
       <c r="R80" s="12" t="inlineStr">
         <is>
-          <t>In force eighteen months after notification (G.S.R. 843(E), group (c)) — not yet operative.</t>
+          <t>In force eighteen months after notification (G.S.R. 843(E), group (c)) — not yet operative. Text rebuilt verbatim 2026-09-23 from the official Act PDF (SHA-256 4deb2398...7d15) -- see docs/act_verbatim_rebuild_2026-09-23.md.</t>
         </is>
       </c>
       <c r="S80" s="14">
@@ -7913,7 +7931,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P87"/>
+  <dimension ref="A1:P136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -13889,6 +13907,3442 @@
       <c r="P87" s="12" t="inlineStr">
         <is>
           <t>One-time manual data-quality correction (not a detected regulatory change): DB text diverged from the enacted Act at seeding time. Corrected against a freshly downloaded, hash-verified copy of the official PDF, re-verified against a hash-confirmed copy of the source PDF via a second, independent extraction pass and a second review pass. review_status left 'Pending Review' since no human has read the literal corrected text line-by-line yet — see docs/act_table_audit_2026-09-23.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="12" t="inlineStr">
+        <is>
+          <t>CHG-0040</t>
+        </is>
+      </c>
+      <c r="B88" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-23T07:07:11.937949+00:00</t>
+        </is>
+      </c>
+      <c r="C88" s="12" t="inlineStr">
+        <is>
+          <t>DPDPA-S2</t>
+        </is>
+      </c>
+      <c r="D88" s="12" t="inlineStr">
+        <is>
+          <t>Correction</t>
+        </is>
+      </c>
+      <c r="E88" s="12" t="inlineStr">
+        <is>
+          <t>data_correction</t>
+        </is>
+      </c>
+      <c r="F88" s="12" t="inlineStr">
+        <is>
+          <t>Text rebuilt verbatim from the official Act PDF (data-quality fix, not a legal change).</t>
+        </is>
+      </c>
+      <c r="G88" s="12" t="inlineStr">
+        <is>
+          <t>Text rebuilt verbatim from the official Act PDF (data-quality fix, not a legal change).</t>
+        </is>
+      </c>
+      <c r="H88" s="12" t="inlineStr">
+        <is>
+          <t>DPDP Act, 2023 (official PDF)</t>
+        </is>
+      </c>
+      <c r="I88" s="12" t="inlineStr">
+        <is>
+          <t>docs/full_text/DPDP_Act_2023_official_2026-09-23.pdf</t>
+        </is>
+      </c>
+      <c r="J88" s="12" t="inlineStr">
+        <is>
+          <t>manual:verbatim-rebuild-2026-09-23 (code-extracted, no model-written text)</t>
+        </is>
+      </c>
+      <c r="K88" s="12" t="n"/>
+      <c r="L88" s="12" t="inlineStr">
+        <is>
+          <t>Pending Review</t>
+        </is>
+      </c>
+      <c r="M88" s="12" t="n"/>
+      <c r="N88" s="12" t="n"/>
+      <c r="O88" s="12" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P88" s="12" t="inlineStr">
+        <is>
+          <t>Verbatim rebuild, 2026-09-23. See docs/act_verbatim_rebuild_2026-09-23.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="12" t="inlineStr">
+        <is>
+          <t>CHG-0041</t>
+        </is>
+      </c>
+      <c r="B89" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-23T07:07:11.937949+00:00</t>
+        </is>
+      </c>
+      <c r="C89" s="12" t="inlineStr">
+        <is>
+          <t>DPDPA-S3</t>
+        </is>
+      </c>
+      <c r="D89" s="12" t="inlineStr">
+        <is>
+          <t>Correction</t>
+        </is>
+      </c>
+      <c r="E89" s="12" t="inlineStr">
+        <is>
+          <t>data_correction</t>
+        </is>
+      </c>
+      <c r="F89" s="12" t="inlineStr">
+        <is>
+          <t>Text rebuilt verbatim from the official Act PDF (data-quality fix, not a legal change).</t>
+        </is>
+      </c>
+      <c r="G89" s="12" t="inlineStr">
+        <is>
+          <t>Text rebuilt verbatim from the official Act PDF (data-quality fix, not a legal change).</t>
+        </is>
+      </c>
+      <c r="H89" s="12" t="inlineStr">
+        <is>
+          <t>DPDP Act, 2023 (official PDF)</t>
+        </is>
+      </c>
+      <c r="I89" s="12" t="inlineStr">
+        <is>
+          <t>docs/full_text/DPDP_Act_2023_official_2026-09-23.pdf</t>
+        </is>
+      </c>
+      <c r="J89" s="12" t="inlineStr">
+        <is>
+          <t>manual:verbatim-rebuild-2026-09-23 (code-extracted, no model-written text)</t>
+        </is>
+      </c>
+      <c r="K89" s="12" t="n"/>
+      <c r="L89" s="12" t="inlineStr">
+        <is>
+          <t>Pending Review</t>
+        </is>
+      </c>
+      <c r="M89" s="12" t="n"/>
+      <c r="N89" s="12" t="n"/>
+      <c r="O89" s="12" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P89" s="12" t="inlineStr">
+        <is>
+          <t>Verbatim rebuild, 2026-09-23. See docs/act_verbatim_rebuild_2026-09-23.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="12" t="inlineStr">
+        <is>
+          <t>CHG-0042</t>
+        </is>
+      </c>
+      <c r="B90" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-23T07:07:11.937949+00:00</t>
+        </is>
+      </c>
+      <c r="C90" s="12" t="inlineStr">
+        <is>
+          <t>DPDPA-S4</t>
+        </is>
+      </c>
+      <c r="D90" s="12" t="inlineStr">
+        <is>
+          <t>Correction</t>
+        </is>
+      </c>
+      <c r="E90" s="12" t="inlineStr">
+        <is>
+          <t>data_correction</t>
+        </is>
+      </c>
+      <c r="F90" s="12" t="inlineStr">
+        <is>
+          <t>Text rebuilt verbatim from the official Act PDF (data-quality fix, not a legal change).</t>
+        </is>
+      </c>
+      <c r="G90" s="12" t="inlineStr">
+        <is>
+          <t>Text rebuilt verbatim from the official Act PDF (data-quality fix, not a legal change).</t>
+        </is>
+      </c>
+      <c r="H90" s="12" t="inlineStr">
+        <is>
+          <t>DPDP Act, 2023 (official PDF)</t>
+        </is>
+      </c>
+      <c r="I90" s="12" t="inlineStr">
+        <is>
+          <t>docs/full_text/DPDP_Act_2023_official_2026-09-23.pdf</t>
+        </is>
+      </c>
+      <c r="J90" s="12" t="inlineStr">
+        <is>
+          <t>manual:verbatim-rebuild-2026-09-23 (code-extracted, no model-written text)</t>
+        </is>
+      </c>
+      <c r="K90" s="12" t="n"/>
+      <c r="L90" s="12" t="inlineStr">
+        <is>
+          <t>Pending Review</t>
+        </is>
+      </c>
+      <c r="M90" s="12" t="n"/>
+      <c r="N90" s="12" t="n"/>
+      <c r="O90" s="12" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P90" s="12" t="inlineStr">
+        <is>
+          <t>Verbatim rebuild, 2026-09-23. See docs/act_verbatim_rebuild_2026-09-23.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="12" t="inlineStr">
+        <is>
+          <t>CHG-0043</t>
+        </is>
+      </c>
+      <c r="B91" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-23T07:07:11.937949+00:00</t>
+        </is>
+      </c>
+      <c r="C91" s="12" t="inlineStr">
+        <is>
+          <t>DPDPA-S5</t>
+        </is>
+      </c>
+      <c r="D91" s="12" t="inlineStr">
+        <is>
+          <t>Correction</t>
+        </is>
+      </c>
+      <c r="E91" s="12" t="inlineStr">
+        <is>
+          <t>data_correction</t>
+        </is>
+      </c>
+      <c r="F91" s="12" t="inlineStr">
+        <is>
+          <t>Text rebuilt verbatim from the official Act PDF (data-quality fix, not a legal change).</t>
+        </is>
+      </c>
+      <c r="G91" s="12" t="inlineStr">
+        <is>
+          <t>Text rebuilt verbatim from the official Act PDF (data-quality fix, not a legal change).</t>
+        </is>
+      </c>
+      <c r="H91" s="12" t="inlineStr">
+        <is>
+          <t>DPDP Act, 2023 (official PDF)</t>
+        </is>
+      </c>
+      <c r="I91" s="12" t="inlineStr">
+        <is>
+          <t>docs/full_text/DPDP_Act_2023_official_2026-09-23.pdf</t>
+        </is>
+      </c>
+      <c r="J91" s="12" t="inlineStr">
+        <is>
+          <t>manual:verbatim-rebuild-2026-09-23 (code-extracted, no model-written text)</t>
+        </is>
+      </c>
+      <c r="K91" s="12" t="n"/>
+      <c r="L91" s="12" t="inlineStr">
+        <is>
+          <t>Pending Review</t>
+        </is>
+      </c>
+      <c r="M91" s="12" t="n"/>
+      <c r="N91" s="12" t="n"/>
+      <c r="O91" s="12" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P91" s="12" t="inlineStr">
+        <is>
+          <t>Verbatim rebuild, 2026-09-23. See docs/act_verbatim_rebuild_2026-09-23.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="12" t="inlineStr">
+        <is>
+          <t>CHG-0044</t>
+        </is>
+      </c>
+      <c r="B92" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-23T07:07:11.937949+00:00</t>
+        </is>
+      </c>
+      <c r="C92" s="12" t="inlineStr">
+        <is>
+          <t>DPDPA-S6.1_8_10</t>
+        </is>
+      </c>
+      <c r="D92" s="12" t="inlineStr">
+        <is>
+          <t>Correction</t>
+        </is>
+      </c>
+      <c r="E92" s="12" t="inlineStr">
+        <is>
+          <t>data_correction</t>
+        </is>
+      </c>
+      <c r="F92" s="12" t="inlineStr">
+        <is>
+          <t>Text rebuilt verbatim from the official Act PDF (data-quality fix, not a legal change).</t>
+        </is>
+      </c>
+      <c r="G92" s="12" t="inlineStr">
+        <is>
+          <t>Text rebuilt verbatim from the official Act PDF (data-quality fix, not a legal change).</t>
+        </is>
+      </c>
+      <c r="H92" s="12" t="inlineStr">
+        <is>
+          <t>DPDP Act, 2023 (official PDF)</t>
+        </is>
+      </c>
+      <c r="I92" s="12" t="inlineStr">
+        <is>
+          <t>docs/full_text/DPDP_Act_2023_official_2026-09-23.pdf</t>
+        </is>
+      </c>
+      <c r="J92" s="12" t="inlineStr">
+        <is>
+          <t>manual:verbatim-rebuild-2026-09-23 (code-extracted, no model-written text)</t>
+        </is>
+      </c>
+      <c r="K92" s="12" t="n"/>
+      <c r="L92" s="12" t="inlineStr">
+        <is>
+          <t>Pending Review</t>
+        </is>
+      </c>
+      <c r="M92" s="12" t="n"/>
+      <c r="N92" s="12" t="n"/>
+      <c r="O92" s="12" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P92" s="12" t="inlineStr">
+        <is>
+          <t>Verbatim rebuild, 2026-09-23. See docs/act_verbatim_rebuild_2026-09-23.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="12" t="inlineStr">
+        <is>
+          <t>CHG-0045</t>
+        </is>
+      </c>
+      <c r="B93" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-23T07:07:11.937949+00:00</t>
+        </is>
+      </c>
+      <c r="C93" s="12" t="inlineStr">
+        <is>
+          <t>DPDPA-S6.9</t>
+        </is>
+      </c>
+      <c r="D93" s="12" t="inlineStr">
+        <is>
+          <t>Correction</t>
+        </is>
+      </c>
+      <c r="E93" s="12" t="inlineStr">
+        <is>
+          <t>data_correction</t>
+        </is>
+      </c>
+      <c r="F93" s="12" t="inlineStr">
+        <is>
+          <t>Text rebuilt verbatim from the official Act PDF (data-quality fix, not a legal change).</t>
+        </is>
+      </c>
+      <c r="G93" s="12" t="inlineStr">
+        <is>
+          <t>Text rebuilt verbatim from the official Act PDF (data-quality fix, not a legal change).</t>
+        </is>
+      </c>
+      <c r="H93" s="12" t="inlineStr">
+        <is>
+          <t>DPDP Act, 2023 (official PDF)</t>
+        </is>
+      </c>
+      <c r="I93" s="12" t="inlineStr">
+        <is>
+          <t>docs/full_text/DPDP_Act_2023_official_2026-09-23.pdf</t>
+        </is>
+      </c>
+      <c r="J93" s="12" t="inlineStr">
+        <is>
+          <t>manual:verbatim-rebuild-2026-09-23 (code-extracted, no model-written text)</t>
+        </is>
+      </c>
+      <c r="K93" s="12" t="n"/>
+      <c r="L93" s="12" t="inlineStr">
+        <is>
+          <t>Pending Review</t>
+        </is>
+      </c>
+      <c r="M93" s="12" t="n"/>
+      <c r="N93" s="12" t="n"/>
+      <c r="O93" s="12" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P93" s="12" t="inlineStr">
+        <is>
+          <t>Verbatim rebuild, 2026-09-23. See docs/act_verbatim_rebuild_2026-09-23.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="12" t="inlineStr">
+        <is>
+          <t>CHG-0046</t>
+        </is>
+      </c>
+      <c r="B94" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-23T07:07:11.937949+00:00</t>
+        </is>
+      </c>
+      <c r="C94" s="12" t="inlineStr">
+        <is>
+          <t>DPDPA-S7</t>
+        </is>
+      </c>
+      <c r="D94" s="12" t="inlineStr">
+        <is>
+          <t>Correction</t>
+        </is>
+      </c>
+      <c r="E94" s="12" t="inlineStr">
+        <is>
+          <t>data_correction</t>
+        </is>
+      </c>
+      <c r="F94" s="12" t="inlineStr">
+        <is>
+          <t>Text rebuilt verbatim from the official Act PDF (data-quality fix, not a legal change).</t>
+        </is>
+      </c>
+      <c r="G94" s="12" t="inlineStr">
+        <is>
+          <t>Text rebuilt verbatim from the official Act PDF (data-quality fix, not a legal change).</t>
+        </is>
+      </c>
+      <c r="H94" s="12" t="inlineStr">
+        <is>
+          <t>DPDP Act, 2023 (official PDF)</t>
+        </is>
+      </c>
+      <c r="I94" s="12" t="inlineStr">
+        <is>
+          <t>docs/full_text/DPDP_Act_2023_official_2026-09-23.pdf</t>
+        </is>
+      </c>
+      <c r="J94" s="12" t="inlineStr">
+        <is>
+          <t>manual:verbatim-rebuild-2026-09-23 (code-extracted, no model-written text)</t>
+        </is>
+      </c>
+      <c r="K94" s="12" t="n"/>
+      <c r="L94" s="12" t="inlineStr">
+        <is>
+          <t>Pending Review</t>
+        </is>
+      </c>
+      <c r="M94" s="12" t="n"/>
+      <c r="N94" s="12" t="n"/>
+      <c r="O94" s="12" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P94" s="12" t="inlineStr">
+        <is>
+          <t>Verbatim rebuild, 2026-09-23. See docs/act_verbatim_rebuild_2026-09-23.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="12" t="inlineStr">
+        <is>
+          <t>CHG-0047</t>
+        </is>
+      </c>
+      <c r="B95" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-23T07:07:11.937949+00:00</t>
+        </is>
+      </c>
+      <c r="C95" s="12" t="inlineStr">
+        <is>
+          <t>DPDPA-S8</t>
+        </is>
+      </c>
+      <c r="D95" s="12" t="inlineStr">
+        <is>
+          <t>Correction</t>
+        </is>
+      </c>
+      <c r="E95" s="12" t="inlineStr">
+        <is>
+          <t>data_correction</t>
+        </is>
+      </c>
+      <c r="F95" s="12" t="inlineStr">
+        <is>
+          <t>Text rebuilt verbatim from the official Act PDF (data-quality fix, not a legal change).</t>
+        </is>
+      </c>
+      <c r="G95" s="12" t="inlineStr">
+        <is>
+          <t>Text rebuilt verbatim from the official Act PDF (data-quality fix, not a legal change).</t>
+        </is>
+      </c>
+      <c r="H95" s="12" t="inlineStr">
+        <is>
+          <t>DPDP Act, 2023 (official PDF)</t>
+        </is>
+      </c>
+      <c r="I95" s="12" t="inlineStr">
+        <is>
+          <t>docs/full_text/DPDP_Act_2023_official_2026-09-23.pdf</t>
+        </is>
+      </c>
+      <c r="J95" s="12" t="inlineStr">
+        <is>
+          <t>manual:verbatim-rebuild-2026-09-23 (code-extracted, no model-written text)</t>
+        </is>
+      </c>
+      <c r="K95" s="12" t="n"/>
+      <c r="L95" s="12" t="inlineStr">
+        <is>
+          <t>Pending Review</t>
+        </is>
+      </c>
+      <c r="M95" s="12" t="n"/>
+      <c r="N95" s="12" t="n"/>
+      <c r="O95" s="12" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P95" s="12" t="inlineStr">
+        <is>
+          <t>Verbatim rebuild, 2026-09-23. See docs/act_verbatim_rebuild_2026-09-23.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="12" t="inlineStr">
+        <is>
+          <t>CHG-0048</t>
+        </is>
+      </c>
+      <c r="B96" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-23T07:07:11.937949+00:00</t>
+        </is>
+      </c>
+      <c r="C96" s="12" t="inlineStr">
+        <is>
+          <t>DPDPA-S9</t>
+        </is>
+      </c>
+      <c r="D96" s="12" t="inlineStr">
+        <is>
+          <t>Correction</t>
+        </is>
+      </c>
+      <c r="E96" s="12" t="inlineStr">
+        <is>
+          <t>data_correction</t>
+        </is>
+      </c>
+      <c r="F96" s="12" t="inlineStr">
+        <is>
+          <t>Text rebuilt verbatim from the official Act PDF (data-quality fix, not a legal change).</t>
+        </is>
+      </c>
+      <c r="G96" s="12" t="inlineStr">
+        <is>
+          <t>Text rebuilt verbatim from the official Act PDF (data-quality fix, not a legal change).</t>
+        </is>
+      </c>
+      <c r="H96" s="12" t="inlineStr">
+        <is>
+          <t>DPDP Act, 2023 (official PDF)</t>
+        </is>
+      </c>
+      <c r="I96" s="12" t="inlineStr">
+        <is>
+          <t>docs/full_text/DPDP_Act_2023_official_2026-09-23.pdf</t>
+        </is>
+      </c>
+      <c r="J96" s="12" t="inlineStr">
+        <is>
+          <t>manual:verbatim-rebuild-2026-09-23 (code-extracted, no model-written text)</t>
+        </is>
+      </c>
+      <c r="K96" s="12" t="n"/>
+      <c r="L96" s="12" t="inlineStr">
+        <is>
+          <t>Pending Review</t>
+        </is>
+      </c>
+      <c r="M96" s="12" t="n"/>
+      <c r="N96" s="12" t="n"/>
+      <c r="O96" s="12" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P96" s="12" t="inlineStr">
+        <is>
+          <t>Verbatim rebuild, 2026-09-23. See docs/act_verbatim_rebuild_2026-09-23.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="12" t="inlineStr">
+        <is>
+          <t>CHG-0049</t>
+        </is>
+      </c>
+      <c r="B97" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-23T07:07:11.937949+00:00</t>
+        </is>
+      </c>
+      <c r="C97" s="12" t="inlineStr">
+        <is>
+          <t>DPDPA-S10</t>
+        </is>
+      </c>
+      <c r="D97" s="12" t="inlineStr">
+        <is>
+          <t>Correction</t>
+        </is>
+      </c>
+      <c r="E97" s="12" t="inlineStr">
+        <is>
+          <t>data_correction</t>
+        </is>
+      </c>
+      <c r="F97" s="12" t="inlineStr">
+        <is>
+          <t>Text rebuilt verbatim from the official Act PDF (data-quality fix, not a legal change).</t>
+        </is>
+      </c>
+      <c r="G97" s="12" t="inlineStr">
+        <is>
+          <t>Text rebuilt verbatim from the official Act PDF (data-quality fix, not a legal change).</t>
+        </is>
+      </c>
+      <c r="H97" s="12" t="inlineStr">
+        <is>
+          <t>DPDP Act, 2023 (official PDF)</t>
+        </is>
+      </c>
+      <c r="I97" s="12" t="inlineStr">
+        <is>
+          <t>docs/full_text/DPDP_Act_2023_official_2026-09-23.pdf</t>
+        </is>
+      </c>
+      <c r="J97" s="12" t="inlineStr">
+        <is>
+          <t>manual:verbatim-rebuild-2026-09-23 (code-extracted, no model-written text)</t>
+        </is>
+      </c>
+      <c r="K97" s="12" t="n"/>
+      <c r="L97" s="12" t="inlineStr">
+        <is>
+          <t>Pending Review</t>
+        </is>
+      </c>
+      <c r="M97" s="12" t="n"/>
+      <c r="N97" s="12" t="n"/>
+      <c r="O97" s="12" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P97" s="12" t="inlineStr">
+        <is>
+          <t>Verbatim rebuild, 2026-09-23. See docs/act_verbatim_rebuild_2026-09-23.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="12" t="inlineStr">
+        <is>
+          <t>CHG-0050</t>
+        </is>
+      </c>
+      <c r="B98" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-23T07:07:11.937949+00:00</t>
+        </is>
+      </c>
+      <c r="C98" s="12" t="inlineStr">
+        <is>
+          <t>DPDPA-S11</t>
+        </is>
+      </c>
+      <c r="D98" s="12" t="inlineStr">
+        <is>
+          <t>Correction</t>
+        </is>
+      </c>
+      <c r="E98" s="12" t="inlineStr">
+        <is>
+          <t>data_correction</t>
+        </is>
+      </c>
+      <c r="F98" s="12" t="inlineStr">
+        <is>
+          <t>Text rebuilt verbatim from the official Act PDF (data-quality fix, not a legal change).</t>
+        </is>
+      </c>
+      <c r="G98" s="12" t="inlineStr">
+        <is>
+          <t>Text rebuilt verbatim from the official Act PDF (data-quality fix, not a legal change).</t>
+        </is>
+      </c>
+      <c r="H98" s="12" t="inlineStr">
+        <is>
+          <t>DPDP Act, 2023 (official PDF)</t>
+        </is>
+      </c>
+      <c r="I98" s="12" t="inlineStr">
+        <is>
+          <t>docs/full_text/DPDP_Act_2023_official_2026-09-23.pdf</t>
+        </is>
+      </c>
+      <c r="J98" s="12" t="inlineStr">
+        <is>
+          <t>manual:verbatim-rebuild-2026-09-23 (code-extracted, no model-written text)</t>
+        </is>
+      </c>
+      <c r="K98" s="12" t="n"/>
+      <c r="L98" s="12" t="inlineStr">
+        <is>
+          <t>Pending Review</t>
+        </is>
+      </c>
+      <c r="M98" s="12" t="n"/>
+      <c r="N98" s="12" t="n"/>
+      <c r="O98" s="12" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P98" s="12" t="inlineStr">
+        <is>
+          <t>Verbatim rebuild, 2026-09-23. See docs/act_verbatim_rebuild_2026-09-23.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="12" t="inlineStr">
+        <is>
+          <t>CHG-0051</t>
+        </is>
+      </c>
+      <c r="B99" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-23T07:07:11.937949+00:00</t>
+        </is>
+      </c>
+      <c r="C99" s="12" t="inlineStr">
+        <is>
+          <t>DPDPA-S12</t>
+        </is>
+      </c>
+      <c r="D99" s="12" t="inlineStr">
+        <is>
+          <t>Correction</t>
+        </is>
+      </c>
+      <c r="E99" s="12" t="inlineStr">
+        <is>
+          <t>data_correction</t>
+        </is>
+      </c>
+      <c r="F99" s="12" t="inlineStr">
+        <is>
+          <t>Text rebuilt verbatim from the official Act PDF (data-quality fix, not a legal change).</t>
+        </is>
+      </c>
+      <c r="G99" s="12" t="inlineStr">
+        <is>
+          <t>Text rebuilt verbatim from the official Act PDF (data-quality fix, not a legal change).</t>
+        </is>
+      </c>
+      <c r="H99" s="12" t="inlineStr">
+        <is>
+          <t>DPDP Act, 2023 (official PDF)</t>
+        </is>
+      </c>
+      <c r="I99" s="12" t="inlineStr">
+        <is>
+          <t>docs/full_text/DPDP_Act_2023_official_2026-09-23.pdf</t>
+        </is>
+      </c>
+      <c r="J99" s="12" t="inlineStr">
+        <is>
+          <t>manual:verbatim-rebuild-2026-09-23 (code-extracted, no model-written text)</t>
+        </is>
+      </c>
+      <c r="K99" s="12" t="n"/>
+      <c r="L99" s="12" t="inlineStr">
+        <is>
+          <t>Pending Review</t>
+        </is>
+      </c>
+      <c r="M99" s="12" t="n"/>
+      <c r="N99" s="12" t="n"/>
+      <c r="O99" s="12" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P99" s="12" t="inlineStr">
+        <is>
+          <t>Verbatim rebuild, 2026-09-23. See docs/act_verbatim_rebuild_2026-09-23.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="12" t="inlineStr">
+        <is>
+          <t>CHG-0052</t>
+        </is>
+      </c>
+      <c r="B100" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-23T07:07:11.937949+00:00</t>
+        </is>
+      </c>
+      <c r="C100" s="12" t="inlineStr">
+        <is>
+          <t>DPDPA-S13</t>
+        </is>
+      </c>
+      <c r="D100" s="12" t="inlineStr">
+        <is>
+          <t>Correction</t>
+        </is>
+      </c>
+      <c r="E100" s="12" t="inlineStr">
+        <is>
+          <t>data_correction</t>
+        </is>
+      </c>
+      <c r="F100" s="12" t="inlineStr">
+        <is>
+          <t>Text rebuilt verbatim from the official Act PDF (data-quality fix, not a legal change).</t>
+        </is>
+      </c>
+      <c r="G100" s="12" t="inlineStr">
+        <is>
+          <t>Text rebuilt verbatim from the official Act PDF (data-quality fix, not a legal change).</t>
+        </is>
+      </c>
+      <c r="H100" s="12" t="inlineStr">
+        <is>
+          <t>DPDP Act, 2023 (official PDF)</t>
+        </is>
+      </c>
+      <c r="I100" s="12" t="inlineStr">
+        <is>
+          <t>docs/full_text/DPDP_Act_2023_official_2026-09-23.pdf</t>
+        </is>
+      </c>
+      <c r="J100" s="12" t="inlineStr">
+        <is>
+          <t>manual:verbatim-rebuild-2026-09-23 (code-extracted, no model-written text)</t>
+        </is>
+      </c>
+      <c r="K100" s="12" t="n"/>
+      <c r="L100" s="12" t="inlineStr">
+        <is>
+          <t>Pending Review</t>
+        </is>
+      </c>
+      <c r="M100" s="12" t="n"/>
+      <c r="N100" s="12" t="n"/>
+      <c r="O100" s="12" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P100" s="12" t="inlineStr">
+        <is>
+          <t>Verbatim rebuild, 2026-09-23. See docs/act_verbatim_rebuild_2026-09-23.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="12" t="inlineStr">
+        <is>
+          <t>CHG-0053</t>
+        </is>
+      </c>
+      <c r="B101" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-23T07:07:11.937949+00:00</t>
+        </is>
+      </c>
+      <c r="C101" s="12" t="inlineStr">
+        <is>
+          <t>DPDPA-S14</t>
+        </is>
+      </c>
+      <c r="D101" s="12" t="inlineStr">
+        <is>
+          <t>Correction</t>
+        </is>
+      </c>
+      <c r="E101" s="12" t="inlineStr">
+        <is>
+          <t>data_correction</t>
+        </is>
+      </c>
+      <c r="F101" s="12" t="inlineStr">
+        <is>
+          <t>Text rebuilt verbatim from the official Act PDF (data-quality fix, not a legal change).</t>
+        </is>
+      </c>
+      <c r="G101" s="12" t="inlineStr">
+        <is>
+          <t>Text rebuilt verbatim from the official Act PDF (data-quality fix, not a legal change).</t>
+        </is>
+      </c>
+      <c r="H101" s="12" t="inlineStr">
+        <is>
+          <t>DPDP Act, 2023 (official PDF)</t>
+        </is>
+      </c>
+      <c r="I101" s="12" t="inlineStr">
+        <is>
+          <t>docs/full_text/DPDP_Act_2023_official_2026-09-23.pdf</t>
+        </is>
+      </c>
+      <c r="J101" s="12" t="inlineStr">
+        <is>
+          <t>manual:verbatim-rebuild-2026-09-23 (code-extracted, no model-written text)</t>
+        </is>
+      </c>
+      <c r="K101" s="12" t="n"/>
+      <c r="L101" s="12" t="inlineStr">
+        <is>
+          <t>Pending Review</t>
+        </is>
+      </c>
+      <c r="M101" s="12" t="n"/>
+      <c r="N101" s="12" t="n"/>
+      <c r="O101" s="12" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P101" s="12" t="inlineStr">
+        <is>
+          <t>Verbatim rebuild, 2026-09-23. See docs/act_verbatim_rebuild_2026-09-23.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="12" t="inlineStr">
+        <is>
+          <t>CHG-0054</t>
+        </is>
+      </c>
+      <c r="B102" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-23T07:07:11.937949+00:00</t>
+        </is>
+      </c>
+      <c r="C102" s="12" t="inlineStr">
+        <is>
+          <t>DPDPA-S15</t>
+        </is>
+      </c>
+      <c r="D102" s="12" t="inlineStr">
+        <is>
+          <t>Correction</t>
+        </is>
+      </c>
+      <c r="E102" s="12" t="inlineStr">
+        <is>
+          <t>data_correction</t>
+        </is>
+      </c>
+      <c r="F102" s="12" t="inlineStr">
+        <is>
+          <t>Text rebuilt verbatim from the official Act PDF (data-quality fix, not a legal change).</t>
+        </is>
+      </c>
+      <c r="G102" s="12" t="inlineStr">
+        <is>
+          <t>Text rebuilt verbatim from the official Act PDF (data-quality fix, not a legal change).</t>
+        </is>
+      </c>
+      <c r="H102" s="12" t="inlineStr">
+        <is>
+          <t>DPDP Act, 2023 (official PDF)</t>
+        </is>
+      </c>
+      <c r="I102" s="12" t="inlineStr">
+        <is>
+          <t>docs/full_text/DPDP_Act_2023_official_2026-09-23.pdf</t>
+        </is>
+      </c>
+      <c r="J102" s="12" t="inlineStr">
+        <is>
+          <t>manual:verbatim-rebuild-2026-09-23 (code-extracted, no model-written text)</t>
+        </is>
+      </c>
+      <c r="K102" s="12" t="n"/>
+      <c r="L102" s="12" t="inlineStr">
+        <is>
+          <t>Pending Review</t>
+        </is>
+      </c>
+      <c r="M102" s="12" t="n"/>
+      <c r="N102" s="12" t="n"/>
+      <c r="O102" s="12" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P102" s="12" t="inlineStr">
+        <is>
+          <t>Verbatim rebuild, 2026-09-23. See docs/act_verbatim_rebuild_2026-09-23.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="12" t="inlineStr">
+        <is>
+          <t>CHG-0055</t>
+        </is>
+      </c>
+      <c r="B103" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-23T07:07:11.937949+00:00</t>
+        </is>
+      </c>
+      <c r="C103" s="12" t="inlineStr">
+        <is>
+          <t>DPDPA-S16</t>
+        </is>
+      </c>
+      <c r="D103" s="12" t="inlineStr">
+        <is>
+          <t>Correction</t>
+        </is>
+      </c>
+      <c r="E103" s="12" t="inlineStr">
+        <is>
+          <t>data_correction</t>
+        </is>
+      </c>
+      <c r="F103" s="12" t="inlineStr">
+        <is>
+          <t>Text rebuilt verbatim from the official Act PDF (data-quality fix, not a legal change).</t>
+        </is>
+      </c>
+      <c r="G103" s="12" t="inlineStr">
+        <is>
+          <t>Text rebuilt verbatim from the official Act PDF (data-quality fix, not a legal change).</t>
+        </is>
+      </c>
+      <c r="H103" s="12" t="inlineStr">
+        <is>
+          <t>DPDP Act, 2023 (official PDF)</t>
+        </is>
+      </c>
+      <c r="I103" s="12" t="inlineStr">
+        <is>
+          <t>docs/full_text/DPDP_Act_2023_official_2026-09-23.pdf</t>
+        </is>
+      </c>
+      <c r="J103" s="12" t="inlineStr">
+        <is>
+          <t>manual:verbatim-rebuild-2026-09-23 (code-extracted, no model-written text)</t>
+        </is>
+      </c>
+      <c r="K103" s="12" t="n"/>
+      <c r="L103" s="12" t="inlineStr">
+        <is>
+          <t>Pending Review</t>
+        </is>
+      </c>
+      <c r="M103" s="12" t="n"/>
+      <c r="N103" s="12" t="n"/>
+      <c r="O103" s="12" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P103" s="12" t="inlineStr">
+        <is>
+          <t>Verbatim rebuild, 2026-09-23. See docs/act_verbatim_rebuild_2026-09-23.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="12" t="inlineStr">
+        <is>
+          <t>CHG-0056</t>
+        </is>
+      </c>
+      <c r="B104" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-23T07:07:11.937949+00:00</t>
+        </is>
+      </c>
+      <c r="C104" s="12" t="inlineStr">
+        <is>
+          <t>DPDPA-S17</t>
+        </is>
+      </c>
+      <c r="D104" s="12" t="inlineStr">
+        <is>
+          <t>Correction</t>
+        </is>
+      </c>
+      <c r="E104" s="12" t="inlineStr">
+        <is>
+          <t>data_correction</t>
+        </is>
+      </c>
+      <c r="F104" s="12" t="inlineStr">
+        <is>
+          <t>Text rebuilt verbatim from the official Act PDF (data-quality fix, not a legal change).</t>
+        </is>
+      </c>
+      <c r="G104" s="12" t="inlineStr">
+        <is>
+          <t>Text rebuilt verbatim from the official Act PDF (data-quality fix, not a legal change).</t>
+        </is>
+      </c>
+      <c r="H104" s="12" t="inlineStr">
+        <is>
+          <t>DPDP Act, 2023 (official PDF)</t>
+        </is>
+      </c>
+      <c r="I104" s="12" t="inlineStr">
+        <is>
+          <t>docs/full_text/DPDP_Act_2023_official_2026-09-23.pdf</t>
+        </is>
+      </c>
+      <c r="J104" s="12" t="inlineStr">
+        <is>
+          <t>manual:verbatim-rebuild-2026-09-23 (code-extracted, no model-written text)</t>
+        </is>
+      </c>
+      <c r="K104" s="12" t="n"/>
+      <c r="L104" s="12" t="inlineStr">
+        <is>
+          <t>Pending Review</t>
+        </is>
+      </c>
+      <c r="M104" s="12" t="n"/>
+      <c r="N104" s="12" t="n"/>
+      <c r="O104" s="12" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P104" s="12" t="inlineStr">
+        <is>
+          <t>Verbatim rebuild, 2026-09-23. See docs/act_verbatim_rebuild_2026-09-23.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="12" t="inlineStr">
+        <is>
+          <t>CHG-0057</t>
+        </is>
+      </c>
+      <c r="B105" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-23T07:07:11.937949+00:00</t>
+        </is>
+      </c>
+      <c r="C105" s="12" t="inlineStr">
+        <is>
+          <t>DPDPA-S18</t>
+        </is>
+      </c>
+      <c r="D105" s="12" t="inlineStr">
+        <is>
+          <t>Correction</t>
+        </is>
+      </c>
+      <c r="E105" s="12" t="inlineStr">
+        <is>
+          <t>data_correction</t>
+        </is>
+      </c>
+      <c r="F105" s="12" t="inlineStr">
+        <is>
+          <t>Text rebuilt verbatim from the official Act PDF (data-quality fix, not a legal change).</t>
+        </is>
+      </c>
+      <c r="G105" s="12" t="inlineStr">
+        <is>
+          <t>Text rebuilt verbatim from the official Act PDF (data-quality fix, not a legal change).</t>
+        </is>
+      </c>
+      <c r="H105" s="12" t="inlineStr">
+        <is>
+          <t>DPDP Act, 2023 (official PDF)</t>
+        </is>
+      </c>
+      <c r="I105" s="12" t="inlineStr">
+        <is>
+          <t>docs/full_text/DPDP_Act_2023_official_2026-09-23.pdf</t>
+        </is>
+      </c>
+      <c r="J105" s="12" t="inlineStr">
+        <is>
+          <t>manual:verbatim-rebuild-2026-09-23 (code-extracted, no model-written text)</t>
+        </is>
+      </c>
+      <c r="K105" s="12" t="n"/>
+      <c r="L105" s="12" t="inlineStr">
+        <is>
+          <t>Pending Review</t>
+        </is>
+      </c>
+      <c r="M105" s="12" t="n"/>
+      <c r="N105" s="12" t="n"/>
+      <c r="O105" s="12" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P105" s="12" t="inlineStr">
+        <is>
+          <t>Verbatim rebuild, 2026-09-23. See docs/act_verbatim_rebuild_2026-09-23.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="12" t="inlineStr">
+        <is>
+          <t>CHG-0058</t>
+        </is>
+      </c>
+      <c r="B106" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-23T07:07:11.937949+00:00</t>
+        </is>
+      </c>
+      <c r="C106" s="12" t="inlineStr">
+        <is>
+          <t>DPDPA-S19</t>
+        </is>
+      </c>
+      <c r="D106" s="12" t="inlineStr">
+        <is>
+          <t>Correction</t>
+        </is>
+      </c>
+      <c r="E106" s="12" t="inlineStr">
+        <is>
+          <t>data_correction</t>
+        </is>
+      </c>
+      <c r="F106" s="12" t="inlineStr">
+        <is>
+          <t>Text rebuilt verbatim from the official Act PDF (data-quality fix, not a legal change).</t>
+        </is>
+      </c>
+      <c r="G106" s="12" t="inlineStr">
+        <is>
+          <t>Text rebuilt verbatim from the official Act PDF (data-quality fix, not a legal change).</t>
+        </is>
+      </c>
+      <c r="H106" s="12" t="inlineStr">
+        <is>
+          <t>DPDP Act, 2023 (official PDF)</t>
+        </is>
+      </c>
+      <c r="I106" s="12" t="inlineStr">
+        <is>
+          <t>docs/full_text/DPDP_Act_2023_official_2026-09-23.pdf</t>
+        </is>
+      </c>
+      <c r="J106" s="12" t="inlineStr">
+        <is>
+          <t>manual:verbatim-rebuild-2026-09-23 (code-extracted, no model-written text)</t>
+        </is>
+      </c>
+      <c r="K106" s="12" t="n"/>
+      <c r="L106" s="12" t="inlineStr">
+        <is>
+          <t>Pending Review</t>
+        </is>
+      </c>
+      <c r="M106" s="12" t="n"/>
+      <c r="N106" s="12" t="n"/>
+      <c r="O106" s="12" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P106" s="12" t="inlineStr">
+        <is>
+          <t>Verbatim rebuild, 2026-09-23. See docs/act_verbatim_rebuild_2026-09-23.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="12" t="inlineStr">
+        <is>
+          <t>CHG-0059</t>
+        </is>
+      </c>
+      <c r="B107" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-23T07:07:11.937949+00:00</t>
+        </is>
+      </c>
+      <c r="C107" s="12" t="inlineStr">
+        <is>
+          <t>DPDPA-S20</t>
+        </is>
+      </c>
+      <c r="D107" s="12" t="inlineStr">
+        <is>
+          <t>Correction</t>
+        </is>
+      </c>
+      <c r="E107" s="12" t="inlineStr">
+        <is>
+          <t>data_correction</t>
+        </is>
+      </c>
+      <c r="F107" s="12" t="inlineStr">
+        <is>
+          <t>Text rebuilt verbatim from the official Act PDF (data-quality fix, not a legal change).</t>
+        </is>
+      </c>
+      <c r="G107" s="12" t="inlineStr">
+        <is>
+          <t>Text rebuilt verbatim from the official Act PDF (data-quality fix, not a legal change).</t>
+        </is>
+      </c>
+      <c r="H107" s="12" t="inlineStr">
+        <is>
+          <t>DPDP Act, 2023 (official PDF)</t>
+        </is>
+      </c>
+      <c r="I107" s="12" t="inlineStr">
+        <is>
+          <t>docs/full_text/DPDP_Act_2023_official_2026-09-23.pdf</t>
+        </is>
+      </c>
+      <c r="J107" s="12" t="inlineStr">
+        <is>
+          <t>manual:verbatim-rebuild-2026-09-23 (code-extracted, no model-written text)</t>
+        </is>
+      </c>
+      <c r="K107" s="12" t="n"/>
+      <c r="L107" s="12" t="inlineStr">
+        <is>
+          <t>Pending Review</t>
+        </is>
+      </c>
+      <c r="M107" s="12" t="n"/>
+      <c r="N107" s="12" t="n"/>
+      <c r="O107" s="12" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P107" s="12" t="inlineStr">
+        <is>
+          <t>Verbatim rebuild, 2026-09-23. See docs/act_verbatim_rebuild_2026-09-23.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="12" t="inlineStr">
+        <is>
+          <t>CHG-0060</t>
+        </is>
+      </c>
+      <c r="B108" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-23T07:07:11.937949+00:00</t>
+        </is>
+      </c>
+      <c r="C108" s="12" t="inlineStr">
+        <is>
+          <t>DPDPA-S21</t>
+        </is>
+      </c>
+      <c r="D108" s="12" t="inlineStr">
+        <is>
+          <t>Correction</t>
+        </is>
+      </c>
+      <c r="E108" s="12" t="inlineStr">
+        <is>
+          <t>data_correction</t>
+        </is>
+      </c>
+      <c r="F108" s="12" t="inlineStr">
+        <is>
+          <t>Text rebuilt verbatim from the official Act PDF (data-quality fix, not a legal change).</t>
+        </is>
+      </c>
+      <c r="G108" s="12" t="inlineStr">
+        <is>
+          <t>Text rebuilt verbatim from the official Act PDF (data-quality fix, not a legal change).</t>
+        </is>
+      </c>
+      <c r="H108" s="12" t="inlineStr">
+        <is>
+          <t>DPDP Act, 2023 (official PDF)</t>
+        </is>
+      </c>
+      <c r="I108" s="12" t="inlineStr">
+        <is>
+          <t>docs/full_text/DPDP_Act_2023_official_2026-09-23.pdf</t>
+        </is>
+      </c>
+      <c r="J108" s="12" t="inlineStr">
+        <is>
+          <t>manual:verbatim-rebuild-2026-09-23 (code-extracted, no model-written text)</t>
+        </is>
+      </c>
+      <c r="K108" s="12" t="n"/>
+      <c r="L108" s="12" t="inlineStr">
+        <is>
+          <t>Pending Review</t>
+        </is>
+      </c>
+      <c r="M108" s="12" t="n"/>
+      <c r="N108" s="12" t="n"/>
+      <c r="O108" s="12" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P108" s="12" t="inlineStr">
+        <is>
+          <t>Verbatim rebuild, 2026-09-23. See docs/act_verbatim_rebuild_2026-09-23.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="12" t="inlineStr">
+        <is>
+          <t>CHG-0061</t>
+        </is>
+      </c>
+      <c r="B109" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-23T07:07:11.937949+00:00</t>
+        </is>
+      </c>
+      <c r="C109" s="12" t="inlineStr">
+        <is>
+          <t>DPDPA-S22</t>
+        </is>
+      </c>
+      <c r="D109" s="12" t="inlineStr">
+        <is>
+          <t>Correction</t>
+        </is>
+      </c>
+      <c r="E109" s="12" t="inlineStr">
+        <is>
+          <t>data_correction</t>
+        </is>
+      </c>
+      <c r="F109" s="12" t="inlineStr">
+        <is>
+          <t>Text rebuilt verbatim from the official Act PDF (data-quality fix, not a legal change).</t>
+        </is>
+      </c>
+      <c r="G109" s="12" t="inlineStr">
+        <is>
+          <t>Text rebuilt verbatim from the official Act PDF (data-quality fix, not a legal change).</t>
+        </is>
+      </c>
+      <c r="H109" s="12" t="inlineStr">
+        <is>
+          <t>DPDP Act, 2023 (official PDF)</t>
+        </is>
+      </c>
+      <c r="I109" s="12" t="inlineStr">
+        <is>
+          <t>docs/full_text/DPDP_Act_2023_official_2026-09-23.pdf</t>
+        </is>
+      </c>
+      <c r="J109" s="12" t="inlineStr">
+        <is>
+          <t>manual:verbatim-rebuild-2026-09-23 (code-extracted, no model-written text)</t>
+        </is>
+      </c>
+      <c r="K109" s="12" t="n"/>
+      <c r="L109" s="12" t="inlineStr">
+        <is>
+          <t>Pending Review</t>
+        </is>
+      </c>
+      <c r="M109" s="12" t="n"/>
+      <c r="N109" s="12" t="n"/>
+      <c r="O109" s="12" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P109" s="12" t="inlineStr">
+        <is>
+          <t>Verbatim rebuild, 2026-09-23. See docs/act_verbatim_rebuild_2026-09-23.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="12" t="inlineStr">
+        <is>
+          <t>CHG-0062</t>
+        </is>
+      </c>
+      <c r="B110" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-23T07:07:11.937949+00:00</t>
+        </is>
+      </c>
+      <c r="C110" s="12" t="inlineStr">
+        <is>
+          <t>DPDPA-S23</t>
+        </is>
+      </c>
+      <c r="D110" s="12" t="inlineStr">
+        <is>
+          <t>Correction</t>
+        </is>
+      </c>
+      <c r="E110" s="12" t="inlineStr">
+        <is>
+          <t>data_correction</t>
+        </is>
+      </c>
+      <c r="F110" s="12" t="inlineStr">
+        <is>
+          <t>Text rebuilt verbatim from the official Act PDF (data-quality fix, not a legal change).</t>
+        </is>
+      </c>
+      <c r="G110" s="12" t="inlineStr">
+        <is>
+          <t>Text rebuilt verbatim from the official Act PDF (data-quality fix, not a legal change).</t>
+        </is>
+      </c>
+      <c r="H110" s="12" t="inlineStr">
+        <is>
+          <t>DPDP Act, 2023 (official PDF)</t>
+        </is>
+      </c>
+      <c r="I110" s="12" t="inlineStr">
+        <is>
+          <t>docs/full_text/DPDP_Act_2023_official_2026-09-23.pdf</t>
+        </is>
+      </c>
+      <c r="J110" s="12" t="inlineStr">
+        <is>
+          <t>manual:verbatim-rebuild-2026-09-23 (code-extracted, no model-written text)</t>
+        </is>
+      </c>
+      <c r="K110" s="12" t="n"/>
+      <c r="L110" s="12" t="inlineStr">
+        <is>
+          <t>Pending Review</t>
+        </is>
+      </c>
+      <c r="M110" s="12" t="n"/>
+      <c r="N110" s="12" t="n"/>
+      <c r="O110" s="12" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P110" s="12" t="inlineStr">
+        <is>
+          <t>Verbatim rebuild, 2026-09-23. See docs/act_verbatim_rebuild_2026-09-23.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="12" t="inlineStr">
+        <is>
+          <t>CHG-0063</t>
+        </is>
+      </c>
+      <c r="B111" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-23T07:07:11.937949+00:00</t>
+        </is>
+      </c>
+      <c r="C111" s="12" t="inlineStr">
+        <is>
+          <t>DPDPA-S24</t>
+        </is>
+      </c>
+      <c r="D111" s="12" t="inlineStr">
+        <is>
+          <t>Correction</t>
+        </is>
+      </c>
+      <c r="E111" s="12" t="inlineStr">
+        <is>
+          <t>data_correction</t>
+        </is>
+      </c>
+      <c r="F111" s="12" t="inlineStr">
+        <is>
+          <t>Text rebuilt verbatim from the official Act PDF (data-quality fix, not a legal change).</t>
+        </is>
+      </c>
+      <c r="G111" s="12" t="inlineStr">
+        <is>
+          <t>Text rebuilt verbatim from the official Act PDF (data-quality fix, not a legal change).</t>
+        </is>
+      </c>
+      <c r="H111" s="12" t="inlineStr">
+        <is>
+          <t>DPDP Act, 2023 (official PDF)</t>
+        </is>
+      </c>
+      <c r="I111" s="12" t="inlineStr">
+        <is>
+          <t>docs/full_text/DPDP_Act_2023_official_2026-09-23.pdf</t>
+        </is>
+      </c>
+      <c r="J111" s="12" t="inlineStr">
+        <is>
+          <t>manual:verbatim-rebuild-2026-09-23 (code-extracted, no model-written text)</t>
+        </is>
+      </c>
+      <c r="K111" s="12" t="n"/>
+      <c r="L111" s="12" t="inlineStr">
+        <is>
+          <t>Pending Review</t>
+        </is>
+      </c>
+      <c r="M111" s="12" t="n"/>
+      <c r="N111" s="12" t="n"/>
+      <c r="O111" s="12" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P111" s="12" t="inlineStr">
+        <is>
+          <t>Verbatim rebuild, 2026-09-23. See docs/act_verbatim_rebuild_2026-09-23.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="12" t="inlineStr">
+        <is>
+          <t>CHG-0064</t>
+        </is>
+      </c>
+      <c r="B112" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-23T07:07:11.937949+00:00</t>
+        </is>
+      </c>
+      <c r="C112" s="12" t="inlineStr">
+        <is>
+          <t>DPDPA-S25</t>
+        </is>
+      </c>
+      <c r="D112" s="12" t="inlineStr">
+        <is>
+          <t>Correction</t>
+        </is>
+      </c>
+      <c r="E112" s="12" t="inlineStr">
+        <is>
+          <t>data_correction</t>
+        </is>
+      </c>
+      <c r="F112" s="12" t="inlineStr">
+        <is>
+          <t>Text rebuilt verbatim from the official Act PDF (data-quality fix, not a legal change).</t>
+        </is>
+      </c>
+      <c r="G112" s="12" t="inlineStr">
+        <is>
+          <t>Text rebuilt verbatim from the official Act PDF (data-quality fix, not a legal change).</t>
+        </is>
+      </c>
+      <c r="H112" s="12" t="inlineStr">
+        <is>
+          <t>DPDP Act, 2023 (official PDF)</t>
+        </is>
+      </c>
+      <c r="I112" s="12" t="inlineStr">
+        <is>
+          <t>docs/full_text/DPDP_Act_2023_official_2026-09-23.pdf</t>
+        </is>
+      </c>
+      <c r="J112" s="12" t="inlineStr">
+        <is>
+          <t>manual:verbatim-rebuild-2026-09-23 (code-extracted, no model-written text)</t>
+        </is>
+      </c>
+      <c r="K112" s="12" t="n"/>
+      <c r="L112" s="12" t="inlineStr">
+        <is>
+          <t>Pending Review</t>
+        </is>
+      </c>
+      <c r="M112" s="12" t="n"/>
+      <c r="N112" s="12" t="n"/>
+      <c r="O112" s="12" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P112" s="12" t="inlineStr">
+        <is>
+          <t>Verbatim rebuild, 2026-09-23. See docs/act_verbatim_rebuild_2026-09-23.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="12" t="inlineStr">
+        <is>
+          <t>CHG-0065</t>
+        </is>
+      </c>
+      <c r="B113" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-23T07:07:11.937949+00:00</t>
+        </is>
+      </c>
+      <c r="C113" s="12" t="inlineStr">
+        <is>
+          <t>DPDPA-S26</t>
+        </is>
+      </c>
+      <c r="D113" s="12" t="inlineStr">
+        <is>
+          <t>Correction</t>
+        </is>
+      </c>
+      <c r="E113" s="12" t="inlineStr">
+        <is>
+          <t>data_correction</t>
+        </is>
+      </c>
+      <c r="F113" s="12" t="inlineStr">
+        <is>
+          <t>Text rebuilt verbatim from the official Act PDF (data-quality fix, not a legal change).</t>
+        </is>
+      </c>
+      <c r="G113" s="12" t="inlineStr">
+        <is>
+          <t>Text rebuilt verbatim from the official Act PDF (data-quality fix, not a legal change).</t>
+        </is>
+      </c>
+      <c r="H113" s="12" t="inlineStr">
+        <is>
+          <t>DPDP Act, 2023 (official PDF)</t>
+        </is>
+      </c>
+      <c r="I113" s="12" t="inlineStr">
+        <is>
+          <t>docs/full_text/DPDP_Act_2023_official_2026-09-23.pdf</t>
+        </is>
+      </c>
+      <c r="J113" s="12" t="inlineStr">
+        <is>
+          <t>manual:verbatim-rebuild-2026-09-23 (code-extracted, no model-written text)</t>
+        </is>
+      </c>
+      <c r="K113" s="12" t="n"/>
+      <c r="L113" s="12" t="inlineStr">
+        <is>
+          <t>Pending Review</t>
+        </is>
+      </c>
+      <c r="M113" s="12" t="n"/>
+      <c r="N113" s="12" t="n"/>
+      <c r="O113" s="12" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P113" s="12" t="inlineStr">
+        <is>
+          <t>Verbatim rebuild, 2026-09-23. See docs/act_verbatim_rebuild_2026-09-23.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="12" t="inlineStr">
+        <is>
+          <t>CHG-0066</t>
+        </is>
+      </c>
+      <c r="B114" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-23T07:07:11.937949+00:00</t>
+        </is>
+      </c>
+      <c r="C114" s="12" t="inlineStr">
+        <is>
+          <t>DPDPA-S27.1a_c_e_2_3</t>
+        </is>
+      </c>
+      <c r="D114" s="12" t="inlineStr">
+        <is>
+          <t>Correction</t>
+        </is>
+      </c>
+      <c r="E114" s="12" t="inlineStr">
+        <is>
+          <t>data_correction</t>
+        </is>
+      </c>
+      <c r="F114" s="12" t="inlineStr">
+        <is>
+          <t>Text rebuilt verbatim from the official Act PDF (data-quality fix, not a legal change).</t>
+        </is>
+      </c>
+      <c r="G114" s="12" t="inlineStr">
+        <is>
+          <t>Text rebuilt verbatim from the official Act PDF (data-quality fix, not a legal change).</t>
+        </is>
+      </c>
+      <c r="H114" s="12" t="inlineStr">
+        <is>
+          <t>DPDP Act, 2023 (official PDF)</t>
+        </is>
+      </c>
+      <c r="I114" s="12" t="inlineStr">
+        <is>
+          <t>docs/full_text/DPDP_Act_2023_official_2026-09-23.pdf</t>
+        </is>
+      </c>
+      <c r="J114" s="12" t="inlineStr">
+        <is>
+          <t>manual:verbatim-rebuild-2026-09-23 (code-extracted, no model-written text)</t>
+        </is>
+      </c>
+      <c r="K114" s="12" t="n"/>
+      <c r="L114" s="12" t="inlineStr">
+        <is>
+          <t>Pending Review</t>
+        </is>
+      </c>
+      <c r="M114" s="12" t="n"/>
+      <c r="N114" s="12" t="n"/>
+      <c r="O114" s="12" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P114" s="12" t="inlineStr">
+        <is>
+          <t>Verbatim rebuild, 2026-09-23. See docs/act_verbatim_rebuild_2026-09-23.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="12" t="inlineStr">
+        <is>
+          <t>CHG-0067</t>
+        </is>
+      </c>
+      <c r="B115" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-23T07:07:11.937949+00:00</t>
+        </is>
+      </c>
+      <c r="C115" s="12" t="inlineStr">
+        <is>
+          <t>DPDPA-S27.1d</t>
+        </is>
+      </c>
+      <c r="D115" s="12" t="inlineStr">
+        <is>
+          <t>Correction</t>
+        </is>
+      </c>
+      <c r="E115" s="12" t="inlineStr">
+        <is>
+          <t>data_correction</t>
+        </is>
+      </c>
+      <c r="F115" s="12" t="inlineStr">
+        <is>
+          <t>Text rebuilt verbatim from the official Act PDF (data-quality fix, not a legal change).</t>
+        </is>
+      </c>
+      <c r="G115" s="12" t="inlineStr">
+        <is>
+          <t>Text rebuilt verbatim from the official Act PDF (data-quality fix, not a legal change).</t>
+        </is>
+      </c>
+      <c r="H115" s="12" t="inlineStr">
+        <is>
+          <t>DPDP Act, 2023 (official PDF)</t>
+        </is>
+      </c>
+      <c r="I115" s="12" t="inlineStr">
+        <is>
+          <t>docs/full_text/DPDP_Act_2023_official_2026-09-23.pdf</t>
+        </is>
+      </c>
+      <c r="J115" s="12" t="inlineStr">
+        <is>
+          <t>manual:verbatim-rebuild-2026-09-23 (code-extracted, no model-written text)</t>
+        </is>
+      </c>
+      <c r="K115" s="12" t="n"/>
+      <c r="L115" s="12" t="inlineStr">
+        <is>
+          <t>Pending Review</t>
+        </is>
+      </c>
+      <c r="M115" s="12" t="n"/>
+      <c r="N115" s="12" t="n"/>
+      <c r="O115" s="12" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P115" s="12" t="inlineStr">
+        <is>
+          <t>Verbatim rebuild, 2026-09-23. See docs/act_verbatim_rebuild_2026-09-23.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="12" t="inlineStr">
+        <is>
+          <t>CHG-0068</t>
+        </is>
+      </c>
+      <c r="B116" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-23T07:07:11.937949+00:00</t>
+        </is>
+      </c>
+      <c r="C116" s="12" t="inlineStr">
+        <is>
+          <t>DPDPA-S28</t>
+        </is>
+      </c>
+      <c r="D116" s="12" t="inlineStr">
+        <is>
+          <t>Correction</t>
+        </is>
+      </c>
+      <c r="E116" s="12" t="inlineStr">
+        <is>
+          <t>data_correction</t>
+        </is>
+      </c>
+      <c r="F116" s="12" t="inlineStr">
+        <is>
+          <t>Text rebuilt verbatim from the official Act PDF (data-quality fix, not a legal change).</t>
+        </is>
+      </c>
+      <c r="G116" s="12" t="inlineStr">
+        <is>
+          <t>Text rebuilt verbatim from the official Act PDF (data-quality fix, not a legal change).</t>
+        </is>
+      </c>
+      <c r="H116" s="12" t="inlineStr">
+        <is>
+          <t>DPDP Act, 2023 (official PDF)</t>
+        </is>
+      </c>
+      <c r="I116" s="12" t="inlineStr">
+        <is>
+          <t>docs/full_text/DPDP_Act_2023_official_2026-09-23.pdf</t>
+        </is>
+      </c>
+      <c r="J116" s="12" t="inlineStr">
+        <is>
+          <t>manual:verbatim-rebuild-2026-09-23 (code-extracted, no model-written text)</t>
+        </is>
+      </c>
+      <c r="K116" s="12" t="n"/>
+      <c r="L116" s="12" t="inlineStr">
+        <is>
+          <t>Pending Review</t>
+        </is>
+      </c>
+      <c r="M116" s="12" t="n"/>
+      <c r="N116" s="12" t="n"/>
+      <c r="O116" s="12" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P116" s="12" t="inlineStr">
+        <is>
+          <t>Verbatim rebuild, 2026-09-23. See docs/act_verbatim_rebuild_2026-09-23.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="12" t="inlineStr">
+        <is>
+          <t>CHG-0069</t>
+        </is>
+      </c>
+      <c r="B117" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-23T07:07:11.937949+00:00</t>
+        </is>
+      </c>
+      <c r="C117" s="12" t="inlineStr">
+        <is>
+          <t>DPDPA-S29</t>
+        </is>
+      </c>
+      <c r="D117" s="12" t="inlineStr">
+        <is>
+          <t>Correction</t>
+        </is>
+      </c>
+      <c r="E117" s="12" t="inlineStr">
+        <is>
+          <t>data_correction</t>
+        </is>
+      </c>
+      <c r="F117" s="12" t="inlineStr">
+        <is>
+          <t>Text rebuilt verbatim from the official Act PDF (data-quality fix, not a legal change).</t>
+        </is>
+      </c>
+      <c r="G117" s="12" t="inlineStr">
+        <is>
+          <t>Text rebuilt verbatim from the official Act PDF (data-quality fix, not a legal change).</t>
+        </is>
+      </c>
+      <c r="H117" s="12" t="inlineStr">
+        <is>
+          <t>DPDP Act, 2023 (official PDF)</t>
+        </is>
+      </c>
+      <c r="I117" s="12" t="inlineStr">
+        <is>
+          <t>docs/full_text/DPDP_Act_2023_official_2026-09-23.pdf</t>
+        </is>
+      </c>
+      <c r="J117" s="12" t="inlineStr">
+        <is>
+          <t>manual:verbatim-rebuild-2026-09-23 (code-extracted, no model-written text)</t>
+        </is>
+      </c>
+      <c r="K117" s="12" t="n"/>
+      <c r="L117" s="12" t="inlineStr">
+        <is>
+          <t>Pending Review</t>
+        </is>
+      </c>
+      <c r="M117" s="12" t="n"/>
+      <c r="N117" s="12" t="n"/>
+      <c r="O117" s="12" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P117" s="12" t="inlineStr">
+        <is>
+          <t>Verbatim rebuild, 2026-09-23. See docs/act_verbatim_rebuild_2026-09-23.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="12" t="inlineStr">
+        <is>
+          <t>CHG-0070</t>
+        </is>
+      </c>
+      <c r="B118" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-23T07:07:11.937949+00:00</t>
+        </is>
+      </c>
+      <c r="C118" s="12" t="inlineStr">
+        <is>
+          <t>DPDPA-S30</t>
+        </is>
+      </c>
+      <c r="D118" s="12" t="inlineStr">
+        <is>
+          <t>Correction</t>
+        </is>
+      </c>
+      <c r="E118" s="12" t="inlineStr">
+        <is>
+          <t>data_correction</t>
+        </is>
+      </c>
+      <c r="F118" s="12" t="inlineStr">
+        <is>
+          <t>Text rebuilt verbatim from the official Act PDF (data-quality fix, not a legal change).</t>
+        </is>
+      </c>
+      <c r="G118" s="12" t="inlineStr">
+        <is>
+          <t>Text rebuilt verbatim from the official Act PDF (data-quality fix, not a legal change).</t>
+        </is>
+      </c>
+      <c r="H118" s="12" t="inlineStr">
+        <is>
+          <t>DPDP Act, 2023 (official PDF)</t>
+        </is>
+      </c>
+      <c r="I118" s="12" t="inlineStr">
+        <is>
+          <t>docs/full_text/DPDP_Act_2023_official_2026-09-23.pdf</t>
+        </is>
+      </c>
+      <c r="J118" s="12" t="inlineStr">
+        <is>
+          <t>manual:verbatim-rebuild-2026-09-23 (code-extracted, no model-written text)</t>
+        </is>
+      </c>
+      <c r="K118" s="12" t="n"/>
+      <c r="L118" s="12" t="inlineStr">
+        <is>
+          <t>Pending Review</t>
+        </is>
+      </c>
+      <c r="M118" s="12" t="n"/>
+      <c r="N118" s="12" t="n"/>
+      <c r="O118" s="12" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P118" s="12" t="inlineStr">
+        <is>
+          <t>Verbatim rebuild, 2026-09-23. See docs/act_verbatim_rebuild_2026-09-23.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="12" t="inlineStr">
+        <is>
+          <t>CHG-0071</t>
+        </is>
+      </c>
+      <c r="B119" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-23T07:07:11.937949+00:00</t>
+        </is>
+      </c>
+      <c r="C119" s="12" t="inlineStr">
+        <is>
+          <t>DPDPA-S31</t>
+        </is>
+      </c>
+      <c r="D119" s="12" t="inlineStr">
+        <is>
+          <t>Correction</t>
+        </is>
+      </c>
+      <c r="E119" s="12" t="inlineStr">
+        <is>
+          <t>data_correction</t>
+        </is>
+      </c>
+      <c r="F119" s="12" t="inlineStr">
+        <is>
+          <t>Text rebuilt verbatim from the official Act PDF (data-quality fix, not a legal change).</t>
+        </is>
+      </c>
+      <c r="G119" s="12" t="inlineStr">
+        <is>
+          <t>Text rebuilt verbatim from the official Act PDF (data-quality fix, not a legal change).</t>
+        </is>
+      </c>
+      <c r="H119" s="12" t="inlineStr">
+        <is>
+          <t>DPDP Act, 2023 (official PDF)</t>
+        </is>
+      </c>
+      <c r="I119" s="12" t="inlineStr">
+        <is>
+          <t>docs/full_text/DPDP_Act_2023_official_2026-09-23.pdf</t>
+        </is>
+      </c>
+      <c r="J119" s="12" t="inlineStr">
+        <is>
+          <t>manual:verbatim-rebuild-2026-09-23 (code-extracted, no model-written text)</t>
+        </is>
+      </c>
+      <c r="K119" s="12" t="n"/>
+      <c r="L119" s="12" t="inlineStr">
+        <is>
+          <t>Pending Review</t>
+        </is>
+      </c>
+      <c r="M119" s="12" t="n"/>
+      <c r="N119" s="12" t="n"/>
+      <c r="O119" s="12" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P119" s="12" t="inlineStr">
+        <is>
+          <t>Verbatim rebuild, 2026-09-23. See docs/act_verbatim_rebuild_2026-09-23.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="12" t="inlineStr">
+        <is>
+          <t>CHG-0072</t>
+        </is>
+      </c>
+      <c r="B120" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-23T07:07:11.937949+00:00</t>
+        </is>
+      </c>
+      <c r="C120" s="12" t="inlineStr">
+        <is>
+          <t>DPDPA-S32</t>
+        </is>
+      </c>
+      <c r="D120" s="12" t="inlineStr">
+        <is>
+          <t>Correction</t>
+        </is>
+      </c>
+      <c r="E120" s="12" t="inlineStr">
+        <is>
+          <t>data_correction</t>
+        </is>
+      </c>
+      <c r="F120" s="12" t="inlineStr">
+        <is>
+          <t>Text rebuilt verbatim from the official Act PDF (data-quality fix, not a legal change).</t>
+        </is>
+      </c>
+      <c r="G120" s="12" t="inlineStr">
+        <is>
+          <t>Text rebuilt verbatim from the official Act PDF (data-quality fix, not a legal change).</t>
+        </is>
+      </c>
+      <c r="H120" s="12" t="inlineStr">
+        <is>
+          <t>DPDP Act, 2023 (official PDF)</t>
+        </is>
+      </c>
+      <c r="I120" s="12" t="inlineStr">
+        <is>
+          <t>docs/full_text/DPDP_Act_2023_official_2026-09-23.pdf</t>
+        </is>
+      </c>
+      <c r="J120" s="12" t="inlineStr">
+        <is>
+          <t>manual:verbatim-rebuild-2026-09-23 (code-extracted, no model-written text)</t>
+        </is>
+      </c>
+      <c r="K120" s="12" t="n"/>
+      <c r="L120" s="12" t="inlineStr">
+        <is>
+          <t>Pending Review</t>
+        </is>
+      </c>
+      <c r="M120" s="12" t="n"/>
+      <c r="N120" s="12" t="n"/>
+      <c r="O120" s="12" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P120" s="12" t="inlineStr">
+        <is>
+          <t>Verbatim rebuild, 2026-09-23. See docs/act_verbatim_rebuild_2026-09-23.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="12" t="inlineStr">
+        <is>
+          <t>CHG-0073</t>
+        </is>
+      </c>
+      <c r="B121" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-23T07:07:11.937949+00:00</t>
+        </is>
+      </c>
+      <c r="C121" s="12" t="inlineStr">
+        <is>
+          <t>DPDPA-S33</t>
+        </is>
+      </c>
+      <c r="D121" s="12" t="inlineStr">
+        <is>
+          <t>Correction</t>
+        </is>
+      </c>
+      <c r="E121" s="12" t="inlineStr">
+        <is>
+          <t>data_correction</t>
+        </is>
+      </c>
+      <c r="F121" s="12" t="inlineStr">
+        <is>
+          <t>Text rebuilt verbatim from the official Act PDF (data-quality fix, not a legal change).</t>
+        </is>
+      </c>
+      <c r="G121" s="12" t="inlineStr">
+        <is>
+          <t>Text rebuilt verbatim from the official Act PDF (data-quality fix, not a legal change).</t>
+        </is>
+      </c>
+      <c r="H121" s="12" t="inlineStr">
+        <is>
+          <t>DPDP Act, 2023 (official PDF)</t>
+        </is>
+      </c>
+      <c r="I121" s="12" t="inlineStr">
+        <is>
+          <t>docs/full_text/DPDP_Act_2023_official_2026-09-23.pdf</t>
+        </is>
+      </c>
+      <c r="J121" s="12" t="inlineStr">
+        <is>
+          <t>manual:verbatim-rebuild-2026-09-23 (code-extracted, no model-written text)</t>
+        </is>
+      </c>
+      <c r="K121" s="12" t="n"/>
+      <c r="L121" s="12" t="inlineStr">
+        <is>
+          <t>Pending Review</t>
+        </is>
+      </c>
+      <c r="M121" s="12" t="n"/>
+      <c r="N121" s="12" t="n"/>
+      <c r="O121" s="12" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P121" s="12" t="inlineStr">
+        <is>
+          <t>Verbatim rebuild, 2026-09-23. See docs/act_verbatim_rebuild_2026-09-23.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="12" t="inlineStr">
+        <is>
+          <t>CHG-0074</t>
+        </is>
+      </c>
+      <c r="B122" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-23T07:07:11.937949+00:00</t>
+        </is>
+      </c>
+      <c r="C122" s="12" t="inlineStr">
+        <is>
+          <t>DPDPA-S34</t>
+        </is>
+      </c>
+      <c r="D122" s="12" t="inlineStr">
+        <is>
+          <t>Correction</t>
+        </is>
+      </c>
+      <c r="E122" s="12" t="inlineStr">
+        <is>
+          <t>data_correction</t>
+        </is>
+      </c>
+      <c r="F122" s="12" t="inlineStr">
+        <is>
+          <t>Text rebuilt verbatim from the official Act PDF (data-quality fix, not a legal change).</t>
+        </is>
+      </c>
+      <c r="G122" s="12" t="inlineStr">
+        <is>
+          <t>Text rebuilt verbatim from the official Act PDF (data-quality fix, not a legal change).</t>
+        </is>
+      </c>
+      <c r="H122" s="12" t="inlineStr">
+        <is>
+          <t>DPDP Act, 2023 (official PDF)</t>
+        </is>
+      </c>
+      <c r="I122" s="12" t="inlineStr">
+        <is>
+          <t>docs/full_text/DPDP_Act_2023_official_2026-09-23.pdf</t>
+        </is>
+      </c>
+      <c r="J122" s="12" t="inlineStr">
+        <is>
+          <t>manual:verbatim-rebuild-2026-09-23 (code-extracted, no model-written text)</t>
+        </is>
+      </c>
+      <c r="K122" s="12" t="n"/>
+      <c r="L122" s="12" t="inlineStr">
+        <is>
+          <t>Pending Review</t>
+        </is>
+      </c>
+      <c r="M122" s="12" t="n"/>
+      <c r="N122" s="12" t="n"/>
+      <c r="O122" s="12" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P122" s="12" t="inlineStr">
+        <is>
+          <t>Verbatim rebuild, 2026-09-23. See docs/act_verbatim_rebuild_2026-09-23.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="12" t="inlineStr">
+        <is>
+          <t>CHG-0075</t>
+        </is>
+      </c>
+      <c r="B123" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-23T07:07:11.937949+00:00</t>
+        </is>
+      </c>
+      <c r="C123" s="12" t="inlineStr">
+        <is>
+          <t>DPDPA-S35</t>
+        </is>
+      </c>
+      <c r="D123" s="12" t="inlineStr">
+        <is>
+          <t>Correction</t>
+        </is>
+      </c>
+      <c r="E123" s="12" t="inlineStr">
+        <is>
+          <t>data_correction</t>
+        </is>
+      </c>
+      <c r="F123" s="12" t="inlineStr">
+        <is>
+          <t>Text rebuilt verbatim from the official Act PDF (data-quality fix, not a legal change).</t>
+        </is>
+      </c>
+      <c r="G123" s="12" t="inlineStr">
+        <is>
+          <t>Text rebuilt verbatim from the official Act PDF (data-quality fix, not a legal change).</t>
+        </is>
+      </c>
+      <c r="H123" s="12" t="inlineStr">
+        <is>
+          <t>DPDP Act, 2023 (official PDF)</t>
+        </is>
+      </c>
+      <c r="I123" s="12" t="inlineStr">
+        <is>
+          <t>docs/full_text/DPDP_Act_2023_official_2026-09-23.pdf</t>
+        </is>
+      </c>
+      <c r="J123" s="12" t="inlineStr">
+        <is>
+          <t>manual:verbatim-rebuild-2026-09-23 (code-extracted, no model-written text)</t>
+        </is>
+      </c>
+      <c r="K123" s="12" t="n"/>
+      <c r="L123" s="12" t="inlineStr">
+        <is>
+          <t>Pending Review</t>
+        </is>
+      </c>
+      <c r="M123" s="12" t="n"/>
+      <c r="N123" s="12" t="n"/>
+      <c r="O123" s="12" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P123" s="12" t="inlineStr">
+        <is>
+          <t>Verbatim rebuild, 2026-09-23. See docs/act_verbatim_rebuild_2026-09-23.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="12" t="inlineStr">
+        <is>
+          <t>CHG-0076</t>
+        </is>
+      </c>
+      <c r="B124" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-23T07:07:11.937949+00:00</t>
+        </is>
+      </c>
+      <c r="C124" s="12" t="inlineStr">
+        <is>
+          <t>DPDPA-S36</t>
+        </is>
+      </c>
+      <c r="D124" s="12" t="inlineStr">
+        <is>
+          <t>Correction</t>
+        </is>
+      </c>
+      <c r="E124" s="12" t="inlineStr">
+        <is>
+          <t>data_correction</t>
+        </is>
+      </c>
+      <c r="F124" s="12" t="inlineStr">
+        <is>
+          <t>Text rebuilt verbatim from the official Act PDF (data-quality fix, not a legal change).</t>
+        </is>
+      </c>
+      <c r="G124" s="12" t="inlineStr">
+        <is>
+          <t>Text rebuilt verbatim from the official Act PDF (data-quality fix, not a legal change).</t>
+        </is>
+      </c>
+      <c r="H124" s="12" t="inlineStr">
+        <is>
+          <t>DPDP Act, 2023 (official PDF)</t>
+        </is>
+      </c>
+      <c r="I124" s="12" t="inlineStr">
+        <is>
+          <t>docs/full_text/DPDP_Act_2023_official_2026-09-23.pdf</t>
+        </is>
+      </c>
+      <c r="J124" s="12" t="inlineStr">
+        <is>
+          <t>manual:verbatim-rebuild-2026-09-23 (code-extracted, no model-written text)</t>
+        </is>
+      </c>
+      <c r="K124" s="12" t="n"/>
+      <c r="L124" s="12" t="inlineStr">
+        <is>
+          <t>Pending Review</t>
+        </is>
+      </c>
+      <c r="M124" s="12" t="n"/>
+      <c r="N124" s="12" t="n"/>
+      <c r="O124" s="12" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P124" s="12" t="inlineStr">
+        <is>
+          <t>Verbatim rebuild, 2026-09-23. See docs/act_verbatim_rebuild_2026-09-23.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="12" t="inlineStr">
+        <is>
+          <t>CHG-0077</t>
+        </is>
+      </c>
+      <c r="B125" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-23T07:07:11.937949+00:00</t>
+        </is>
+      </c>
+      <c r="C125" s="12" t="inlineStr">
+        <is>
+          <t>DPDPA-S37</t>
+        </is>
+      </c>
+      <c r="D125" s="12" t="inlineStr">
+        <is>
+          <t>Correction</t>
+        </is>
+      </c>
+      <c r="E125" s="12" t="inlineStr">
+        <is>
+          <t>data_correction</t>
+        </is>
+      </c>
+      <c r="F125" s="12" t="inlineStr">
+        <is>
+          <t>Text rebuilt verbatim from the official Act PDF (data-quality fix, not a legal change).</t>
+        </is>
+      </c>
+      <c r="G125" s="12" t="inlineStr">
+        <is>
+          <t>Text rebuilt verbatim from the official Act PDF (data-quality fix, not a legal change).</t>
+        </is>
+      </c>
+      <c r="H125" s="12" t="inlineStr">
+        <is>
+          <t>DPDP Act, 2023 (official PDF)</t>
+        </is>
+      </c>
+      <c r="I125" s="12" t="inlineStr">
+        <is>
+          <t>docs/full_text/DPDP_Act_2023_official_2026-09-23.pdf</t>
+        </is>
+      </c>
+      <c r="J125" s="12" t="inlineStr">
+        <is>
+          <t>manual:verbatim-rebuild-2026-09-23 (code-extracted, no model-written text)</t>
+        </is>
+      </c>
+      <c r="K125" s="12" t="n"/>
+      <c r="L125" s="12" t="inlineStr">
+        <is>
+          <t>Pending Review</t>
+        </is>
+      </c>
+      <c r="M125" s="12" t="n"/>
+      <c r="N125" s="12" t="n"/>
+      <c r="O125" s="12" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P125" s="12" t="inlineStr">
+        <is>
+          <t>Verbatim rebuild, 2026-09-23. See docs/act_verbatim_rebuild_2026-09-23.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="12" t="inlineStr">
+        <is>
+          <t>CHG-0078</t>
+        </is>
+      </c>
+      <c r="B126" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-23T07:07:11.937949+00:00</t>
+        </is>
+      </c>
+      <c r="C126" s="12" t="inlineStr">
+        <is>
+          <t>DPDPA-S38</t>
+        </is>
+      </c>
+      <c r="D126" s="12" t="inlineStr">
+        <is>
+          <t>Correction</t>
+        </is>
+      </c>
+      <c r="E126" s="12" t="inlineStr">
+        <is>
+          <t>data_correction</t>
+        </is>
+      </c>
+      <c r="F126" s="12" t="inlineStr">
+        <is>
+          <t>Text rebuilt verbatim from the official Act PDF (data-quality fix, not a legal change).</t>
+        </is>
+      </c>
+      <c r="G126" s="12" t="inlineStr">
+        <is>
+          <t>Text rebuilt verbatim from the official Act PDF (data-quality fix, not a legal change).</t>
+        </is>
+      </c>
+      <c r="H126" s="12" t="inlineStr">
+        <is>
+          <t>DPDP Act, 2023 (official PDF)</t>
+        </is>
+      </c>
+      <c r="I126" s="12" t="inlineStr">
+        <is>
+          <t>docs/full_text/DPDP_Act_2023_official_2026-09-23.pdf</t>
+        </is>
+      </c>
+      <c r="J126" s="12" t="inlineStr">
+        <is>
+          <t>manual:verbatim-rebuild-2026-09-23 (code-extracted, no model-written text)</t>
+        </is>
+      </c>
+      <c r="K126" s="12" t="n"/>
+      <c r="L126" s="12" t="inlineStr">
+        <is>
+          <t>Pending Review</t>
+        </is>
+      </c>
+      <c r="M126" s="12" t="n"/>
+      <c r="N126" s="12" t="n"/>
+      <c r="O126" s="12" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P126" s="12" t="inlineStr">
+        <is>
+          <t>Verbatim rebuild, 2026-09-23. See docs/act_verbatim_rebuild_2026-09-23.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="12" t="inlineStr">
+        <is>
+          <t>CHG-0079</t>
+        </is>
+      </c>
+      <c r="B127" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-23T07:07:11.937949+00:00</t>
+        </is>
+      </c>
+      <c r="C127" s="12" t="inlineStr">
+        <is>
+          <t>DPDPA-S39</t>
+        </is>
+      </c>
+      <c r="D127" s="12" t="inlineStr">
+        <is>
+          <t>Correction</t>
+        </is>
+      </c>
+      <c r="E127" s="12" t="inlineStr">
+        <is>
+          <t>data_correction</t>
+        </is>
+      </c>
+      <c r="F127" s="12" t="inlineStr">
+        <is>
+          <t>Text rebuilt verbatim from the official Act PDF (data-quality fix, not a legal change).</t>
+        </is>
+      </c>
+      <c r="G127" s="12" t="inlineStr">
+        <is>
+          <t>Text rebuilt verbatim from the official Act PDF (data-quality fix, not a legal change).</t>
+        </is>
+      </c>
+      <c r="H127" s="12" t="inlineStr">
+        <is>
+          <t>DPDP Act, 2023 (official PDF)</t>
+        </is>
+      </c>
+      <c r="I127" s="12" t="inlineStr">
+        <is>
+          <t>docs/full_text/DPDP_Act_2023_official_2026-09-23.pdf</t>
+        </is>
+      </c>
+      <c r="J127" s="12" t="inlineStr">
+        <is>
+          <t>manual:verbatim-rebuild-2026-09-23 (code-extracted, no model-written text)</t>
+        </is>
+      </c>
+      <c r="K127" s="12" t="n"/>
+      <c r="L127" s="12" t="inlineStr">
+        <is>
+          <t>Pending Review</t>
+        </is>
+      </c>
+      <c r="M127" s="12" t="n"/>
+      <c r="N127" s="12" t="n"/>
+      <c r="O127" s="12" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P127" s="12" t="inlineStr">
+        <is>
+          <t>Verbatim rebuild, 2026-09-23. See docs/act_verbatim_rebuild_2026-09-23.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="12" t="inlineStr">
+        <is>
+          <t>CHG-0080</t>
+        </is>
+      </c>
+      <c r="B128" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-23T07:07:11.937949+00:00</t>
+        </is>
+      </c>
+      <c r="C128" s="12" t="inlineStr">
+        <is>
+          <t>DPDPA-S40</t>
+        </is>
+      </c>
+      <c r="D128" s="12" t="inlineStr">
+        <is>
+          <t>Correction</t>
+        </is>
+      </c>
+      <c r="E128" s="12" t="inlineStr">
+        <is>
+          <t>data_correction</t>
+        </is>
+      </c>
+      <c r="F128" s="12" t="inlineStr">
+        <is>
+          <t>Text rebuilt verbatim from the official Act PDF (data-quality fix, not a legal change).</t>
+        </is>
+      </c>
+      <c r="G128" s="12" t="inlineStr">
+        <is>
+          <t>Text rebuilt verbatim from the official Act PDF (data-quality fix, not a legal change).</t>
+        </is>
+      </c>
+      <c r="H128" s="12" t="inlineStr">
+        <is>
+          <t>DPDP Act, 2023 (official PDF)</t>
+        </is>
+      </c>
+      <c r="I128" s="12" t="inlineStr">
+        <is>
+          <t>docs/full_text/DPDP_Act_2023_official_2026-09-23.pdf</t>
+        </is>
+      </c>
+      <c r="J128" s="12" t="inlineStr">
+        <is>
+          <t>manual:verbatim-rebuild-2026-09-23 (code-extracted, no model-written text)</t>
+        </is>
+      </c>
+      <c r="K128" s="12" t="n"/>
+      <c r="L128" s="12" t="inlineStr">
+        <is>
+          <t>Pending Review</t>
+        </is>
+      </c>
+      <c r="M128" s="12" t="n"/>
+      <c r="N128" s="12" t="n"/>
+      <c r="O128" s="12" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P128" s="12" t="inlineStr">
+        <is>
+          <t>Verbatim rebuild, 2026-09-23. See docs/act_verbatim_rebuild_2026-09-23.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="12" t="inlineStr">
+        <is>
+          <t>CHG-0081</t>
+        </is>
+      </c>
+      <c r="B129" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-23T07:07:11.937949+00:00</t>
+        </is>
+      </c>
+      <c r="C129" s="12" t="inlineStr">
+        <is>
+          <t>DPDPA-S41</t>
+        </is>
+      </c>
+      <c r="D129" s="12" t="inlineStr">
+        <is>
+          <t>Correction</t>
+        </is>
+      </c>
+      <c r="E129" s="12" t="inlineStr">
+        <is>
+          <t>data_correction</t>
+        </is>
+      </c>
+      <c r="F129" s="12" t="inlineStr">
+        <is>
+          <t>Text rebuilt verbatim from the official Act PDF (data-quality fix, not a legal change).</t>
+        </is>
+      </c>
+      <c r="G129" s="12" t="inlineStr">
+        <is>
+          <t>Text rebuilt verbatim from the official Act PDF (data-quality fix, not a legal change).</t>
+        </is>
+      </c>
+      <c r="H129" s="12" t="inlineStr">
+        <is>
+          <t>DPDP Act, 2023 (official PDF)</t>
+        </is>
+      </c>
+      <c r="I129" s="12" t="inlineStr">
+        <is>
+          <t>docs/full_text/DPDP_Act_2023_official_2026-09-23.pdf</t>
+        </is>
+      </c>
+      <c r="J129" s="12" t="inlineStr">
+        <is>
+          <t>manual:verbatim-rebuild-2026-09-23 (code-extracted, no model-written text)</t>
+        </is>
+      </c>
+      <c r="K129" s="12" t="n"/>
+      <c r="L129" s="12" t="inlineStr">
+        <is>
+          <t>Pending Review</t>
+        </is>
+      </c>
+      <c r="M129" s="12" t="n"/>
+      <c r="N129" s="12" t="n"/>
+      <c r="O129" s="12" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P129" s="12" t="inlineStr">
+        <is>
+          <t>Verbatim rebuild, 2026-09-23. See docs/act_verbatim_rebuild_2026-09-23.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="12" t="inlineStr">
+        <is>
+          <t>CHG-0082</t>
+        </is>
+      </c>
+      <c r="B130" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-23T07:07:11.937949+00:00</t>
+        </is>
+      </c>
+      <c r="C130" s="12" t="inlineStr">
+        <is>
+          <t>DPDPA-S43</t>
+        </is>
+      </c>
+      <c r="D130" s="12" t="inlineStr">
+        <is>
+          <t>Correction</t>
+        </is>
+      </c>
+      <c r="E130" s="12" t="inlineStr">
+        <is>
+          <t>data_correction</t>
+        </is>
+      </c>
+      <c r="F130" s="12" t="inlineStr">
+        <is>
+          <t>Text rebuilt verbatim from the official Act PDF (data-quality fix, not a legal change).</t>
+        </is>
+      </c>
+      <c r="G130" s="12" t="inlineStr">
+        <is>
+          <t>Text rebuilt verbatim from the official Act PDF (data-quality fix, not a legal change).</t>
+        </is>
+      </c>
+      <c r="H130" s="12" t="inlineStr">
+        <is>
+          <t>DPDP Act, 2023 (official PDF)</t>
+        </is>
+      </c>
+      <c r="I130" s="12" t="inlineStr">
+        <is>
+          <t>docs/full_text/DPDP_Act_2023_official_2026-09-23.pdf</t>
+        </is>
+      </c>
+      <c r="J130" s="12" t="inlineStr">
+        <is>
+          <t>manual:verbatim-rebuild-2026-09-23 (code-extracted, no model-written text)</t>
+        </is>
+      </c>
+      <c r="K130" s="12" t="n"/>
+      <c r="L130" s="12" t="inlineStr">
+        <is>
+          <t>Pending Review</t>
+        </is>
+      </c>
+      <c r="M130" s="12" t="n"/>
+      <c r="N130" s="12" t="n"/>
+      <c r="O130" s="12" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P130" s="12" t="inlineStr">
+        <is>
+          <t>Verbatim rebuild, 2026-09-23. See docs/act_verbatim_rebuild_2026-09-23.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="12" t="inlineStr">
+        <is>
+          <t>CHG-0083</t>
+        </is>
+      </c>
+      <c r="B131" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-23T07:07:11.937949+00:00</t>
+        </is>
+      </c>
+      <c r="C131" s="12" t="inlineStr">
+        <is>
+          <t>DPDPA-S44.1_3</t>
+        </is>
+      </c>
+      <c r="D131" s="12" t="inlineStr">
+        <is>
+          <t>Correction</t>
+        </is>
+      </c>
+      <c r="E131" s="12" t="inlineStr">
+        <is>
+          <t>data_correction</t>
+        </is>
+      </c>
+      <c r="F131" s="12" t="inlineStr">
+        <is>
+          <t>Text rebuilt verbatim from the official Act PDF (data-quality fix, not a legal change).</t>
+        </is>
+      </c>
+      <c r="G131" s="12" t="inlineStr">
+        <is>
+          <t>Text rebuilt verbatim from the official Act PDF (data-quality fix, not a legal change).</t>
+        </is>
+      </c>
+      <c r="H131" s="12" t="inlineStr">
+        <is>
+          <t>DPDP Act, 2023 (official PDF)</t>
+        </is>
+      </c>
+      <c r="I131" s="12" t="inlineStr">
+        <is>
+          <t>docs/full_text/DPDP_Act_2023_official_2026-09-23.pdf</t>
+        </is>
+      </c>
+      <c r="J131" s="12" t="inlineStr">
+        <is>
+          <t>manual:verbatim-rebuild-2026-09-23 (code-extracted, no model-written text)</t>
+        </is>
+      </c>
+      <c r="K131" s="12" t="n"/>
+      <c r="L131" s="12" t="inlineStr">
+        <is>
+          <t>Pending Review</t>
+        </is>
+      </c>
+      <c r="M131" s="12" t="n"/>
+      <c r="N131" s="12" t="n"/>
+      <c r="O131" s="12" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P131" s="12" t="inlineStr">
+        <is>
+          <t>Verbatim rebuild, 2026-09-23. See docs/act_verbatim_rebuild_2026-09-23.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="12" t="inlineStr">
+        <is>
+          <t>CHG-0084</t>
+        </is>
+      </c>
+      <c r="B132" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-23T07:07:11.937949+00:00</t>
+        </is>
+      </c>
+      <c r="C132" s="12" t="inlineStr">
+        <is>
+          <t>DPDPA-S44.2</t>
+        </is>
+      </c>
+      <c r="D132" s="12" t="inlineStr">
+        <is>
+          <t>Correction</t>
+        </is>
+      </c>
+      <c r="E132" s="12" t="inlineStr">
+        <is>
+          <t>data_correction</t>
+        </is>
+      </c>
+      <c r="F132" s="12" t="inlineStr">
+        <is>
+          <t>Text rebuilt verbatim from the official Act PDF (data-quality fix, not a legal change).</t>
+        </is>
+      </c>
+      <c r="G132" s="12" t="inlineStr">
+        <is>
+          <t>Text rebuilt verbatim from the official Act PDF (data-quality fix, not a legal change).</t>
+        </is>
+      </c>
+      <c r="H132" s="12" t="inlineStr">
+        <is>
+          <t>DPDP Act, 2023 (official PDF)</t>
+        </is>
+      </c>
+      <c r="I132" s="12" t="inlineStr">
+        <is>
+          <t>docs/full_text/DPDP_Act_2023_official_2026-09-23.pdf</t>
+        </is>
+      </c>
+      <c r="J132" s="12" t="inlineStr">
+        <is>
+          <t>manual:verbatim-rebuild-2026-09-23 (code-extracted, no model-written text)</t>
+        </is>
+      </c>
+      <c r="K132" s="12" t="n"/>
+      <c r="L132" s="12" t="inlineStr">
+        <is>
+          <t>Pending Review</t>
+        </is>
+      </c>
+      <c r="M132" s="12" t="n"/>
+      <c r="N132" s="12" t="n"/>
+      <c r="O132" s="12" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P132" s="12" t="inlineStr">
+        <is>
+          <t>Verbatim rebuild, 2026-09-23. See docs/act_verbatim_rebuild_2026-09-23.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="12" t="inlineStr">
+        <is>
+          <t>CHG-0085</t>
+        </is>
+      </c>
+      <c r="B133" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-23T07:07:11.937949+00:00</t>
+        </is>
+      </c>
+      <c r="C133" s="12" t="inlineStr">
+        <is>
+          <t>DPDPA-SCHED</t>
+        </is>
+      </c>
+      <c r="D133" s="12" t="inlineStr">
+        <is>
+          <t>Correction</t>
+        </is>
+      </c>
+      <c r="E133" s="12" t="inlineStr">
+        <is>
+          <t>data_correction</t>
+        </is>
+      </c>
+      <c r="F133" s="12" t="inlineStr">
+        <is>
+          <t>Text rebuilt verbatim from the official Act PDF (data-quality fix, not a legal change).</t>
+        </is>
+      </c>
+      <c r="G133" s="12" t="inlineStr">
+        <is>
+          <t>Text rebuilt verbatim from the official Act PDF (data-quality fix, not a legal change).</t>
+        </is>
+      </c>
+      <c r="H133" s="12" t="inlineStr">
+        <is>
+          <t>DPDP Act, 2023 (official PDF)</t>
+        </is>
+      </c>
+      <c r="I133" s="12" t="inlineStr">
+        <is>
+          <t>docs/full_text/DPDP_Act_2023_official_2026-09-23.pdf</t>
+        </is>
+      </c>
+      <c r="J133" s="12" t="inlineStr">
+        <is>
+          <t>manual:verbatim-rebuild-2026-09-23 (code-extracted, no model-written text)</t>
+        </is>
+      </c>
+      <c r="K133" s="12" t="n"/>
+      <c r="L133" s="12" t="inlineStr">
+        <is>
+          <t>Pending Review</t>
+        </is>
+      </c>
+      <c r="M133" s="12" t="n"/>
+      <c r="N133" s="12" t="n"/>
+      <c r="O133" s="12" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P133" s="12" t="inlineStr">
+        <is>
+          <t>Verbatim rebuild, 2026-09-23. See docs/act_verbatim_rebuild_2026-09-23.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="16" t="inlineStr">
+        <is>
+          <t>CHG-0086</t>
+        </is>
+      </c>
+      <c r="B134" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-23T07:16:14.779319+00:00</t>
+        </is>
+      </c>
+      <c r="C134" s="16" t="inlineStr">
+        <is>
+          <t>DPDPR-R1</t>
+        </is>
+      </c>
+      <c r="D134" s="16" t="inlineStr">
+        <is>
+          <t>Correction</t>
+        </is>
+      </c>
+      <c r="E134" s="16" t="inlineStr">
+        <is>
+          <t>regulatory</t>
+        </is>
+      </c>
+      <c r="F134" s="16" t="inlineStr">
+        <is>
+          <t>Text as originally gazetted in G.S.R. 846(E)</t>
+        </is>
+      </c>
+      <c r="G134" s="16" t="inlineStr">
+        <is>
+          <t>Text as corrected by G.S.R. 892(E)</t>
+        </is>
+      </c>
+      <c r="H134" s="16" t="inlineStr">
+        <is>
+          <t>Corrigenda G.S.R. 892(E), 10 Dec 2025 (Gazette Extraordinary No. 806, 11 Dec 2025)</t>
+        </is>
+      </c>
+      <c r="I134" s="16" t="inlineStr">
+        <is>
+          <t>https://www.meity.gov.in/static/uploads/2025/12/3c7ebbae0e5456f493f486e6845df86b.pdf</t>
+        </is>
+      </c>
+      <c r="J134" s="16" t="inlineStr">
+        <is>
+          <t>manual:audit-2026-09-23-corrigendum (phrase pair extracted by code from the corrigendum PDF)</t>
+        </is>
+      </c>
+      <c r="K134" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L134" s="16" t="inlineStr">
+        <is>
+          <t>Pending Review</t>
+        </is>
+      </c>
+      <c r="M134" s="16" t="n"/>
+      <c r="N134" s="16" t="n"/>
+      <c r="O134" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P134" s="16" t="inlineStr">
+        <is>
+          <t>Government corrigendum (regulatory change): 'of publication of this Gazette' -&gt; 'of publication in the Official Gazette', per G.S.R. 892(E).</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="16" t="inlineStr">
+        <is>
+          <t>CHG-0087</t>
+        </is>
+      </c>
+      <c r="B135" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-23T07:16:14.779319+00:00</t>
+        </is>
+      </c>
+      <c r="C135" s="16" t="inlineStr">
+        <is>
+          <t>DPDPR-SDF-R13</t>
+        </is>
+      </c>
+      <c r="D135" s="16" t="inlineStr">
+        <is>
+          <t>Correction</t>
+        </is>
+      </c>
+      <c r="E135" s="16" t="inlineStr">
+        <is>
+          <t>regulatory</t>
+        </is>
+      </c>
+      <c r="F135" s="16" t="inlineStr">
+        <is>
+          <t>Text as originally gazetted in G.S.R. 846(E)</t>
+        </is>
+      </c>
+      <c r="G135" s="16" t="inlineStr">
+        <is>
+          <t>Text as corrected by G.S.R. 892(E)</t>
+        </is>
+      </c>
+      <c r="H135" s="16" t="inlineStr">
+        <is>
+          <t>Corrigenda G.S.R. 892(E), 10 Dec 2025 (Gazette Extraordinary No. 806, 11 Dec 2025)</t>
+        </is>
+      </c>
+      <c r="I135" s="16" t="inlineStr">
+        <is>
+          <t>https://www.meity.gov.in/static/uploads/2025/12/3c7ebbae0e5456f493f486e6845df86b.pdf</t>
+        </is>
+      </c>
+      <c r="J135" s="16" t="inlineStr">
+        <is>
+          <t>manual:audit-2026-09-23-corrigendum (phrase pair extracted by code from the corrigendum PDF)</t>
+        </is>
+      </c>
+      <c r="K135" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L135" s="16" t="inlineStr">
+        <is>
+          <t>Pending Review</t>
+        </is>
+      </c>
+      <c r="M135" s="16" t="n"/>
+      <c r="N135" s="16" t="n"/>
+      <c r="O135" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P135" s="16" t="inlineStr">
+        <is>
+          <t>Government corrigendum (regulatory change): 'Department' -&gt; 'Departments', per G.S.R. 892(E).</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="16" t="inlineStr">
+        <is>
+          <t>CHG-0088</t>
+        </is>
+      </c>
+      <c r="B136" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-23T07:16:14.779319+00:00</t>
+        </is>
+      </c>
+      <c r="C136" s="16" t="inlineStr">
+        <is>
+          <t>DPDPR-R23</t>
+        </is>
+      </c>
+      <c r="D136" s="16" t="inlineStr">
+        <is>
+          <t>Correction</t>
+        </is>
+      </c>
+      <c r="E136" s="16" t="inlineStr">
+        <is>
+          <t>regulatory</t>
+        </is>
+      </c>
+      <c r="F136" s="16" t="inlineStr">
+        <is>
+          <t>Text as originally gazetted in G.S.R. 846(E)</t>
+        </is>
+      </c>
+      <c r="G136" s="16" t="inlineStr">
+        <is>
+          <t>Text as corrected by G.S.R. 892(E)</t>
+        </is>
+      </c>
+      <c r="H136" s="16" t="inlineStr">
+        <is>
+          <t>Corrigenda G.S.R. 892(E), 10 Dec 2025 (Gazette Extraordinary No. 806, 11 Dec 2025)</t>
+        </is>
+      </c>
+      <c r="I136" s="16" t="inlineStr">
+        <is>
+          <t>https://www.meity.gov.in/static/uploads/2025/12/3c7ebbae0e5456f493f486e6845df86b.pdf</t>
+        </is>
+      </c>
+      <c r="J136" s="16" t="inlineStr">
+        <is>
+          <t>manual:audit-2026-09-23-corrigendum (phrase pair extracted by code from the corrigendum PDF)</t>
+        </is>
+      </c>
+      <c r="K136" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L136" s="16" t="inlineStr">
+        <is>
+          <t>Pending Review</t>
+        </is>
+      </c>
+      <c r="M136" s="16" t="n"/>
+      <c r="N136" s="16" t="n"/>
+      <c r="O136" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P136" s="16" t="inlineStr">
+        <is>
+          <t>Government corrigendum (regulatory change): 'given in such' -&gt; 'given in such order', per G.S.R. 892(E).</t>
         </is>
       </c>
     </row>
@@ -13917,7 +17371,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -13981,27 +17435,27 @@
     <row r="2">
       <c r="A2" s="12" t="inlineStr">
         <is>
-          <t>SRC-0003</t>
+          <t>SRC-0002</t>
         </is>
       </c>
       <c r="B2" s="12" t="inlineStr">
         <is>
-          <t>eGazette</t>
+          <t>MeitY</t>
         </is>
       </c>
       <c r="C2" s="12" t="inlineStr">
         <is>
-          <t>Gazette Notification G.S.R. 843(E), 13 Nov 2025 (Act commencement schedule)</t>
+          <t>Digital Personal Data Protection Act, 2023 (Act No. 22 of 2023)</t>
         </is>
       </c>
       <c r="D2" s="12" t="inlineStr">
         <is>
-          <t>user-upload:Timelines_for_enforcement_of_DPDPA.pdf</t>
+          <t>https://www.meity.gov.in/static/uploads/2024/06/2bf1f0e9f04e6fb4f8fef35e82c42aa5.pdf</t>
         </is>
       </c>
       <c r="E2" s="12" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2023-08-11</t>
         </is>
       </c>
       <c r="F2" s="12" t="inlineStr">
@@ -14028,50 +17482,54 @@
     <row r="3">
       <c r="A3" s="12" t="inlineStr">
         <is>
-          <t>SRC-0001</t>
+          <t>SRC-0003</t>
         </is>
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>MeitY</t>
+          <t>eGazette</t>
         </is>
       </c>
       <c r="C3" s="12" t="inlineStr">
         <is>
-          <t>DPDP Rules, 2025 — MeitY PDF (G.S.R. 846(E))</t>
+          <t>Gazette Notification G.S.R. 843(E), 13 Nov 2025 (Act commencement schedule)</t>
         </is>
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>https://www.meity.gov.in/static/uploads/2025/11/53450e6e5dc0bfa85ebd78686cadad39.pdf</t>
-        </is>
-      </c>
-      <c r="E3" s="12" t="n"/>
+          <t>https://www.meity.gov.in/static/uploads/2025/11/c56ceae6c383460ca69577428d36828b.pdf</t>
+        </is>
+      </c>
+      <c r="E3" s="12" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
       <c r="F3" s="12" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G3" s="12" t="inlineStr">
         <is>
-          <t>76094c7228c8dbff357281552fa2b052fe363303eb8b2c33ee5361d38883070d</t>
+          <t>manual-seed-not-hashed</t>
         </is>
       </c>
       <c r="H3" s="12" t="inlineStr">
         <is>
-          <t>No Change Detected</t>
+          <t>Processed</t>
         </is>
       </c>
       <c r="I3" s="12" t="inlineStr">
         <is>
-          <t>CHG-0002,CHG-0003,CHG-0004,CHG-0005,CHG-0006,CHG-0007,CHG-0008,CHG-0009,CHG-0010,CHG-0011,CHG-0012,CHG-0013,CHG-0014,CHG-0015,CHG-0016,CHG-0017,CHG-0018,CHG-0019,CHG-0020,CHG-0021,CHG-0022,CHG-0023,CHG-0024,CHG-0025,CHG-0026,CHG-0027,CHG-0028,CHG-0029,CHG-0030,CHG-0031,CHG-0032</t>
+          <t>CHG-A0001,CHG-A0002,CHG-A0003,CHG-A0004,CHG-A0005,CHG-A0006,CHG-A0007,CHG-A0008,CHG-A0009,CHG-A0010,CHG-A0011,CHG-A0012,CHG-A0013,CHG-A0014,CHG-A0015,CHG-A0016,CHG-A0017,CHG-A0018,CHG-A0019,CHG-A0020,CHG-A0021,CHG-A0022,CHG-A0023,CHG-A0024,CHG-A0025,CHG-A0026,CHG-A0027,CHG-A0028,CHG-A0029,CHG-A0030,CHG-A0031,CHG-A0032,CHG-A0033,CHG-A0034,CHG-A0035,CHG-A0036,CHG-A0037,CHG-A0038,CHG-A0039,CHG-A0040,CHG-A0041,CHG-A0042,CHG-A0043,CHG-A0044,CHG-A0045,CHG-A0046,CHG-A0047,CHG-A0048</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="12" t="inlineStr">
         <is>
-          <t>SRC-0002</t>
+          <t>SRC-0001</t>
         </is>
       </c>
       <c r="B4" s="12" t="inlineStr">
@@ -14081,12 +17539,12 @@
       </c>
       <c r="C4" s="12" t="inlineStr">
         <is>
-          <t>DPDP Act, 2023 — MeitY PDF</t>
+          <t>DPDP Rules, 2025 — MeitY PDF (G.S.R. 846(E))</t>
         </is>
       </c>
       <c r="D4" s="12" t="inlineStr">
         <is>
-          <t>https://www.meity.gov.in/static/uploads/2024/06/2bf1f0e9f04e6fb4f8fef35e82c42aa5.pdf</t>
+          <t>https://www.meity.gov.in/static/uploads/2025/11/53450e6e5dc0bfa85ebd78686cadad39.pdf</t>
         </is>
       </c>
       <c r="E4" s="12" t="n"/>
@@ -14097,7 +17555,7 @@
       </c>
       <c r="G4" s="12" t="inlineStr">
         <is>
-          <t>f15bda1ff8065c68f8e1cc57c50616264afeb49d72cfc48d1e92a2a3c473c1d2</t>
+          <t>76094c7228c8dbff357281552fa2b052fe363303eb8b2c33ee5361d38883070d</t>
         </is>
       </c>
       <c r="H4" s="12" t="inlineStr">
@@ -14107,7 +17565,7 @@
       </c>
       <c r="I4" s="12" t="inlineStr">
         <is>
-          <t>CHG-A0001,CHG-A0002,CHG-A0003,CHG-A0004,CHG-A0005,CHG-A0006,CHG-A0007,CHG-A0008,CHG-A0009,CHG-A0010,CHG-A0011,CHG-A0012,CHG-A0013,CHG-A0014,CHG-A0015,CHG-A0016,CHG-A0017,CHG-A0018,CHG-A0019,CHG-A0020,CHG-A0021,CHG-A0022,CHG-A0023,CHG-A0024,CHG-A0025,CHG-A0026,CHG-A0027,CHG-A0028,CHG-A0029,CHG-A0030,CHG-A0031,CHG-A0032,CHG-A0033,CHG-A0034,CHG-A0035,CHG-A0036,CHG-A0037,CHG-A0038,CHG-A0039,CHG-A0040,CHG-A0041,CHG-A0042,CHG-A0043,CHG-A0044,CHG-A0045,CHG-A0046,CHG-A0047,CHG-A0048</t>
+          <t>CHG-0002,CHG-0003,CHG-0004,CHG-0005,CHG-0006,CHG-0007,CHG-0008,CHG-0009,CHG-0010,CHG-0011,CHG-0012,CHG-0013,CHG-0014,CHG-0015,CHG-0016,CHG-0017,CHG-0018,CHG-0019,CHG-0020,CHG-0021,CHG-0022,CHG-0023,CHG-0024,CHG-0025,CHG-0026,CHG-0027,CHG-0028,CHG-0029,CHG-0030,CHG-0031,CHG-0032</t>
         </is>
       </c>
     </row>
@@ -14188,6 +17646,53 @@
         </is>
       </c>
       <c r="I6" s="12" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>SRC-0006</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>MeitY</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>Corrigenda G.S.R. 892(E), 10 Dec 2025 (Gazette Extraordinary No. 806, 11 Dec 2025)</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>https://www.meity.gov.in/static/uploads/2025/12/3c7ebbae0e5456f493f486e6845df86b.pdf</t>
+        </is>
+      </c>
+      <c r="E7" s="12" t="inlineStr">
+        <is>
+          <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="F7" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G7" s="12" t="inlineStr">
+        <is>
+          <t>597d69e0d16cc9eeb72d1799195fe4a1b5fe4e2f3cb063310864736b39d3c244</t>
+        </is>
+      </c>
+      <c r="H7" s="12" t="inlineStr">
+        <is>
+          <t>Processed</t>
+        </is>
+      </c>
+      <c r="I7" s="12" t="inlineStr">
+        <is>
+          <t>CHG-0086,CHG-0087,CHG-0088</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="2">

--- a/data/DPDP_Rules_Tracker.xlsx
+++ b/data/DPDP_Rules_Tracker.xlsx
@@ -5263,7 +5263,7 @@
       </c>
       <c r="J51" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="K51" s="12" t="inlineStr">
@@ -5611,7 +5611,7 @@
       </c>
       <c r="J55" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="K55" s="12" t="inlineStr">
@@ -5785,7 +5785,7 @@
       </c>
       <c r="J57" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="K57" s="12" t="inlineStr">
@@ -5959,7 +5959,7 @@
       </c>
       <c r="J59" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="K59" s="12" t="inlineStr">
@@ -7438,7 +7438,7 @@
       </c>
       <c r="J76" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="K76" s="12" t="inlineStr">
@@ -7468,7 +7468,7 @@
       </c>
       <c r="R76" s="12" t="inlineStr">
         <is>
-          <t>Currently in force.</t>
+          <t>Currently in force. Text corrected 2026-09-23 against the official Act PDF (SHA-256 4deb2398...7d15), re-verified against a hash-confirmed copy of the source PDF (second extraction pass; Sonnet+Opus review) — see docs/act_table_audit_2026-09-23.md.</t>
         </is>
       </c>
       <c r="S76" s="14">
@@ -7931,7 +7931,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P136"/>
+  <dimension ref="A1:P140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -17343,6 +17343,294 @@
       <c r="P136" s="16" t="inlineStr">
         <is>
           <t>Government corrigendum (regulatory change): 'given in such' -&gt; 'given in such order', per G.S.R. 892(E).</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="12" t="inlineStr">
+        <is>
+          <t>CHG-0089</t>
+        </is>
+      </c>
+      <c r="B137" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-23T12:11:00.345078+00:00</t>
+        </is>
+      </c>
+      <c r="C137" s="12" t="inlineStr">
+        <is>
+          <t>DPDPR-SCH1</t>
+        </is>
+      </c>
+      <c r="D137" s="12" t="inlineStr">
+        <is>
+          <t>Correction</t>
+        </is>
+      </c>
+      <c r="E137" s="12" t="inlineStr">
+        <is>
+          <t>data_correction</t>
+        </is>
+      </c>
+      <c r="F137" s="12" t="inlineStr">
+        <is>
+          <t>Schedule text incompletely seeded (omitted at the original seeding session)</t>
+        </is>
+      </c>
+      <c r="G137" s="12" t="inlineStr">
+        <is>
+          <t>Restored verbatim from the official Rules PDF</t>
+        </is>
+      </c>
+      <c r="H137" s="12" t="inlineStr">
+        <is>
+          <t>DPDP Rules, 2025 (G.S.R. 846(E))</t>
+        </is>
+      </c>
+      <c r="I137" s="12" t="inlineStr">
+        <is>
+          <t>https://www.meity.gov.in/static/uploads/2025/11/53450e6e5dc0bfa85ebd78686cadad39.pdf</t>
+        </is>
+      </c>
+      <c r="J137" s="12" t="inlineStr">
+        <is>
+          <t>manual:rules-schedule-restoration-2026-09-23 (code-extracted, no model-written text)</t>
+        </is>
+      </c>
+      <c r="K137" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L137" s="12" t="inlineStr">
+        <is>
+          <t>Pending Review</t>
+        </is>
+      </c>
+      <c r="M137" s="12" t="n"/>
+      <c r="N137" s="12" t="n"/>
+      <c r="O137" s="12" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P137" s="12" t="inlineStr">
+        <is>
+          <t>Data-quality fix (not a regulatory change): restored text left out of DPDPR-SCH1 at seeding. See scripts/restore_rules_schedule_gaps_2026-09-23.py.</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="12" t="inlineStr">
+        <is>
+          <t>CHG-0090</t>
+        </is>
+      </c>
+      <c r="B138" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-23T12:11:00.345078+00:00</t>
+        </is>
+      </c>
+      <c r="C138" s="12" t="inlineStr">
+        <is>
+          <t>DPDPR-SCH3</t>
+        </is>
+      </c>
+      <c r="D138" s="12" t="inlineStr">
+        <is>
+          <t>Correction</t>
+        </is>
+      </c>
+      <c r="E138" s="12" t="inlineStr">
+        <is>
+          <t>data_correction</t>
+        </is>
+      </c>
+      <c r="F138" s="12" t="inlineStr">
+        <is>
+          <t>Schedule text incompletely seeded (omitted at the original seeding session)</t>
+        </is>
+      </c>
+      <c r="G138" s="12" t="inlineStr">
+        <is>
+          <t>Restored verbatim from the official Rules PDF</t>
+        </is>
+      </c>
+      <c r="H138" s="12" t="inlineStr">
+        <is>
+          <t>DPDP Rules, 2025 (G.S.R. 846(E))</t>
+        </is>
+      </c>
+      <c r="I138" s="12" t="inlineStr">
+        <is>
+          <t>https://www.meity.gov.in/static/uploads/2025/11/53450e6e5dc0bfa85ebd78686cadad39.pdf</t>
+        </is>
+      </c>
+      <c r="J138" s="12" t="inlineStr">
+        <is>
+          <t>manual:rules-schedule-restoration-2026-09-23 (code-extracted, no model-written text)</t>
+        </is>
+      </c>
+      <c r="K138" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L138" s="12" t="inlineStr">
+        <is>
+          <t>Pending Review</t>
+        </is>
+      </c>
+      <c r="M138" s="12" t="n"/>
+      <c r="N138" s="12" t="n"/>
+      <c r="O138" s="12" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P138" s="12" t="inlineStr">
+        <is>
+          <t>Data-quality fix (not a regulatory change): restored text left out of DPDPR-SCH3 at seeding. See scripts/restore_rules_schedule_gaps_2026-09-23.py.</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="12" t="inlineStr">
+        <is>
+          <t>CHG-0091</t>
+        </is>
+      </c>
+      <c r="B139" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-23T12:11:00.345078+00:00</t>
+        </is>
+      </c>
+      <c r="C139" s="12" t="inlineStr">
+        <is>
+          <t>DPDPR-SCH4</t>
+        </is>
+      </c>
+      <c r="D139" s="12" t="inlineStr">
+        <is>
+          <t>Correction</t>
+        </is>
+      </c>
+      <c r="E139" s="12" t="inlineStr">
+        <is>
+          <t>data_correction</t>
+        </is>
+      </c>
+      <c r="F139" s="12" t="inlineStr">
+        <is>
+          <t>Schedule text incompletely seeded (omitted at the original seeding session)</t>
+        </is>
+      </c>
+      <c r="G139" s="12" t="inlineStr">
+        <is>
+          <t>Restored verbatim from the official Rules PDF</t>
+        </is>
+      </c>
+      <c r="H139" s="12" t="inlineStr">
+        <is>
+          <t>DPDP Rules, 2025 (G.S.R. 846(E))</t>
+        </is>
+      </c>
+      <c r="I139" s="12" t="inlineStr">
+        <is>
+          <t>https://www.meity.gov.in/static/uploads/2025/11/53450e6e5dc0bfa85ebd78686cadad39.pdf</t>
+        </is>
+      </c>
+      <c r="J139" s="12" t="inlineStr">
+        <is>
+          <t>manual:rules-schedule-restoration-2026-09-23 (code-extracted, no model-written text)</t>
+        </is>
+      </c>
+      <c r="K139" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L139" s="12" t="inlineStr">
+        <is>
+          <t>Pending Review</t>
+        </is>
+      </c>
+      <c r="M139" s="12" t="n"/>
+      <c r="N139" s="12" t="n"/>
+      <c r="O139" s="12" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P139" s="12" t="inlineStr">
+        <is>
+          <t>Data-quality fix (not a regulatory change): restored text left out of DPDPR-SCH4 at seeding. See scripts/restore_rules_schedule_gaps_2026-09-23.py.</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="12" t="inlineStr">
+        <is>
+          <t>CHG-0092</t>
+        </is>
+      </c>
+      <c r="B140" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-23T12:11:00.345078+00:00</t>
+        </is>
+      </c>
+      <c r="C140" s="12" t="inlineStr">
+        <is>
+          <t>DPDPR-SCH5</t>
+        </is>
+      </c>
+      <c r="D140" s="12" t="inlineStr">
+        <is>
+          <t>Correction</t>
+        </is>
+      </c>
+      <c r="E140" s="12" t="inlineStr">
+        <is>
+          <t>data_correction</t>
+        </is>
+      </c>
+      <c r="F140" s="12" t="inlineStr">
+        <is>
+          <t>Schedule text incompletely seeded (omitted at the original seeding session)</t>
+        </is>
+      </c>
+      <c r="G140" s="12" t="inlineStr">
+        <is>
+          <t>Restored verbatim from the official Rules PDF</t>
+        </is>
+      </c>
+      <c r="H140" s="12" t="inlineStr">
+        <is>
+          <t>DPDP Rules, 2025 (G.S.R. 846(E))</t>
+        </is>
+      </c>
+      <c r="I140" s="12" t="inlineStr">
+        <is>
+          <t>https://www.meity.gov.in/static/uploads/2025/11/53450e6e5dc0bfa85ebd78686cadad39.pdf</t>
+        </is>
+      </c>
+      <c r="J140" s="12" t="inlineStr">
+        <is>
+          <t>manual:rules-schedule-restoration-2026-09-23 (code-extracted, no model-written text)</t>
+        </is>
+      </c>
+      <c r="K140" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L140" s="12" t="inlineStr">
+        <is>
+          <t>Pending Review</t>
+        </is>
+      </c>
+      <c r="M140" s="12" t="n"/>
+      <c r="N140" s="12" t="n"/>
+      <c r="O140" s="12" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P140" s="12" t="inlineStr">
+        <is>
+          <t>Data-quality fix (not a regulatory change): restored text left out of DPDPR-SCH5 at seeding. See scripts/restore_rules_schedule_gaps_2026-09-23.py.</t>
         </is>
       </c>
     </row>

--- a/data/DPDP_Rules_Tracker.xlsx
+++ b/data/DPDP_Rules_Tracker.xlsx
@@ -2011,7 +2011,7 @@
       </c>
       <c r="E14" s="12" t="inlineStr">
         <is>
-          <t>Every Consent Manager must be registered with the Board, subject to prescribed technical, operational, and financial conditions. (This sub-clause commences a year after the rest of Section 6, alongside Rule 4's registration process.)</t>
+          <t>Every Consent Manager must be registered with the Board, subject to prescribed technical, operational, financial and other conditions. (This sub-section commences one year after publication of G.S.R. 843(E) — six months BEFORE the rest of Section 6 — alongside Rule 4's registration process.)</t>
         </is>
       </c>
       <c r="F14" s="13" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>Exempts specified classes of Data Fiduciary (healthcare providers, educational institutions, crèches, child transport providers — Fourth Schedule Part A) and specified purposes (Part B, e.g. safety tracking, email accounts) from the Act's general prohibition on tracking/behavioural monitoring/targeted ads directed at children.</t>
+          <t>Exempts specified classes of Data Fiduciary (healthcare providers, educational institutions, crèches, child transport providers — Fourth Schedule Part A) and specified purposes (Part B, e.g. safety tracking, email accounts) from BOTH the verifiable parental consent requirement (s.9(1)) and the bar on tracking/behavioural monitoring/targeted ads directed at children (s.9(3)), subject to the Schedule's conditions.</t>
         </is>
       </c>
       <c r="F27" s="13" t="inlineStr">
@@ -3167,7 +3167,7 @@
       </c>
       <c r="J27" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="K27" s="12" t="inlineStr">
@@ -5847,7 +5847,7 @@
       </c>
       <c r="E58" s="12" t="inlineStr">
         <is>
-          <t>Gives the Board the power to inquire into, and penalise, a breach of Consent Manager registration conditions. (Commences a year after the rest of Section 27, alongside Section 6(9)'s Consent Manager registration requirement.)</t>
+          <t>Gives the Board the power to inquire into, and penalise, a breach of Consent Manager registration conditions. (Commences one year after publication of G.S.R. 843(E) — six months BEFORE the rest of Section 27 — alongside Section 6(9)'s Consent Manager registration requirement.)</t>
         </is>
       </c>
       <c r="F58" s="13" t="inlineStr">
@@ -7931,7 +7931,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P140"/>
+  <dimension ref="A1:P143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -17631,6 +17631,210 @@
       <c r="P140" s="12" t="inlineStr">
         <is>
           <t>Data-quality fix (not a regulatory change): restored text left out of DPDPR-SCH5 at seeding. See scripts/restore_rules_schedule_gaps_2026-09-23.py.</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="12" t="inlineStr">
+        <is>
+          <t>CHG-0093</t>
+        </is>
+      </c>
+      <c r="B141" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-23T12:13:05.627930+00:00</t>
+        </is>
+      </c>
+      <c r="C141" s="12" t="inlineStr">
+        <is>
+          <t>DPDPA-S6.9</t>
+        </is>
+      </c>
+      <c r="D141" s="12" t="inlineStr">
+        <is>
+          <t>Correction</t>
+        </is>
+      </c>
+      <c r="E141" s="12" t="inlineStr">
+        <is>
+          <t>data_correction</t>
+        </is>
+      </c>
+      <c r="F141" s="12" t="inlineStr">
+        <is>
+          <t>Every Consent Manager must be registered with the Board, subject to prescribed technical, operational, and financial conditions. (This sub-clause commences a year after the rest of Section 6, alongside Rule 4's registration process.)</t>
+        </is>
+      </c>
+      <c r="G141" s="12" t="inlineStr">
+        <is>
+          <t>Every Consent Manager must be registered with the Board, subject to prescribed technical, operational, financial and other conditions. (This sub-section commences one year after publication of G.S.R. 843(E) — six months BEFORE the rest of Section 6 — alongside Rule 4's registration process.)</t>
+        </is>
+      </c>
+      <c r="H141" s="12" t="inlineStr">
+        <is>
+          <t>Audit 2026-09-23</t>
+        </is>
+      </c>
+      <c r="I141" s="12" t="n"/>
+      <c r="J141" s="12" t="inlineStr">
+        <is>
+          <t>manual:audit-2026-09-23-summary-fix</t>
+        </is>
+      </c>
+      <c r="K141" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L141" s="12" t="inlineStr">
+        <is>
+          <t>Pending Review</t>
+        </is>
+      </c>
+      <c r="M141" s="12" t="n"/>
+      <c r="N141" s="12" t="n"/>
+      <c r="O141" s="12" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P141" s="12" t="inlineStr">
+        <is>
+          <t>Summary-only data-quality fix (not a regulatory change; never highlighted). Basis: G.S.R. 843(E) clause (b) (one year) vs clause (c) (eighteen months: 'sub-sections (1) to (8) and (10) of section 6')</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="12" t="inlineStr">
+        <is>
+          <t>CHG-0094</t>
+        </is>
+      </c>
+      <c r="B142" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-23T12:13:05.627930+00:00</t>
+        </is>
+      </c>
+      <c r="C142" s="12" t="inlineStr">
+        <is>
+          <t>DPDPA-S27.1d</t>
+        </is>
+      </c>
+      <c r="D142" s="12" t="inlineStr">
+        <is>
+          <t>Correction</t>
+        </is>
+      </c>
+      <c r="E142" s="12" t="inlineStr">
+        <is>
+          <t>data_correction</t>
+        </is>
+      </c>
+      <c r="F142" s="12" t="inlineStr">
+        <is>
+          <t>Gives the Board the power to inquire into, and penalise, a breach of Consent Manager registration conditions. (Commences a year after the rest of Section 27, alongside Section 6(9)'s Consent Manager registration requirement.)</t>
+        </is>
+      </c>
+      <c r="G142" s="12" t="inlineStr">
+        <is>
+          <t>Gives the Board the power to inquire into, and penalise, a breach of Consent Manager registration conditions. (Commences one year after publication of G.S.R. 843(E) — six months BEFORE the rest of Section 27 — alongside Section 6(9)'s Consent Manager registration requirement.)</t>
+        </is>
+      </c>
+      <c r="H142" s="12" t="inlineStr">
+        <is>
+          <t>Audit 2026-09-23</t>
+        </is>
+      </c>
+      <c r="I142" s="12" t="n"/>
+      <c r="J142" s="12" t="inlineStr">
+        <is>
+          <t>manual:audit-2026-09-23-summary-fix</t>
+        </is>
+      </c>
+      <c r="K142" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L142" s="12" t="inlineStr">
+        <is>
+          <t>Pending Review</t>
+        </is>
+      </c>
+      <c r="M142" s="12" t="n"/>
+      <c r="N142" s="12" t="n"/>
+      <c r="O142" s="12" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P142" s="12" t="inlineStr">
+        <is>
+          <t>Summary-only data-quality fix (not a regulatory change; never highlighted). Basis: G.S.R. 843(E) clause (b) vs clause (c) ('section 27 except clause (d) of sub-section (1)')</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="12" t="inlineStr">
+        <is>
+          <t>CHG-0095</t>
+        </is>
+      </c>
+      <c r="B143" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-23T12:13:05.627930+00:00</t>
+        </is>
+      </c>
+      <c r="C143" s="12" t="inlineStr">
+        <is>
+          <t>DPDPR-R12</t>
+        </is>
+      </c>
+      <c r="D143" s="12" t="inlineStr">
+        <is>
+          <t>Correction</t>
+        </is>
+      </c>
+      <c r="E143" s="12" t="inlineStr">
+        <is>
+          <t>data_correction</t>
+        </is>
+      </c>
+      <c r="F143" s="12" t="inlineStr">
+        <is>
+          <t>Exempts specified classes of Data Fiduciary (healthcare providers, educational institutions, crèches, child transport providers — Fourth Schedule Part A) and specified purposes (Part B, e.g. safety tracking, email accounts) from the Act's general prohibition on tracking/behavioural monitoring/targeted ads directed at children.</t>
+        </is>
+      </c>
+      <c r="G143" s="12" t="inlineStr">
+        <is>
+          <t>Exempts specified classes of Data Fiduciary (healthcare providers, educational institutions, crèches, child transport providers — Fourth Schedule Part A) and specified purposes (Part B, e.g. safety tracking, email accounts) from BOTH the verifiable parental consent requirement (s.9(1)) and the bar on tracking/behavioural monitoring/targeted ads directed at children (s.9(3)), subject to the Schedule's conditions.</t>
+        </is>
+      </c>
+      <c r="H143" s="12" t="inlineStr">
+        <is>
+          <t>Audit 2026-09-23</t>
+        </is>
+      </c>
+      <c r="I143" s="12" t="n"/>
+      <c r="J143" s="12" t="inlineStr">
+        <is>
+          <t>manual:audit-2026-09-23-summary-fix</t>
+        </is>
+      </c>
+      <c r="K143" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L143" s="12" t="inlineStr">
+        <is>
+          <t>Pending Review</t>
+        </is>
+      </c>
+      <c r="M143" s="12" t="n"/>
+      <c r="N143" s="12" t="n"/>
+      <c r="O143" s="12" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P143" s="12" t="inlineStr">
+        <is>
+          <t>Summary-only data-quality fix (not a regulatory change; never highlighted). Basis: Rule 12(1),(2): 'The provisions of sub-sections (1) and (3) of section 9 of the Act shall not be applicable'</t>
         </is>
       </c>
     </row>

--- a/data/DPDP_Rules_Tracker.xlsx
+++ b/data/DPDP_Rules_Tracker.xlsx
@@ -17863,7 +17863,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -17927,27 +17927,27 @@
     <row r="2">
       <c r="A2" s="12" t="inlineStr">
         <is>
-          <t>SRC-0002</t>
+          <t>SRC-0003</t>
         </is>
       </c>
       <c r="B2" s="12" t="inlineStr">
         <is>
-          <t>MeitY</t>
+          <t>eGazette</t>
         </is>
       </c>
       <c r="C2" s="12" t="inlineStr">
         <is>
-          <t>Digital Personal Data Protection Act, 2023 (Act No. 22 of 2023)</t>
+          <t>Gazette Notification G.S.R. 843(E), 13 Nov 2025 (Act commencement schedule)</t>
         </is>
       </c>
       <c r="D2" s="12" t="inlineStr">
         <is>
-          <t>https://www.meity.gov.in/static/uploads/2024/06/2bf1f0e9f04e6fb4f8fef35e82c42aa5.pdf</t>
+          <t>https://www.meity.gov.in/static/uploads/2025/11/c56ceae6c383460ca69577428d36828b.pdf</t>
         </is>
       </c>
       <c r="E2" s="12" t="inlineStr">
         <is>
-          <t>2023-08-11</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="F2" s="12" t="inlineStr">
@@ -17974,69 +17974,65 @@
     <row r="3">
       <c r="A3" s="12" t="inlineStr">
         <is>
-          <t>SRC-0003</t>
+          <t>SRC-0001</t>
         </is>
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>eGazette</t>
+          <t>MeitY</t>
         </is>
       </c>
       <c r="C3" s="12" t="inlineStr">
         <is>
-          <t>Gazette Notification G.S.R. 843(E), 13 Nov 2025 (Act commencement schedule)</t>
+          <t>DPDP Rules, 2025 — MeitY PDF (G.S.R. 846(E))</t>
         </is>
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>https://www.meity.gov.in/static/uploads/2025/11/c56ceae6c383460ca69577428d36828b.pdf</t>
-        </is>
-      </c>
-      <c r="E3" s="12" t="inlineStr">
-        <is>
-          <t>2025-11-13</t>
-        </is>
-      </c>
+          <t>https://www.meity.gov.in/static/uploads/2025/11/53450e6e5dc0bfa85ebd78686cadad39.pdf</t>
+        </is>
+      </c>
+      <c r="E3" s="12" t="n"/>
       <c r="F3" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G3" s="12" t="inlineStr">
         <is>
-          <t>manual-seed-not-hashed</t>
+          <t>76094c7228c8dbff357281552fa2b052fe363303eb8b2c33ee5361d38883070d</t>
         </is>
       </c>
       <c r="H3" s="12" t="inlineStr">
         <is>
-          <t>Processed</t>
+          <t>No Change Detected</t>
         </is>
       </c>
       <c r="I3" s="12" t="inlineStr">
         <is>
-          <t>CHG-A0001,CHG-A0002,CHG-A0003,CHG-A0004,CHG-A0005,CHG-A0006,CHG-A0007,CHG-A0008,CHG-A0009,CHG-A0010,CHG-A0011,CHG-A0012,CHG-A0013,CHG-A0014,CHG-A0015,CHG-A0016,CHG-A0017,CHG-A0018,CHG-A0019,CHG-A0020,CHG-A0021,CHG-A0022,CHG-A0023,CHG-A0024,CHG-A0025,CHG-A0026,CHG-A0027,CHG-A0028,CHG-A0029,CHG-A0030,CHG-A0031,CHG-A0032,CHG-A0033,CHG-A0034,CHG-A0035,CHG-A0036,CHG-A0037,CHG-A0038,CHG-A0039,CHG-A0040,CHG-A0041,CHG-A0042,CHG-A0043,CHG-A0044,CHG-A0045,CHG-A0046,CHG-A0047,CHG-A0048</t>
+          <t>CHG-0002,CHG-0003,CHG-0004,CHG-0005,CHG-0006,CHG-0007,CHG-0008,CHG-0009,CHG-0010,CHG-0011,CHG-0012,CHG-0013,CHG-0014,CHG-0015,CHG-0016,CHG-0017,CHG-0018,CHG-0019,CHG-0020,CHG-0021,CHG-0022,CHG-0023,CHG-0024,CHG-0025,CHG-0026,CHG-0027,CHG-0028,CHG-0029,CHG-0030,CHG-0031,CHG-0032</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="12" t="inlineStr">
         <is>
-          <t>SRC-0001</t>
+          <t>SRC-0004</t>
         </is>
       </c>
       <c r="B4" s="12" t="inlineStr">
         <is>
-          <t>MeitY</t>
+          <t>PIB</t>
         </is>
       </c>
       <c r="C4" s="12" t="inlineStr">
         <is>
-          <t>DPDP Rules, 2025 — MeitY PDF (G.S.R. 846(E))</t>
+          <t>PIB — All Press Releases (English)</t>
         </is>
       </c>
       <c r="D4" s="12" t="inlineStr">
         <is>
-          <t>https://www.meity.gov.in/static/uploads/2025/11/53450e6e5dc0bfa85ebd78686cadad39.pdf</t>
+          <t>https://www.pib.gov.in/allRel.aspx</t>
         </is>
       </c>
       <c r="E4" s="12" t="n"/>
@@ -18047,7 +18043,7 @@
       </c>
       <c r="G4" s="12" t="inlineStr">
         <is>
-          <t>76094c7228c8dbff357281552fa2b052fe363303eb8b2c33ee5361d38883070d</t>
+          <t>d38842055f43a4f6ee39929156a2c93772a0b128ba3ab14f887a64fcf1c77e89</t>
         </is>
       </c>
       <c r="H4" s="12" t="inlineStr">
@@ -18055,31 +18051,27 @@
           <t>No Change Detected</t>
         </is>
       </c>
-      <c r="I4" s="12" t="inlineStr">
-        <is>
-          <t>CHG-0002,CHG-0003,CHG-0004,CHG-0005,CHG-0006,CHG-0007,CHG-0008,CHG-0009,CHG-0010,CHG-0011,CHG-0012,CHG-0013,CHG-0014,CHG-0015,CHG-0016,CHG-0017,CHG-0018,CHG-0019,CHG-0020,CHG-0021,CHG-0022,CHG-0023,CHG-0024,CHG-0025,CHG-0026,CHG-0027,CHG-0028,CHG-0029,CHG-0030,CHG-0031,CHG-0032</t>
-        </is>
-      </c>
+      <c r="I4" s="12" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="12" t="inlineStr">
         <is>
-          <t>SRC-0004</t>
+          <t>SRC-0005</t>
         </is>
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>PIB</t>
+          <t>eGazette</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>PIB — All Press Releases (English)</t>
+          <t>eGazette — Home (best-effort; no stable search endpoint confirmed)</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/allRel.aspx</t>
+          <t>https://egazette.gov.in/</t>
         </is>
       </c>
       <c r="E5" s="12" t="n"/>
@@ -18090,7 +18082,7 @@
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
-          <t>d38842055f43a4f6ee39929156a2c93772a0b128ba3ab14f887a64fcf1c77e89</t>
+          <t>5804450f38f800c83d0849fd9ad445e103b5d70cd17603a0519ecf3b14ddc5d3</t>
         </is>
       </c>
       <c r="H5" s="12" t="inlineStr">
@@ -18103,22 +18095,22 @@
     <row r="6">
       <c r="A6" s="12" t="inlineStr">
         <is>
-          <t>SRC-0005</t>
+          <t>SRC-0002</t>
         </is>
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>eGazette</t>
+          <t>MeitY</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>eGazette — Home (best-effort; no stable search endpoint confirmed)</t>
+          <t>DPDP Act, 2023 — MeitY PDF</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>https://egazette.gov.in/</t>
+          <t>https://www.meity.gov.in/static/uploads/2024/06/2bf1f0e9f04e6fb4f8fef35e82c42aa5.pdf</t>
         </is>
       </c>
       <c r="E6" s="12" t="n"/>
@@ -18129,7 +18121,7 @@
       </c>
       <c r="G6" s="12" t="inlineStr">
         <is>
-          <t>ca96805449aa0e1eb65ff8f302650b129a742ad9902372ad6409b3dd18248582</t>
+          <t>f15bda1ff8065c68f8e1cc57c50616264afeb49d72cfc48d1e92a2a3c473c1d2</t>
         </is>
       </c>
       <c r="H6" s="12" t="inlineStr">
@@ -18137,7 +18129,11 @@
           <t>No Change Detected</t>
         </is>
       </c>
-      <c r="I6" s="12" t="n"/>
+      <c r="I6" s="12" t="inlineStr">
+        <is>
+          <t>CHG-A0001,CHG-A0002,CHG-A0003,CHG-A0004,CHG-A0005,CHG-A0006,CHG-A0007,CHG-A0008,CHG-A0009,CHG-A0010,CHG-A0011,CHG-A0012,CHG-A0013,CHG-A0014,CHG-A0015,CHG-A0016,CHG-A0017,CHG-A0018,CHG-A0019,CHG-A0020,CHG-A0021,CHG-A0022,CHG-A0023,CHG-A0024,CHG-A0025,CHG-A0026,CHG-A0027,CHG-A0028,CHG-A0029,CHG-A0030,CHG-A0031,CHG-A0032,CHG-A0033,CHG-A0034,CHG-A0035,CHG-A0036,CHG-A0037,CHG-A0038,CHG-A0039,CHG-A0040,CHG-A0041,CHG-A0042,CHG-A0043,CHG-A0044,CHG-A0045,CHG-A0046,CHG-A0047,CHG-A0048</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
@@ -18185,6 +18181,45 @@
           <t>CHG-0086,CHG-0087,CHG-0088</t>
         </is>
       </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>SRC-0007</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>PIB</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>PIB — All Press Releases RSS (English, national)</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>https://www.pib.gov.in/RssMain.aspx?ModId=6&amp;Mid=0&amp;reg=3&amp;lang=1</t>
+        </is>
+      </c>
+      <c r="E8" s="12" t="n"/>
+      <c r="F8" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G8" s="12" t="inlineStr">
+        <is>
+          <t>303646cc4c4bce1f12f990b273eedffaa3f1ba4df657ca84d5418879e39c79ef</t>
+        </is>
+      </c>
+      <c r="H8" s="12" t="inlineStr">
+        <is>
+          <t>No Change Detected</t>
+        </is>
+      </c>
+      <c r="I8" s="12" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="2">

--- a/data/DPDP_Rules_Tracker.xlsx
+++ b/data/DPDP_Rules_Tracker.xlsx
@@ -1006,11 +1006,19 @@
       </c>
       <c r="N2" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="O2" s="12" t="n"/>
-      <c r="P2" s="12" t="n"/>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="O2" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="P2" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="Q2" s="12" t="inlineStr">
         <is>
           <t>CHG-A0001</t>
@@ -1093,11 +1101,19 @@
       </c>
       <c r="N3" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="O3" s="12" t="n"/>
-      <c r="P3" s="12" t="n"/>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="O3" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="P3" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="Q3" s="12" t="inlineStr">
         <is>
           <t>CHG-0086</t>
@@ -1184,11 +1200,19 @@
       </c>
       <c r="N4" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="O4" s="12" t="n"/>
-      <c r="P4" s="12" t="n"/>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="O4" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="P4" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="Q4" s="12" t="inlineStr">
         <is>
           <t>CHG-A0002</t>
@@ -1271,11 +1295,19 @@
       </c>
       <c r="N5" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="O5" s="12" t="n"/>
-      <c r="P5" s="12" t="n"/>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="O5" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="P5" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="Q5" s="12" t="inlineStr">
         <is>
           <t>CHG-0003</t>
@@ -1358,11 +1390,19 @@
       </c>
       <c r="N6" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="O6" s="12" t="n"/>
-      <c r="P6" s="12" t="n"/>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="O6" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="P6" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="Q6" s="12" t="inlineStr">
         <is>
           <t>CHG-A0003</t>
@@ -1445,11 +1485,19 @@
       </c>
       <c r="N7" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="O7" s="12" t="n"/>
-      <c r="P7" s="12" t="n"/>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="O7" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="P7" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="Q7" s="12" t="inlineStr">
         <is>
           <t>CHG-0004</t>
@@ -1532,11 +1580,19 @@
       </c>
       <c r="N8" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="O8" s="12" t="n"/>
-      <c r="P8" s="12" t="n"/>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="O8" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="P8" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="Q8" s="12" t="inlineStr">
         <is>
           <t>CHG-A0004</t>
@@ -1619,11 +1675,19 @@
       </c>
       <c r="N9" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="O9" s="12" t="n"/>
-      <c r="P9" s="12" t="n"/>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="O9" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="P9" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="Q9" s="12" t="inlineStr">
         <is>
           <t>CHG-0005</t>
@@ -1706,11 +1770,19 @@
       </c>
       <c r="N10" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="O10" s="12" t="n"/>
-      <c r="P10" s="12" t="n"/>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="O10" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="P10" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="Q10" s="12" t="inlineStr">
         <is>
           <t>CHG-A0005</t>
@@ -1793,11 +1865,19 @@
       </c>
       <c r="N11" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="O11" s="12" t="n"/>
-      <c r="P11" s="12" t="n"/>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="O11" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="P11" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="Q11" s="12" t="inlineStr">
         <is>
           <t>CHG-0006</t>
@@ -1880,11 +1960,19 @@
       </c>
       <c r="N12" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="O12" s="12" t="n"/>
-      <c r="P12" s="12" t="n"/>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="O12" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="P12" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="Q12" s="12" t="inlineStr">
         <is>
           <t>CHG-A0006</t>
@@ -1967,11 +2055,19 @@
       </c>
       <c r="N13" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="O13" s="12" t="n"/>
-      <c r="P13" s="12" t="n"/>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="O13" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="P13" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="Q13" s="12" t="inlineStr">
         <is>
           <t>CHG-0007</t>
@@ -2054,11 +2150,19 @@
       </c>
       <c r="N14" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="O14" s="12" t="n"/>
-      <c r="P14" s="12" t="n"/>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="O14" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="P14" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="Q14" s="12" t="inlineStr">
         <is>
           <t>CHG-A0007</t>
@@ -2141,11 +2245,19 @@
       </c>
       <c r="N15" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="O15" s="12" t="n"/>
-      <c r="P15" s="12" t="n"/>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="O15" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="P15" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="Q15" s="12" t="inlineStr">
         <is>
           <t>CHG-0008</t>
@@ -2228,11 +2340,19 @@
       </c>
       <c r="N16" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="O16" s="12" t="n"/>
-      <c r="P16" s="12" t="n"/>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="O16" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="P16" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="Q16" s="12" t="inlineStr">
         <is>
           <t>CHG-A0008</t>
@@ -2315,11 +2435,19 @@
       </c>
       <c r="N17" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="O17" s="12" t="n"/>
-      <c r="P17" s="12" t="n"/>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="O17" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="P17" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="Q17" s="12" t="inlineStr">
         <is>
           <t>CHG-0009</t>
@@ -2402,11 +2530,19 @@
       </c>
       <c r="N18" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="O18" s="12" t="n"/>
-      <c r="P18" s="12" t="n"/>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="O18" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="P18" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="Q18" s="12" t="inlineStr">
         <is>
           <t>CHG-A0009</t>
@@ -2489,11 +2625,19 @@
       </c>
       <c r="N19" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="O19" s="12" t="n"/>
-      <c r="P19" s="12" t="n"/>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="O19" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="P19" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="Q19" s="12" t="inlineStr">
         <is>
           <t>CHG-0010</t>
@@ -2576,11 +2720,19 @@
       </c>
       <c r="N20" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="O20" s="12" t="n"/>
-      <c r="P20" s="12" t="n"/>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="O20" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="P20" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="Q20" s="12" t="inlineStr">
         <is>
           <t>CHG-A0010</t>
@@ -2663,11 +2815,19 @@
       </c>
       <c r="N21" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="O21" s="12" t="n"/>
-      <c r="P21" s="12" t="n"/>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="O21" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="P21" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="Q21" s="12" t="inlineStr">
         <is>
           <t>CHG-0011</t>
@@ -2750,11 +2910,19 @@
       </c>
       <c r="N22" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="O22" s="12" t="n"/>
-      <c r="P22" s="12" t="n"/>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="O22" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="P22" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="Q22" s="12" t="inlineStr">
         <is>
           <t>CHG-A0011</t>
@@ -2837,11 +3005,19 @@
       </c>
       <c r="N23" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="O23" s="12" t="n"/>
-      <c r="P23" s="12" t="n"/>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="O23" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="P23" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="Q23" s="12" t="inlineStr">
         <is>
           <t>CHG-0012</t>
@@ -2924,11 +3100,19 @@
       </c>
       <c r="N24" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="O24" s="12" t="n"/>
-      <c r="P24" s="12" t="n"/>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="O24" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="P24" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="Q24" s="12" t="inlineStr">
         <is>
           <t>CHG-A0012</t>
@@ -3011,11 +3195,19 @@
       </c>
       <c r="N25" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="O25" s="12" t="n"/>
-      <c r="P25" s="12" t="n"/>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="O25" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="P25" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="Q25" s="12" t="inlineStr">
         <is>
           <t>CHG-0013</t>
@@ -3098,11 +3290,19 @@
       </c>
       <c r="N26" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="O26" s="12" t="n"/>
-      <c r="P26" s="12" t="n"/>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="O26" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="P26" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="Q26" s="12" t="inlineStr">
         <is>
           <t>CHG-A0013</t>
@@ -3185,11 +3385,19 @@
       </c>
       <c r="N27" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="O27" s="12" t="n"/>
-      <c r="P27" s="12" t="n"/>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="O27" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="P27" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="Q27" s="12" t="inlineStr">
         <is>
           <t>CHG-0014</t>
@@ -3272,11 +3480,19 @@
       </c>
       <c r="N28" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="O28" s="12" t="n"/>
-      <c r="P28" s="12" t="n"/>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="O28" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="P28" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="Q28" s="12" t="inlineStr">
         <is>
           <t>CHG-A0014</t>
@@ -3359,11 +3575,19 @@
       </c>
       <c r="N29" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="O29" s="12" t="n"/>
-      <c r="P29" s="12" t="n"/>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="O29" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="P29" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="Q29" s="12" t="inlineStr">
         <is>
           <t>CHG-0087</t>
@@ -3450,11 +3674,19 @@
       </c>
       <c r="N30" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="O30" s="12" t="n"/>
-      <c r="P30" s="12" t="n"/>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="O30" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="P30" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="Q30" s="12" t="inlineStr">
         <is>
           <t>CHG-A0015</t>
@@ -3537,11 +3769,19 @@
       </c>
       <c r="N31" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="O31" s="12" t="n"/>
-      <c r="P31" s="12" t="n"/>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="O31" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="P31" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="Q31" s="12" t="inlineStr">
         <is>
           <t>CHG-0016</t>
@@ -3624,11 +3864,19 @@
       </c>
       <c r="N32" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="O32" s="12" t="n"/>
-      <c r="P32" s="12" t="n"/>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="O32" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="P32" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="Q32" s="12" t="inlineStr">
         <is>
           <t>CHG-A0016</t>
@@ -3711,11 +3959,19 @@
       </c>
       <c r="N33" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="O33" s="12" t="n"/>
-      <c r="P33" s="12" t="n"/>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="O33" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="P33" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="Q33" s="12" t="inlineStr">
         <is>
           <t>CHG-0017</t>
@@ -3798,11 +4054,19 @@
       </c>
       <c r="N34" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="O34" s="12" t="n"/>
-      <c r="P34" s="12" t="n"/>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="O34" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="P34" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="Q34" s="12" t="inlineStr">
         <is>
           <t>CHG-A0017</t>
@@ -3885,11 +4149,19 @@
       </c>
       <c r="N35" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="O35" s="12" t="n"/>
-      <c r="P35" s="12" t="n"/>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="O35" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="P35" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="Q35" s="12" t="inlineStr">
         <is>
           <t>CHG-0018</t>
@@ -3972,11 +4244,19 @@
       </c>
       <c r="N36" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="O36" s="12" t="n"/>
-      <c r="P36" s="12" t="n"/>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="O36" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="P36" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="Q36" s="12" t="inlineStr">
         <is>
           <t>CHG-A0018</t>
@@ -4059,11 +4339,19 @@
       </c>
       <c r="N37" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="O37" s="12" t="n"/>
-      <c r="P37" s="12" t="n"/>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="O37" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="P37" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="Q37" s="12" t="inlineStr">
         <is>
           <t>CHG-0019</t>
@@ -4146,11 +4434,19 @@
       </c>
       <c r="N38" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="O38" s="12" t="n"/>
-      <c r="P38" s="12" t="n"/>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="O38" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="P38" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="Q38" s="12" t="inlineStr">
         <is>
           <t>CHG-A0019</t>
@@ -4233,11 +4529,19 @@
       </c>
       <c r="N39" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="O39" s="12" t="n"/>
-      <c r="P39" s="12" t="n"/>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="O39" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="P39" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="Q39" s="12" t="inlineStr">
         <is>
           <t>CHG-0020</t>
@@ -4320,11 +4624,19 @@
       </c>
       <c r="N40" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="O40" s="12" t="n"/>
-      <c r="P40" s="12" t="n"/>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="O40" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="P40" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="Q40" s="12" t="inlineStr">
         <is>
           <t>CHG-A0020</t>
@@ -4407,11 +4719,19 @@
       </c>
       <c r="N41" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="O41" s="12" t="n"/>
-      <c r="P41" s="12" t="n"/>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="O41" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="P41" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="Q41" s="12" t="inlineStr">
         <is>
           <t>CHG-0021</t>
@@ -4494,11 +4814,19 @@
       </c>
       <c r="N42" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="O42" s="12" t="n"/>
-      <c r="P42" s="12" t="n"/>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="O42" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="P42" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="Q42" s="12" t="inlineStr">
         <is>
           <t>CHG-A0021</t>
@@ -4581,11 +4909,19 @@
       </c>
       <c r="N43" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="O43" s="12" t="n"/>
-      <c r="P43" s="12" t="n"/>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="O43" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="P43" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="Q43" s="12" t="inlineStr">
         <is>
           <t>CHG-0022</t>
@@ -4668,11 +5004,19 @@
       </c>
       <c r="N44" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="O44" s="12" t="n"/>
-      <c r="P44" s="12" t="n"/>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="O44" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="P44" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="Q44" s="12" t="inlineStr">
         <is>
           <t>CHG-A0022</t>
@@ -4755,11 +5099,19 @@
       </c>
       <c r="N45" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="O45" s="12" t="n"/>
-      <c r="P45" s="12" t="n"/>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="O45" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="P45" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="Q45" s="12" t="inlineStr">
         <is>
           <t>CHG-0023</t>
@@ -4842,11 +5194,19 @@
       </c>
       <c r="N46" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="O46" s="12" t="n"/>
-      <c r="P46" s="12" t="n"/>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="O46" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="P46" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="Q46" s="12" t="inlineStr">
         <is>
           <t>CHG-A0023</t>
@@ -4929,11 +5289,19 @@
       </c>
       <c r="N47" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="O47" s="12" t="n"/>
-      <c r="P47" s="12" t="n"/>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="O47" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="P47" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="Q47" s="12" t="inlineStr">
         <is>
           <t>CHG-0024</t>
@@ -5016,11 +5384,19 @@
       </c>
       <c r="N48" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="O48" s="12" t="n"/>
-      <c r="P48" s="12" t="n"/>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="O48" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="P48" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="Q48" s="12" t="inlineStr">
         <is>
           <t>CHG-A0024</t>
@@ -5103,11 +5479,19 @@
       </c>
       <c r="N49" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="O49" s="12" t="n"/>
-      <c r="P49" s="12" t="n"/>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="O49" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="P49" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="Q49" s="12" t="inlineStr">
         <is>
           <t>CHG-0088</t>
@@ -5194,11 +5578,19 @@
       </c>
       <c r="N50" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="O50" s="12" t="n"/>
-      <c r="P50" s="12" t="n"/>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="O50" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="P50" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="Q50" s="12" t="inlineStr">
         <is>
           <t>CHG-A0025</t>
@@ -5281,11 +5673,19 @@
       </c>
       <c r="N51" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="O51" s="12" t="n"/>
-      <c r="P51" s="12" t="n"/>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="O51" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="P51" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="Q51" s="12" t="inlineStr">
         <is>
           <t>CHG-0026</t>
@@ -5368,11 +5768,19 @@
       </c>
       <c r="N52" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="O52" s="12" t="n"/>
-      <c r="P52" s="12" t="n"/>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="O52" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="P52" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="Q52" s="12" t="inlineStr">
         <is>
           <t>CHG-A0026</t>
@@ -5455,11 +5863,19 @@
       </c>
       <c r="N53" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="O53" s="12" t="n"/>
-      <c r="P53" s="12" t="n"/>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="O53" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="P53" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="Q53" s="12" t="inlineStr">
         <is>
           <t>CHG-0027</t>
@@ -5542,11 +5958,19 @@
       </c>
       <c r="N54" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="O54" s="12" t="n"/>
-      <c r="P54" s="12" t="n"/>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="O54" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="P54" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="Q54" s="12" t="inlineStr">
         <is>
           <t>CHG-A0027</t>
@@ -5629,11 +6053,19 @@
       </c>
       <c r="N55" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="O55" s="12" t="n"/>
-      <c r="P55" s="12" t="n"/>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="O55" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="P55" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="Q55" s="12" t="inlineStr">
         <is>
           <t>CHG-0028</t>
@@ -5716,11 +6148,19 @@
       </c>
       <c r="N56" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="O56" s="12" t="n"/>
-      <c r="P56" s="12" t="n"/>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="O56" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="P56" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="Q56" s="12" t="inlineStr">
         <is>
           <t>CHG-A0028</t>
@@ -5803,11 +6243,19 @@
       </c>
       <c r="N57" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="O57" s="12" t="n"/>
-      <c r="P57" s="12" t="n"/>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="O57" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="P57" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="Q57" s="12" t="inlineStr">
         <is>
           <t>CHG-0029</t>
@@ -5890,11 +6338,19 @@
       </c>
       <c r="N58" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="O58" s="12" t="n"/>
-      <c r="P58" s="12" t="n"/>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="O58" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="P58" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="Q58" s="12" t="inlineStr">
         <is>
           <t>CHG-A0029</t>
@@ -5977,11 +6433,19 @@
       </c>
       <c r="N59" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="O59" s="12" t="n"/>
-      <c r="P59" s="12" t="n"/>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="O59" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="P59" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="Q59" s="12" t="inlineStr">
         <is>
           <t>CHG-0030</t>
@@ -6064,11 +6528,19 @@
       </c>
       <c r="N60" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="O60" s="12" t="n"/>
-      <c r="P60" s="12" t="n"/>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="O60" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="P60" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="Q60" s="12" t="inlineStr">
         <is>
           <t>CHG-A0030</t>
@@ -6151,11 +6623,19 @@
       </c>
       <c r="N61" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="O61" s="12" t="n"/>
-      <c r="P61" s="12" t="n"/>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="O61" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="P61" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="Q61" s="12" t="inlineStr">
         <is>
           <t>CHG-0031</t>
@@ -6238,11 +6718,19 @@
       </c>
       <c r="N62" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="O62" s="12" t="n"/>
-      <c r="P62" s="12" t="n"/>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="O62" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="P62" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="Q62" s="12" t="inlineStr">
         <is>
           <t>CHG-A0031</t>
@@ -6325,11 +6813,19 @@
       </c>
       <c r="N63" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="O63" s="12" t="n"/>
-      <c r="P63" s="12" t="n"/>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="O63" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="P63" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="Q63" s="12" t="inlineStr">
         <is>
           <t>CHG-0032</t>
@@ -6412,11 +6908,19 @@
       </c>
       <c r="N64" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="O64" s="12" t="n"/>
-      <c r="P64" s="12" t="n"/>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="O64" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="P64" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="Q64" s="12" t="inlineStr">
         <is>
           <t>CHG-A0032</t>
@@ -6499,11 +7003,19 @@
       </c>
       <c r="N65" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="O65" s="12" t="n"/>
-      <c r="P65" s="12" t="n"/>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="O65" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="P65" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="Q65" s="12" t="inlineStr">
         <is>
           <t>CHG-A0033</t>
@@ -6586,11 +7098,19 @@
       </c>
       <c r="N66" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="O66" s="12" t="n"/>
-      <c r="P66" s="12" t="n"/>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="O66" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="P66" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="Q66" s="12" t="inlineStr">
         <is>
           <t>CHG-A0034</t>
@@ -6673,11 +7193,19 @@
       </c>
       <c r="N67" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="O67" s="12" t="n"/>
-      <c r="P67" s="12" t="n"/>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="O67" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="P67" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="Q67" s="12" t="inlineStr">
         <is>
           <t>CHG-A0035</t>
@@ -6760,11 +7288,19 @@
       </c>
       <c r="N68" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="O68" s="12" t="n"/>
-      <c r="P68" s="12" t="n"/>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="O68" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="P68" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="Q68" s="12" t="inlineStr">
         <is>
           <t>CHG-A0036</t>
@@ -6847,11 +7383,19 @@
       </c>
       <c r="N69" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="O69" s="12" t="n"/>
-      <c r="P69" s="12" t="n"/>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="O69" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="P69" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="Q69" s="12" t="inlineStr">
         <is>
           <t>CHG-A0037</t>
@@ -6934,11 +7478,19 @@
       </c>
       <c r="N70" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="O70" s="12" t="n"/>
-      <c r="P70" s="12" t="n"/>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="O70" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="P70" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="Q70" s="12" t="inlineStr">
         <is>
           <t>CHG-A0038</t>
@@ -7021,11 +7573,19 @@
       </c>
       <c r="N71" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="O71" s="12" t="n"/>
-      <c r="P71" s="12" t="n"/>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="O71" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="P71" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="Q71" s="12" t="inlineStr">
         <is>
           <t>CHG-A0039</t>
@@ -7108,11 +7668,19 @@
       </c>
       <c r="N72" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="O72" s="12" t="n"/>
-      <c r="P72" s="12" t="n"/>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="O72" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="P72" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="Q72" s="12" t="inlineStr">
         <is>
           <t>CHG-A0040</t>
@@ -7195,11 +7763,19 @@
       </c>
       <c r="N73" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="O73" s="12" t="n"/>
-      <c r="P73" s="12" t="n"/>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="O73" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="P73" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="Q73" s="12" t="inlineStr">
         <is>
           <t>CHG-A0041</t>
@@ -7282,11 +7858,19 @@
       </c>
       <c r="N74" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="O74" s="12" t="n"/>
-      <c r="P74" s="12" t="n"/>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="O74" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="P74" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="Q74" s="12" t="inlineStr">
         <is>
           <t>CHG-A0042</t>
@@ -7369,11 +7953,19 @@
       </c>
       <c r="N75" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="O75" s="12" t="n"/>
-      <c r="P75" s="12" t="n"/>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="O75" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="P75" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="Q75" s="12" t="inlineStr">
         <is>
           <t>CHG-A0043</t>
@@ -7456,11 +8048,19 @@
       </c>
       <c r="N76" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="O76" s="12" t="n"/>
-      <c r="P76" s="12" t="n"/>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="O76" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="P76" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="Q76" s="12" t="inlineStr">
         <is>
           <t>CHG-A0044</t>
@@ -7543,11 +8143,19 @@
       </c>
       <c r="N77" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="O77" s="12" t="n"/>
-      <c r="P77" s="12" t="n"/>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="O77" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="P77" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="Q77" s="12" t="inlineStr">
         <is>
           <t>CHG-A0045</t>
@@ -7630,11 +8238,19 @@
       </c>
       <c r="N78" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="O78" s="12" t="n"/>
-      <c r="P78" s="12" t="n"/>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="O78" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="P78" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="Q78" s="12" t="inlineStr">
         <is>
           <t>CHG-A0046</t>
@@ -7717,11 +8333,19 @@
       </c>
       <c r="N79" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="O79" s="12" t="n"/>
-      <c r="P79" s="12" t="n"/>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="O79" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="P79" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="Q79" s="12" t="inlineStr">
         <is>
           <t>CHG-A0047</t>
@@ -7804,11 +8428,19 @@
       </c>
       <c r="N80" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="O80" s="12" t="n"/>
-      <c r="P80" s="12" t="n"/>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="O80" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="P80" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="Q80" s="12" t="inlineStr">
         <is>
           <t>CHG-A0048</t>
@@ -8086,11 +8718,19 @@
       </c>
       <c r="L2" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M2" s="12" t="n"/>
-      <c r="N2" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M2" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N2" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O2" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -8154,11 +8794,19 @@
       </c>
       <c r="L3" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M3" s="12" t="n"/>
-      <c r="N3" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M3" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N3" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O3" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -8222,11 +8870,19 @@
       </c>
       <c r="L4" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M4" s="12" t="n"/>
-      <c r="N4" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M4" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N4" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O4" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -8290,11 +8946,19 @@
       </c>
       <c r="L5" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M5" s="12" t="n"/>
-      <c r="N5" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M5" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N5" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O5" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -8358,11 +9022,19 @@
       </c>
       <c r="L6" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M6" s="12" t="n"/>
-      <c r="N6" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M6" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N6" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O6" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -8426,11 +9098,19 @@
       </c>
       <c r="L7" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M7" s="12" t="n"/>
-      <c r="N7" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M7" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N7" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O7" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -8494,11 +9174,19 @@
       </c>
       <c r="L8" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M8" s="12" t="n"/>
-      <c r="N8" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M8" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N8" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O8" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -8562,11 +9250,19 @@
       </c>
       <c r="L9" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M9" s="12" t="n"/>
-      <c r="N9" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M9" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N9" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O9" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -8630,11 +9326,19 @@
       </c>
       <c r="L10" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M10" s="12" t="n"/>
-      <c r="N10" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M10" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N10" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O10" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -8698,11 +9402,19 @@
       </c>
       <c r="L11" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M11" s="12" t="n"/>
-      <c r="N11" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M11" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N11" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O11" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -8766,11 +9478,19 @@
       </c>
       <c r="L12" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M12" s="12" t="n"/>
-      <c r="N12" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M12" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N12" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O12" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -8834,11 +9554,19 @@
       </c>
       <c r="L13" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M13" s="12" t="n"/>
-      <c r="N13" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M13" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N13" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O13" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -8902,11 +9630,19 @@
       </c>
       <c r="L14" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M14" s="12" t="n"/>
-      <c r="N14" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M14" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N14" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O14" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -8970,11 +9706,19 @@
       </c>
       <c r="L15" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M15" s="12" t="n"/>
-      <c r="N15" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M15" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N15" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O15" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -9038,11 +9782,19 @@
       </c>
       <c r="L16" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M16" s="12" t="n"/>
-      <c r="N16" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M16" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N16" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O16" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -9106,11 +9858,19 @@
       </c>
       <c r="L17" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M17" s="12" t="n"/>
-      <c r="N17" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M17" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N17" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O17" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -9174,11 +9934,19 @@
       </c>
       <c r="L18" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M18" s="12" t="n"/>
-      <c r="N18" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M18" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N18" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O18" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -9242,11 +10010,19 @@
       </c>
       <c r="L19" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M19" s="12" t="n"/>
-      <c r="N19" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M19" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N19" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O19" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -9310,11 +10086,19 @@
       </c>
       <c r="L20" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M20" s="12" t="n"/>
-      <c r="N20" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M20" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N20" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O20" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -9378,11 +10162,19 @@
       </c>
       <c r="L21" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M21" s="12" t="n"/>
-      <c r="N21" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M21" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N21" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O21" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -9446,11 +10238,19 @@
       </c>
       <c r="L22" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M22" s="12" t="n"/>
-      <c r="N22" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M22" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N22" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O22" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -9514,11 +10314,19 @@
       </c>
       <c r="L23" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M23" s="12" t="n"/>
-      <c r="N23" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M23" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N23" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O23" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -9582,11 +10390,19 @@
       </c>
       <c r="L24" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M24" s="12" t="n"/>
-      <c r="N24" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M24" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N24" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O24" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -9650,11 +10466,19 @@
       </c>
       <c r="L25" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M25" s="12" t="n"/>
-      <c r="N25" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M25" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N25" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O25" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -9718,11 +10542,19 @@
       </c>
       <c r="L26" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M26" s="12" t="n"/>
-      <c r="N26" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M26" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N26" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O26" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -9786,11 +10618,19 @@
       </c>
       <c r="L27" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M27" s="12" t="n"/>
-      <c r="N27" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M27" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N27" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O27" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -9854,11 +10694,19 @@
       </c>
       <c r="L28" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M28" s="12" t="n"/>
-      <c r="N28" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M28" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N28" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O28" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -9922,11 +10770,19 @@
       </c>
       <c r="L29" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M29" s="12" t="n"/>
-      <c r="N29" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M29" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N29" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O29" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -9990,11 +10846,19 @@
       </c>
       <c r="L30" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M30" s="12" t="n"/>
-      <c r="N30" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M30" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N30" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O30" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -10058,11 +10922,19 @@
       </c>
       <c r="L31" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M31" s="12" t="n"/>
-      <c r="N31" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M31" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N31" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O31" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -10126,11 +10998,19 @@
       </c>
       <c r="L32" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M32" s="12" t="n"/>
-      <c r="N32" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M32" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N32" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O32" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -10194,11 +11074,19 @@
       </c>
       <c r="L33" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M33" s="12" t="n"/>
-      <c r="N33" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M33" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N33" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O33" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -10262,11 +11150,19 @@
       </c>
       <c r="L34" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M34" s="12" t="n"/>
-      <c r="N34" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M34" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N34" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O34" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -10330,11 +11226,19 @@
       </c>
       <c r="L35" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M35" s="12" t="n"/>
-      <c r="N35" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M35" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N35" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O35" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -10398,11 +11302,19 @@
       </c>
       <c r="L36" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M36" s="12" t="n"/>
-      <c r="N36" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M36" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N36" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O36" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -10466,11 +11378,19 @@
       </c>
       <c r="L37" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M37" s="12" t="n"/>
-      <c r="N37" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M37" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N37" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O37" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -10534,11 +11454,19 @@
       </c>
       <c r="L38" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M38" s="12" t="n"/>
-      <c r="N38" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M38" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N38" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O38" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -10602,11 +11530,19 @@
       </c>
       <c r="L39" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M39" s="12" t="n"/>
-      <c r="N39" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M39" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N39" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O39" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -10670,11 +11606,19 @@
       </c>
       <c r="L40" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M40" s="12" t="n"/>
-      <c r="N40" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M40" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N40" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O40" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -10738,11 +11682,19 @@
       </c>
       <c r="L41" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M41" s="12" t="n"/>
-      <c r="N41" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M41" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N41" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O41" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -10806,11 +11758,19 @@
       </c>
       <c r="L42" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M42" s="12" t="n"/>
-      <c r="N42" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M42" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N42" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O42" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -10874,11 +11834,19 @@
       </c>
       <c r="L43" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M43" s="12" t="n"/>
-      <c r="N43" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M43" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N43" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O43" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -10942,11 +11910,19 @@
       </c>
       <c r="L44" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M44" s="12" t="n"/>
-      <c r="N44" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M44" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N44" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O44" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -11010,11 +11986,19 @@
       </c>
       <c r="L45" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M45" s="12" t="n"/>
-      <c r="N45" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M45" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N45" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O45" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -11078,11 +12062,19 @@
       </c>
       <c r="L46" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M46" s="12" t="n"/>
-      <c r="N46" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M46" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N46" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O46" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -11146,11 +12138,19 @@
       </c>
       <c r="L47" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M47" s="12" t="n"/>
-      <c r="N47" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M47" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N47" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O47" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -11214,11 +12214,19 @@
       </c>
       <c r="L48" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M48" s="12" t="n"/>
-      <c r="N48" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M48" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N48" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O48" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -11282,11 +12290,19 @@
       </c>
       <c r="L49" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M49" s="12" t="n"/>
-      <c r="N49" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M49" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N49" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O49" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -11350,11 +12366,19 @@
       </c>
       <c r="L50" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M50" s="12" t="n"/>
-      <c r="N50" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M50" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N50" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O50" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -11418,11 +12442,19 @@
       </c>
       <c r="L51" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M51" s="12" t="n"/>
-      <c r="N51" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M51" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N51" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O51" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -11486,11 +12518,19 @@
       </c>
       <c r="L52" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M52" s="12" t="n"/>
-      <c r="N52" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M52" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N52" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O52" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -11554,11 +12594,19 @@
       </c>
       <c r="L53" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M53" s="12" t="n"/>
-      <c r="N53" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M53" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N53" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O53" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -11622,11 +12670,19 @@
       </c>
       <c r="L54" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M54" s="12" t="n"/>
-      <c r="N54" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M54" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N54" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O54" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -11690,11 +12746,19 @@
       </c>
       <c r="L55" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M55" s="12" t="n"/>
-      <c r="N55" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M55" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N55" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O55" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -11758,11 +12822,19 @@
       </c>
       <c r="L56" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M56" s="12" t="n"/>
-      <c r="N56" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M56" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N56" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O56" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -11826,11 +12898,19 @@
       </c>
       <c r="L57" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M57" s="12" t="n"/>
-      <c r="N57" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M57" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N57" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O57" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -11894,11 +12974,19 @@
       </c>
       <c r="L58" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M58" s="12" t="n"/>
-      <c r="N58" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M58" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N58" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O58" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -11962,11 +13050,19 @@
       </c>
       <c r="L59" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M59" s="12" t="n"/>
-      <c r="N59" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M59" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N59" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O59" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -12030,11 +13126,19 @@
       </c>
       <c r="L60" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M60" s="12" t="n"/>
-      <c r="N60" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M60" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N60" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O60" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -12098,11 +13202,19 @@
       </c>
       <c r="L61" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M61" s="12" t="n"/>
-      <c r="N61" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M61" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N61" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O61" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -12166,11 +13278,19 @@
       </c>
       <c r="L62" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M62" s="12" t="n"/>
-      <c r="N62" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M62" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N62" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O62" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -12234,11 +13354,19 @@
       </c>
       <c r="L63" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M63" s="12" t="n"/>
-      <c r="N63" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M63" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N63" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O63" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -12302,11 +13430,19 @@
       </c>
       <c r="L64" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M64" s="12" t="n"/>
-      <c r="N64" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M64" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N64" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O64" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -12370,11 +13506,19 @@
       </c>
       <c r="L65" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M65" s="12" t="n"/>
-      <c r="N65" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M65" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N65" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O65" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -12438,11 +13582,19 @@
       </c>
       <c r="L66" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M66" s="12" t="n"/>
-      <c r="N66" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M66" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N66" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O66" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -12506,11 +13658,19 @@
       </c>
       <c r="L67" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M67" s="12" t="n"/>
-      <c r="N67" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M67" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N67" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O67" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -12574,11 +13734,19 @@
       </c>
       <c r="L68" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M68" s="12" t="n"/>
-      <c r="N68" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M68" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N68" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O68" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -12642,11 +13810,19 @@
       </c>
       <c r="L69" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M69" s="12" t="n"/>
-      <c r="N69" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M69" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N69" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O69" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -12710,11 +13886,19 @@
       </c>
       <c r="L70" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M70" s="12" t="n"/>
-      <c r="N70" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M70" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N70" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O70" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -12778,11 +13962,19 @@
       </c>
       <c r="L71" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M71" s="12" t="n"/>
-      <c r="N71" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M71" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N71" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O71" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -12846,11 +14038,19 @@
       </c>
       <c r="L72" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M72" s="12" t="n"/>
-      <c r="N72" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M72" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N72" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O72" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -12914,11 +14114,19 @@
       </c>
       <c r="L73" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M73" s="12" t="n"/>
-      <c r="N73" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M73" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N73" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O73" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -12982,11 +14190,19 @@
       </c>
       <c r="L74" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M74" s="12" t="n"/>
-      <c r="N74" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M74" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N74" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O74" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -13050,11 +14266,19 @@
       </c>
       <c r="L75" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M75" s="12" t="n"/>
-      <c r="N75" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M75" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N75" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O75" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -13118,11 +14342,19 @@
       </c>
       <c r="L76" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M76" s="12" t="n"/>
-      <c r="N76" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M76" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N76" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O76" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -13186,11 +14418,19 @@
       </c>
       <c r="L77" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M77" s="12" t="n"/>
-      <c r="N77" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M77" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N77" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O77" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -13254,11 +14494,19 @@
       </c>
       <c r="L78" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M78" s="12" t="n"/>
-      <c r="N78" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M78" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N78" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O78" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -13322,11 +14570,19 @@
       </c>
       <c r="L79" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M79" s="12" t="n"/>
-      <c r="N79" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M79" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N79" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O79" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -13390,11 +14646,19 @@
       </c>
       <c r="L80" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M80" s="12" t="n"/>
-      <c r="N80" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M80" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N80" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O80" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -13462,11 +14726,19 @@
       </c>
       <c r="L81" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M81" s="12" t="n"/>
-      <c r="N81" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M81" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N81" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O81" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -13534,11 +14806,19 @@
       </c>
       <c r="L82" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M82" s="12" t="n"/>
-      <c r="N82" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M82" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N82" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O82" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -13606,11 +14886,19 @@
       </c>
       <c r="L83" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M83" s="12" t="n"/>
-      <c r="N83" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M83" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N83" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O83" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -13678,11 +14966,19 @@
       </c>
       <c r="L84" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M84" s="12" t="n"/>
-      <c r="N84" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M84" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N84" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O84" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -13750,11 +15046,19 @@
       </c>
       <c r="L85" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M85" s="12" t="n"/>
-      <c r="N85" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M85" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N85" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O85" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -13822,11 +15126,19 @@
       </c>
       <c r="L86" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M86" s="12" t="n"/>
-      <c r="N86" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M86" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N86" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O86" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -13894,11 +15206,19 @@
       </c>
       <c r="L87" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M87" s="12" t="n"/>
-      <c r="N87" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M87" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N87" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O87" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -13964,11 +15284,19 @@
       <c r="K88" s="12" t="n"/>
       <c r="L88" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M88" s="12" t="n"/>
-      <c r="N88" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M88" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N88" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O88" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -14034,11 +15362,19 @@
       <c r="K89" s="12" t="n"/>
       <c r="L89" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M89" s="12" t="n"/>
-      <c r="N89" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M89" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N89" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O89" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -14104,11 +15440,19 @@
       <c r="K90" s="12" t="n"/>
       <c r="L90" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M90" s="12" t="n"/>
-      <c r="N90" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M90" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N90" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O90" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -14174,11 +15518,19 @@
       <c r="K91" s="12" t="n"/>
       <c r="L91" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M91" s="12" t="n"/>
-      <c r="N91" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M91" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N91" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O91" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -14244,11 +15596,19 @@
       <c r="K92" s="12" t="n"/>
       <c r="L92" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M92" s="12" t="n"/>
-      <c r="N92" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M92" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N92" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O92" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -14314,11 +15674,19 @@
       <c r="K93" s="12" t="n"/>
       <c r="L93" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M93" s="12" t="n"/>
-      <c r="N93" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M93" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N93" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O93" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -14384,11 +15752,19 @@
       <c r="K94" s="12" t="n"/>
       <c r="L94" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M94" s="12" t="n"/>
-      <c r="N94" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M94" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N94" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O94" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -14454,11 +15830,19 @@
       <c r="K95" s="12" t="n"/>
       <c r="L95" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M95" s="12" t="n"/>
-      <c r="N95" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M95" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N95" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O95" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -14524,11 +15908,19 @@
       <c r="K96" s="12" t="n"/>
       <c r="L96" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M96" s="12" t="n"/>
-      <c r="N96" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M96" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N96" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O96" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -14594,11 +15986,19 @@
       <c r="K97" s="12" t="n"/>
       <c r="L97" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M97" s="12" t="n"/>
-      <c r="N97" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M97" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N97" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O97" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -14664,11 +16064,19 @@
       <c r="K98" s="12" t="n"/>
       <c r="L98" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M98" s="12" t="n"/>
-      <c r="N98" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M98" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N98" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O98" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -14734,11 +16142,19 @@
       <c r="K99" s="12" t="n"/>
       <c r="L99" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M99" s="12" t="n"/>
-      <c r="N99" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M99" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N99" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O99" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -14804,11 +16220,19 @@
       <c r="K100" s="12" t="n"/>
       <c r="L100" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M100" s="12" t="n"/>
-      <c r="N100" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M100" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N100" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O100" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -14874,11 +16298,19 @@
       <c r="K101" s="12" t="n"/>
       <c r="L101" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M101" s="12" t="n"/>
-      <c r="N101" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M101" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N101" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O101" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -14944,11 +16376,19 @@
       <c r="K102" s="12" t="n"/>
       <c r="L102" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M102" s="12" t="n"/>
-      <c r="N102" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M102" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N102" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O102" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -15014,11 +16454,19 @@
       <c r="K103" s="12" t="n"/>
       <c r="L103" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M103" s="12" t="n"/>
-      <c r="N103" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M103" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N103" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O103" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -15084,11 +16532,19 @@
       <c r="K104" s="12" t="n"/>
       <c r="L104" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M104" s="12" t="n"/>
-      <c r="N104" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M104" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N104" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O104" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -15154,11 +16610,19 @@
       <c r="K105" s="12" t="n"/>
       <c r="L105" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M105" s="12" t="n"/>
-      <c r="N105" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M105" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N105" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O105" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -15224,11 +16688,19 @@
       <c r="K106" s="12" t="n"/>
       <c r="L106" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M106" s="12" t="n"/>
-      <c r="N106" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M106" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N106" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O106" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -15294,11 +16766,19 @@
       <c r="K107" s="12" t="n"/>
       <c r="L107" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M107" s="12" t="n"/>
-      <c r="N107" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M107" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N107" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O107" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -15364,11 +16844,19 @@
       <c r="K108" s="12" t="n"/>
       <c r="L108" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M108" s="12" t="n"/>
-      <c r="N108" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M108" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N108" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O108" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -15434,11 +16922,19 @@
       <c r="K109" s="12" t="n"/>
       <c r="L109" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M109" s="12" t="n"/>
-      <c r="N109" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M109" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N109" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O109" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -15504,11 +17000,19 @@
       <c r="K110" s="12" t="n"/>
       <c r="L110" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M110" s="12" t="n"/>
-      <c r="N110" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M110" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N110" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O110" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -15574,11 +17078,19 @@
       <c r="K111" s="12" t="n"/>
       <c r="L111" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M111" s="12" t="n"/>
-      <c r="N111" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M111" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N111" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O111" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -15644,11 +17156,19 @@
       <c r="K112" s="12" t="n"/>
       <c r="L112" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M112" s="12" t="n"/>
-      <c r="N112" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M112" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N112" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O112" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -15714,11 +17234,19 @@
       <c r="K113" s="12" t="n"/>
       <c r="L113" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M113" s="12" t="n"/>
-      <c r="N113" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M113" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N113" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O113" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -15784,11 +17312,19 @@
       <c r="K114" s="12" t="n"/>
       <c r="L114" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M114" s="12" t="n"/>
-      <c r="N114" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M114" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N114" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O114" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -15854,11 +17390,19 @@
       <c r="K115" s="12" t="n"/>
       <c r="L115" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M115" s="12" t="n"/>
-      <c r="N115" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M115" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N115" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O115" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -15924,11 +17468,19 @@
       <c r="K116" s="12" t="n"/>
       <c r="L116" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M116" s="12" t="n"/>
-      <c r="N116" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M116" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N116" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O116" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -15994,11 +17546,19 @@
       <c r="K117" s="12" t="n"/>
       <c r="L117" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M117" s="12" t="n"/>
-      <c r="N117" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M117" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N117" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O117" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -16064,11 +17624,19 @@
       <c r="K118" s="12" t="n"/>
       <c r="L118" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M118" s="12" t="n"/>
-      <c r="N118" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M118" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N118" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O118" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -16134,11 +17702,19 @@
       <c r="K119" s="12" t="n"/>
       <c r="L119" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M119" s="12" t="n"/>
-      <c r="N119" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M119" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N119" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O119" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -16204,11 +17780,19 @@
       <c r="K120" s="12" t="n"/>
       <c r="L120" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M120" s="12" t="n"/>
-      <c r="N120" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M120" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N120" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O120" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -16274,11 +17858,19 @@
       <c r="K121" s="12" t="n"/>
       <c r="L121" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M121" s="12" t="n"/>
-      <c r="N121" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M121" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N121" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O121" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -16344,11 +17936,19 @@
       <c r="K122" s="12" t="n"/>
       <c r="L122" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M122" s="12" t="n"/>
-      <c r="N122" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M122" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N122" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O122" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -16414,11 +18014,19 @@
       <c r="K123" s="12" t="n"/>
       <c r="L123" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M123" s="12" t="n"/>
-      <c r="N123" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M123" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N123" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O123" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -16484,11 +18092,19 @@
       <c r="K124" s="12" t="n"/>
       <c r="L124" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M124" s="12" t="n"/>
-      <c r="N124" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M124" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N124" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O124" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -16554,11 +18170,19 @@
       <c r="K125" s="12" t="n"/>
       <c r="L125" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M125" s="12" t="n"/>
-      <c r="N125" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M125" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N125" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O125" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -16624,11 +18248,19 @@
       <c r="K126" s="12" t="n"/>
       <c r="L126" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M126" s="12" t="n"/>
-      <c r="N126" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M126" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N126" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O126" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -16694,11 +18326,19 @@
       <c r="K127" s="12" t="n"/>
       <c r="L127" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M127" s="12" t="n"/>
-      <c r="N127" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M127" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N127" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O127" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -16764,11 +18404,19 @@
       <c r="K128" s="12" t="n"/>
       <c r="L128" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M128" s="12" t="n"/>
-      <c r="N128" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M128" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N128" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O128" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -16834,11 +18482,19 @@
       <c r="K129" s="12" t="n"/>
       <c r="L129" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M129" s="12" t="n"/>
-      <c r="N129" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M129" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N129" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O129" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -16904,11 +18560,19 @@
       <c r="K130" s="12" t="n"/>
       <c r="L130" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M130" s="12" t="n"/>
-      <c r="N130" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M130" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N130" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O130" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -16974,11 +18638,19 @@
       <c r="K131" s="12" t="n"/>
       <c r="L131" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M131" s="12" t="n"/>
-      <c r="N131" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M131" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N131" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O131" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -17044,11 +18716,19 @@
       <c r="K132" s="12" t="n"/>
       <c r="L132" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M132" s="12" t="n"/>
-      <c r="N132" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M132" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N132" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O132" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -17114,11 +18794,19 @@
       <c r="K133" s="12" t="n"/>
       <c r="L133" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M133" s="12" t="n"/>
-      <c r="N133" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M133" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N133" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O133" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -17186,11 +18874,19 @@
       </c>
       <c r="L134" s="16" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M134" s="16" t="n"/>
-      <c r="N134" s="16" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M134" s="16" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N134" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O134" s="16" t="inlineStr">
         <is>
           <t>Y</t>
@@ -17258,11 +18954,19 @@
       </c>
       <c r="L135" s="16" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M135" s="16" t="n"/>
-      <c r="N135" s="16" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M135" s="16" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N135" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O135" s="16" t="inlineStr">
         <is>
           <t>Y</t>
@@ -17330,11 +19034,19 @@
       </c>
       <c r="L136" s="16" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M136" s="16" t="n"/>
-      <c r="N136" s="16" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M136" s="16" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N136" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O136" s="16" t="inlineStr">
         <is>
           <t>Y</t>
@@ -17402,11 +19114,19 @@
       </c>
       <c r="L137" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M137" s="12" t="n"/>
-      <c r="N137" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M137" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N137" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O137" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -17474,11 +19194,19 @@
       </c>
       <c r="L138" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M138" s="12" t="n"/>
-      <c r="N138" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M138" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N138" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O138" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -17546,11 +19274,19 @@
       </c>
       <c r="L139" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M139" s="12" t="n"/>
-      <c r="N139" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M139" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N139" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O139" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -17618,11 +19354,19 @@
       </c>
       <c r="L140" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M140" s="12" t="n"/>
-      <c r="N140" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M140" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N140" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O140" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -17686,11 +19430,19 @@
       </c>
       <c r="L141" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M141" s="12" t="n"/>
-      <c r="N141" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M141" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N141" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O141" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -17754,11 +19506,19 @@
       </c>
       <c r="L142" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M142" s="12" t="n"/>
-      <c r="N142" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M142" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N142" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O142" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -17822,11 +19582,19 @@
       </c>
       <c r="L143" s="12" t="inlineStr">
         <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="M143" s="12" t="n"/>
-      <c r="N143" s="12" t="n"/>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="M143" s="12" t="inlineStr">
+        <is>
+          <t>Gautam Kundalia</t>
+        </is>
+      </c>
+      <c r="N143" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="O143" s="12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -17974,22 +19742,22 @@
     <row r="3">
       <c r="A3" s="12" t="inlineStr">
         <is>
-          <t>SRC-0001</t>
+          <t>SRC-0004</t>
         </is>
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>MeitY</t>
+          <t>PIB</t>
         </is>
       </c>
       <c r="C3" s="12" t="inlineStr">
         <is>
-          <t>DPDP Rules, 2025 — MeitY PDF (G.S.R. 846(E))</t>
+          <t>PIB — All Press Releases (English)</t>
         </is>
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>https://www.meity.gov.in/static/uploads/2025/11/53450e6e5dc0bfa85ebd78686cadad39.pdf</t>
+          <t>https://www.pib.gov.in/allRel.aspx</t>
         </is>
       </c>
       <c r="E3" s="12" t="n"/>
@@ -18000,7 +19768,7 @@
       </c>
       <c r="G3" s="12" t="inlineStr">
         <is>
-          <t>76094c7228c8dbff357281552fa2b052fe363303eb8b2c33ee5361d38883070d</t>
+          <t>d38842055f43a4f6ee39929156a2c93772a0b128ba3ab14f887a64fcf1c77e89</t>
         </is>
       </c>
       <c r="H3" s="12" t="inlineStr">
@@ -18008,34 +19776,34 @@
           <t>No Change Detected</t>
         </is>
       </c>
-      <c r="I3" s="12" t="inlineStr">
-        <is>
-          <t>CHG-0002,CHG-0003,CHG-0004,CHG-0005,CHG-0006,CHG-0007,CHG-0008,CHG-0009,CHG-0010,CHG-0011,CHG-0012,CHG-0013,CHG-0014,CHG-0015,CHG-0016,CHG-0017,CHG-0018,CHG-0019,CHG-0020,CHG-0021,CHG-0022,CHG-0023,CHG-0024,CHG-0025,CHG-0026,CHG-0027,CHG-0028,CHG-0029,CHG-0030,CHG-0031,CHG-0032</t>
-        </is>
-      </c>
+      <c r="I3" s="12" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="12" t="inlineStr">
         <is>
-          <t>SRC-0004</t>
+          <t>SRC-0006</t>
         </is>
       </c>
       <c r="B4" s="12" t="inlineStr">
         <is>
-          <t>PIB</t>
+          <t>MeitY</t>
         </is>
       </c>
       <c r="C4" s="12" t="inlineStr">
         <is>
-          <t>PIB — All Press Releases (English)</t>
+          <t>Corrigenda G.S.R. 892(E), 10 Dec 2025 (Gazette Extraordinary No. 806, 11 Dec 2025)</t>
         </is>
       </c>
       <c r="D4" s="12" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/allRel.aspx</t>
-        </is>
-      </c>
-      <c r="E4" s="12" t="n"/>
+          <t>https://www.meity.gov.in/static/uploads/2025/12/3c7ebbae0e5456f493f486e6845df86b.pdf</t>
+        </is>
+      </c>
+      <c r="E4" s="12" t="inlineStr">
+        <is>
+          <t>2025-12-11</t>
+        </is>
+      </c>
       <c r="F4" s="12" t="inlineStr">
         <is>
           <t>2026-09-23</t>
@@ -18043,46 +19811,50 @@
       </c>
       <c r="G4" s="12" t="inlineStr">
         <is>
-          <t>d38842055f43a4f6ee39929156a2c93772a0b128ba3ab14f887a64fcf1c77e89</t>
+          <t>597d69e0d16cc9eeb72d1799195fe4a1b5fe4e2f3cb063310864736b39d3c244</t>
         </is>
       </c>
       <c r="H4" s="12" t="inlineStr">
         <is>
-          <t>No Change Detected</t>
-        </is>
-      </c>
-      <c r="I4" s="12" t="n"/>
+          <t>Processed</t>
+        </is>
+      </c>
+      <c r="I4" s="12" t="inlineStr">
+        <is>
+          <t>CHG-0086,CHG-0087,CHG-0088</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="12" t="inlineStr">
         <is>
-          <t>SRC-0005</t>
+          <t>SRC-0001</t>
         </is>
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>eGazette</t>
+          <t>MeitY</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>eGazette — Home (best-effort; no stable search endpoint confirmed)</t>
+          <t>DPDP Rules, 2025 — MeitY PDF (G.S.R. 846(E))</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>https://egazette.gov.in/</t>
+          <t>https://www.meity.gov.in/static/uploads/2025/11/53450e6e5dc0bfa85ebd78686cadad39.pdf</t>
         </is>
       </c>
       <c r="E5" s="12" t="n"/>
       <c r="F5" s="12" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
-          <t>5804450f38f800c83d0849fd9ad445e103b5d70cd17603a0519ecf3b14ddc5d3</t>
+          <t>76094c7228c8dbff357281552fa2b052fe363303eb8b2c33ee5361d38883070d</t>
         </is>
       </c>
       <c r="H5" s="12" t="inlineStr">
@@ -18090,38 +19862,42 @@
           <t>No Change Detected</t>
         </is>
       </c>
-      <c r="I5" s="12" t="n"/>
+      <c r="I5" s="12" t="inlineStr">
+        <is>
+          <t>CHG-0002,CHG-0003,CHG-0004,CHG-0005,CHG-0006,CHG-0007,CHG-0008,CHG-0009,CHG-0010,CHG-0011,CHG-0012,CHG-0013,CHG-0014,CHG-0015,CHG-0016,CHG-0017,CHG-0018,CHG-0019,CHG-0020,CHG-0021,CHG-0022,CHG-0023,CHG-0024,CHG-0025,CHG-0026,CHG-0027,CHG-0028,CHG-0029,CHG-0030,CHG-0031,CHG-0032</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="12" t="inlineStr">
         <is>
-          <t>SRC-0002</t>
+          <t>SRC-0005</t>
         </is>
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>MeitY</t>
+          <t>eGazette</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>DPDP Act, 2023 — MeitY PDF</t>
+          <t>eGazette — Home (best-effort; no stable search endpoint confirmed)</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>https://www.meity.gov.in/static/uploads/2024/06/2bf1f0e9f04e6fb4f8fef35e82c42aa5.pdf</t>
+          <t>https://egazette.gov.in/</t>
         </is>
       </c>
       <c r="E6" s="12" t="n"/>
       <c r="F6" s="12" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G6" s="12" t="inlineStr">
         <is>
-          <t>f15bda1ff8065c68f8e1cc57c50616264afeb49d72cfc48d1e92a2a3c473c1d2</t>
+          <t>0263e67d63e88fa4ad218b927a6cf82dbeeca9065635dc9c16464a94f9c2392c</t>
         </is>
       </c>
       <c r="H6" s="12" t="inlineStr">
@@ -18129,16 +19905,12 @@
           <t>No Change Detected</t>
         </is>
       </c>
-      <c r="I6" s="12" t="inlineStr">
-        <is>
-          <t>CHG-A0001,CHG-A0002,CHG-A0003,CHG-A0004,CHG-A0005,CHG-A0006,CHG-A0007,CHG-A0008,CHG-A0009,CHG-A0010,CHG-A0011,CHG-A0012,CHG-A0013,CHG-A0014,CHG-A0015,CHG-A0016,CHG-A0017,CHG-A0018,CHG-A0019,CHG-A0020,CHG-A0021,CHG-A0022,CHG-A0023,CHG-A0024,CHG-A0025,CHG-A0026,CHG-A0027,CHG-A0028,CHG-A0029,CHG-A0030,CHG-A0031,CHG-A0032,CHG-A0033,CHG-A0034,CHG-A0035,CHG-A0036,CHG-A0037,CHG-A0038,CHG-A0039,CHG-A0040,CHG-A0041,CHG-A0042,CHG-A0043,CHG-A0044,CHG-A0045,CHG-A0046,CHG-A0047,CHG-A0048</t>
-        </is>
-      </c>
+      <c r="I6" s="12" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
         <is>
-          <t>SRC-0006</t>
+          <t>SRC-0002</t>
         </is>
       </c>
       <c r="B7" s="12" t="inlineStr">
@@ -18148,37 +19920,33 @@
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>Corrigenda G.S.R. 892(E), 10 Dec 2025 (Gazette Extraordinary No. 806, 11 Dec 2025)</t>
+          <t>DPDP Act, 2023 — MeitY PDF</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>https://www.meity.gov.in/static/uploads/2025/12/3c7ebbae0e5456f493f486e6845df86b.pdf</t>
-        </is>
-      </c>
-      <c r="E7" s="12" t="inlineStr">
-        <is>
-          <t>2025-12-11</t>
-        </is>
-      </c>
+          <t>https://www.meity.gov.in/static/uploads/2024/06/2bf1f0e9f04e6fb4f8fef35e82c42aa5.pdf</t>
+        </is>
+      </c>
+      <c r="E7" s="12" t="n"/>
       <c r="F7" s="12" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
-          <t>597d69e0d16cc9eeb72d1799195fe4a1b5fe4e2f3cb063310864736b39d3c244</t>
+          <t>f15bda1ff8065c68f8e1cc57c50616264afeb49d72cfc48d1e92a2a3c473c1d2</t>
         </is>
       </c>
       <c r="H7" s="12" t="inlineStr">
         <is>
-          <t>Processed</t>
+          <t>No Change Detected</t>
         </is>
       </c>
       <c r="I7" s="12" t="inlineStr">
         <is>
-          <t>CHG-0086,CHG-0087,CHG-0088</t>
+          <t>CHG-A0001,CHG-A0002,CHG-A0003,CHG-A0004,CHG-A0005,CHG-A0006,CHG-A0007,CHG-A0008,CHG-A0009,CHG-A0010,CHG-A0011,CHG-A0012,CHG-A0013,CHG-A0014,CHG-A0015,CHG-A0016,CHG-A0017,CHG-A0018,CHG-A0019,CHG-A0020,CHG-A0021,CHG-A0022,CHG-A0023,CHG-A0024,CHG-A0025,CHG-A0026,CHG-A0027,CHG-A0028,CHG-A0029,CHG-A0030,CHG-A0031,CHG-A0032,CHG-A0033,CHG-A0034,CHG-A0035,CHG-A0036,CHG-A0037,CHG-A0038,CHG-A0039,CHG-A0040,CHG-A0041,CHG-A0042,CHG-A0043,CHG-A0044,CHG-A0045,CHG-A0046,CHG-A0047,CHG-A0048</t>
         </is>
       </c>
     </row>
@@ -18206,12 +19974,12 @@
       <c r="E8" s="12" t="n"/>
       <c r="F8" s="12" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
-          <t>303646cc4c4bce1f12f990b273eedffaa3f1ba4df657ca84d5418879e39c79ef</t>
+          <t>999b9fcb656461e59cfefe3a33ff05d77e449b7e6da0dbb7ff692c3c1ba46334</t>
         </is>
       </c>
       <c r="H8" s="12" t="inlineStr">

--- a/data/DPDP_Rules_Tracker.xlsx
+++ b/data/DPDP_Rules_Tracker.xlsx
@@ -535,7 +535,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B32"/>
+  <dimension ref="A1:B34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -592,7 +592,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>One row per provision (an Act section, Rule, or Schedule clause). This is the 'current state' view a consultant reads. Full_Text_Path is a clickable link that opens the full clause text in the consolidated Word document (DPDP_Rules_2025.docx or DPDP_Act_2023.docx), jumping straight to that provision's bookmark.</t>
+          <t>One row per provision (an Act section, Rule, or Schedule clause). This is the 'current state' view a consultant reads. Full_Text_Path is a clickable link that opens the full clause text in the consolidated Word document (DPDP_Rules_2025.docx or DPDP_Act_2023.docx), jumping straight to that provision's bookmark. The link is relative to this workbook's own folder (../docs/...), so it works as long as the docs folder travels with the file. If you email this workbook on its own, the links will not resolve — attach the two Word documents too.</t>
         </is>
       </c>
     </row>
@@ -616,7 +616,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>One row per source address (URL) the pipeline watches (a MeitY page, a Gazette notification, a PIB listing) — not one row per fetch. Each row is overwritten every run with the latest fetch's date and content fingerprint, so this sheet shows what's being watched right now and when it was last checked, not a history of past runs. Past detected changes live in Change_Log instead.</t>
+          <t>One row per source address (URL) the pipeline is watching RIGHT NOW — not one row per fetch, and not a history. Each row is overwritten every run with the latest fetch's date and content fingerprint. Addresses that were fetched once and are no longer watched (a one-off Gazette PDF, a retired page) are kept in the database for their change history but are deliberately left out of this sheet, because it would otherwise claim to be watching things it isn't. Past detected changes live in Change_Log instead.</t>
         </is>
       </c>
     </row>
@@ -692,7 +692,7 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Only a 'regulatory' change is ever highlighted, and only the specific words that changed — not the whole provision. In the Word documents: the changed words are highlighted yellow, with any removed words shown struck through in grey immediately before their replacement, plus a small caption naming the source and change. In this Change_Log sheet, an entire row is filled light yellow when it's a regulatory change. Our own data corrections are never highlighted anywhere — they stay in Change_Log as a record, but the current, correct text is simply shown as-is, with nothing marked up.</t>
+          <t>Only a 'regulatory' change is ever highlighted, and only the specific words that changed — not the whole provision. In the Word documents: the changed words are highlighted yellow, with any removed words shown struck through in grey immediately before their replacement, plus a small caption naming the source and change. EVERY government change to a provision is shown, not just the most recent one, and each gets its own caption line. In this Change_Log sheet, an entire row is filled light yellow when it's a regulatory change. Our own data corrections are never highlighted anywhere — they stay in Change_Log as a record, but the current, correct text is simply shown as-is, with nothing marked up. A data correction also cannot hide an earlier government change: the highlighting is worked out from Change_Log itself, not from whichever change happens to be the most recent one of any kind.</t>
         </is>
       </c>
     </row>
@@ -731,7 +731,7 @@
       <c r="A25" s="8" t="inlineStr"/>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Light yellow marks a real government change: the whole row in Change_Log, or just the Last_Regulatory_Change cell in Master_Provisions.</t>
+          <t>Light yellow marks a real government change: the whole row in Change_Log, or just the Last_Regulatory_Change cell in Master_Provisions. That cell names the most recent one and, if there have been others, says how many earlier ones there are — e.g. '2025-12-11 (CHG-0092) (+1 earlier)'. The full list is in Change_Log.</t>
         </is>
       </c>
     </row>
@@ -751,47 +751,71 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>This pipeline runs fully automatically, every day, with no human approval step before a detected change is written to Master_Provisions. Review_Status on a Change_Log row records how confident the automated classification was — it is not a queue waiting for a consultant's sign-off. If you want a human check before a change goes live, that would need to be added as a deliberate change to the pipeline; right now, it isn't there.</t>
+          <t>This pipeline runs fully automatically, every day, with no human approval step before a detected change is written to Master_Provisions. Review_Status is NOT a queue that holds a change back — a change is applied whether or not anyone has looked at it. It is a record of whether a person has since checked that row. Everything in this workbook as at 29 September 2026 HAS been reviewed by hand: all 79 provisions were set to Confirmed and all 142 change rows to Approved by Gautam Kundalia on that date. Anything added after that is applied automatically and is not reviewed until somebody does it. If you want a human check before a change goes live, that has to be built; right now it isn't there, and whether to build it is an open decision.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>1. Detect</t>
+          <t>What Confidence_Score is not</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>The pipeline checks each Source_Log-tracked address on schedule; a changed fingerprint updates that row.</t>
+          <t>Every AI-classified change records the model's own confidence, and a low score does NOT stop the change being applied. That is deliberate: an independent audit measured a genuine, correctly-identified amendment at 0.65, so a cut-off would have blocked a real change in the law. Treat the number as a hint while reviewing, never as a safety net.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>2. Extract &amp; classify</t>
+          <t>1. Detect</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>Only the changed passages of the source are compared against the current text and sent to Claude, which reports what changed and how (Change_Type, Change_Origin, Old/New text).</t>
+          <t>The pipeline checks each Source_Log-tracked address on schedule; a changed fingerprint updates that row.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
+          <t>2. Extract &amp; classify</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Only the changed passages of the source are compared against the current text and sent to Claude, which reports what changed and how (Change_Type, Change_Origin, Old/New text).</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>2a. Check the source is allowed to say that</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>Only the official MeitY PDF of an instrument may change that instrument's text: the DPDP Rules PDF may change Rule and Schedule rows, the DPDP Act PDF may change Act Section rows, and nothing else may change anything. A press release or a Gazette index page can raise an alert for a human to read, never a change to the text. Anything refused is reported as an error in the daily email — it is never dropped quietly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
           <t>3. Apply, automatically</t>
         </is>
       </c>
-      <c r="B31" s="5" t="inlineStr">
+      <c r="B33" s="5" t="inlineStr">
         <is>
           <t>Master_Provisions is updated immediately, Change_Log's Applied_To_Master is marked Y, and the next export_word.py / export_excel.py run renders the result — a highlighted amendment if Change_Origin is 'regulatory', nothing visible if it's a 'data_correction'.</t>
         </is>
       </c>
     </row>
-    <row r="32"/>
+    <row r="34"/>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A4:B4"/>
@@ -1030,7 +1054,7 @@
         </is>
       </c>
       <c r="S2" s="14">
-        <f>IF(I2="","",IF(TODAY()&gt;=DATEVALUE(I2),"Yes","No"))</f>
+        <f>IF(I2="","",IFERROR(IF(TODAY()&gt;=DATEVALUE(I2),"Yes","No"),""))</f>
         <v/>
       </c>
       <c r="T2" s="14" t="n"/>
@@ -1125,7 +1149,7 @@
         </is>
       </c>
       <c r="S3" s="14">
-        <f>IF(I3="","",IF(TODAY()&gt;=DATEVALUE(I3),"Yes","No"))</f>
+        <f>IF(I3="","",IFERROR(IF(TODAY()&gt;=DATEVALUE(I3),"Yes","No"),""))</f>
         <v/>
       </c>
       <c r="T3" s="15" t="inlineStr">
@@ -1224,7 +1248,7 @@
         </is>
       </c>
       <c r="S4" s="14">
-        <f>IF(I4="","",IF(TODAY()&gt;=DATEVALUE(I4),"Yes","No"))</f>
+        <f>IF(I4="","",IFERROR(IF(TODAY()&gt;=DATEVALUE(I4),"Yes","No"),""))</f>
         <v/>
       </c>
       <c r="T4" s="14" t="n"/>
@@ -1319,7 +1343,7 @@
         </is>
       </c>
       <c r="S5" s="14">
-        <f>IF(I5="","",IF(TODAY()&gt;=DATEVALUE(I5),"Yes","No"))</f>
+        <f>IF(I5="","",IFERROR(IF(TODAY()&gt;=DATEVALUE(I5),"Yes","No"),""))</f>
         <v/>
       </c>
       <c r="T5" s="14" t="n"/>
@@ -1414,7 +1438,7 @@
         </is>
       </c>
       <c r="S6" s="14">
-        <f>IF(I6="","",IF(TODAY()&gt;=DATEVALUE(I6),"Yes","No"))</f>
+        <f>IF(I6="","",IFERROR(IF(TODAY()&gt;=DATEVALUE(I6),"Yes","No"),""))</f>
         <v/>
       </c>
       <c r="T6" s="14" t="n"/>
@@ -1509,7 +1533,7 @@
         </is>
       </c>
       <c r="S7" s="14">
-        <f>IF(I7="","",IF(TODAY()&gt;=DATEVALUE(I7),"Yes","No"))</f>
+        <f>IF(I7="","",IFERROR(IF(TODAY()&gt;=DATEVALUE(I7),"Yes","No"),""))</f>
         <v/>
       </c>
       <c r="T7" s="14" t="n"/>
@@ -1604,7 +1628,7 @@
         </is>
       </c>
       <c r="S8" s="14">
-        <f>IF(I8="","",IF(TODAY()&gt;=DATEVALUE(I8),"Yes","No"))</f>
+        <f>IF(I8="","",IFERROR(IF(TODAY()&gt;=DATEVALUE(I8),"Yes","No"),""))</f>
         <v/>
       </c>
       <c r="T8" s="14" t="n"/>
@@ -1699,7 +1723,7 @@
         </is>
       </c>
       <c r="S9" s="14">
-        <f>IF(I9="","",IF(TODAY()&gt;=DATEVALUE(I9),"Yes","No"))</f>
+        <f>IF(I9="","",IFERROR(IF(TODAY()&gt;=DATEVALUE(I9),"Yes","No"),""))</f>
         <v/>
       </c>
       <c r="T9" s="14" t="n"/>
@@ -1794,7 +1818,7 @@
         </is>
       </c>
       <c r="S10" s="14">
-        <f>IF(I10="","",IF(TODAY()&gt;=DATEVALUE(I10),"Yes","No"))</f>
+        <f>IF(I10="","",IFERROR(IF(TODAY()&gt;=DATEVALUE(I10),"Yes","No"),""))</f>
         <v/>
       </c>
       <c r="T10" s="14" t="n"/>
@@ -1889,7 +1913,7 @@
         </is>
       </c>
       <c r="S11" s="14">
-        <f>IF(I11="","",IF(TODAY()&gt;=DATEVALUE(I11),"Yes","No"))</f>
+        <f>IF(I11="","",IFERROR(IF(TODAY()&gt;=DATEVALUE(I11),"Yes","No"),""))</f>
         <v/>
       </c>
       <c r="T11" s="14" t="n"/>
@@ -1984,7 +2008,7 @@
         </is>
       </c>
       <c r="S12" s="14">
-        <f>IF(I12="","",IF(TODAY()&gt;=DATEVALUE(I12),"Yes","No"))</f>
+        <f>IF(I12="","",IFERROR(IF(TODAY()&gt;=DATEVALUE(I12),"Yes","No"),""))</f>
         <v/>
       </c>
       <c r="T12" s="14" t="n"/>
@@ -2079,7 +2103,7 @@
         </is>
       </c>
       <c r="S13" s="14">
-        <f>IF(I13="","",IF(TODAY()&gt;=DATEVALUE(I13),"Yes","No"))</f>
+        <f>IF(I13="","",IFERROR(IF(TODAY()&gt;=DATEVALUE(I13),"Yes","No"),""))</f>
         <v/>
       </c>
       <c r="T13" s="14" t="n"/>
@@ -2174,7 +2198,7 @@
         </is>
       </c>
       <c r="S14" s="14">
-        <f>IF(I14="","",IF(TODAY()&gt;=DATEVALUE(I14),"Yes","No"))</f>
+        <f>IF(I14="","",IFERROR(IF(TODAY()&gt;=DATEVALUE(I14),"Yes","No"),""))</f>
         <v/>
       </c>
       <c r="T14" s="14" t="n"/>
@@ -2269,7 +2293,7 @@
         </is>
       </c>
       <c r="S15" s="14">
-        <f>IF(I15="","",IF(TODAY()&gt;=DATEVALUE(I15),"Yes","No"))</f>
+        <f>IF(I15="","",IFERROR(IF(TODAY()&gt;=DATEVALUE(I15),"Yes","No"),""))</f>
         <v/>
       </c>
       <c r="T15" s="14" t="n"/>
@@ -2364,7 +2388,7 @@
         </is>
       </c>
       <c r="S16" s="14">
-        <f>IF(I16="","",IF(TODAY()&gt;=DATEVALUE(I16),"Yes","No"))</f>
+        <f>IF(I16="","",IFERROR(IF(TODAY()&gt;=DATEVALUE(I16),"Yes","No"),""))</f>
         <v/>
       </c>
       <c r="T16" s="14" t="n"/>
@@ -2459,7 +2483,7 @@
         </is>
       </c>
       <c r="S17" s="14">
-        <f>IF(I17="","",IF(TODAY()&gt;=DATEVALUE(I17),"Yes","No"))</f>
+        <f>IF(I17="","",IFERROR(IF(TODAY()&gt;=DATEVALUE(I17),"Yes","No"),""))</f>
         <v/>
       </c>
       <c r="T17" s="14" t="n"/>
@@ -2554,7 +2578,7 @@
         </is>
       </c>
       <c r="S18" s="14">
-        <f>IF(I18="","",IF(TODAY()&gt;=DATEVALUE(I18),"Yes","No"))</f>
+        <f>IF(I18="","",IFERROR(IF(TODAY()&gt;=DATEVALUE(I18),"Yes","No"),""))</f>
         <v/>
       </c>
       <c r="T18" s="14" t="n"/>
@@ -2649,7 +2673,7 @@
         </is>
       </c>
       <c r="S19" s="14">
-        <f>IF(I19="","",IF(TODAY()&gt;=DATEVALUE(I19),"Yes","No"))</f>
+        <f>IF(I19="","",IFERROR(IF(TODAY()&gt;=DATEVALUE(I19),"Yes","No"),""))</f>
         <v/>
       </c>
       <c r="T19" s="14" t="n"/>
@@ -2744,7 +2768,7 @@
         </is>
       </c>
       <c r="S20" s="14">
-        <f>IF(I20="","",IF(TODAY()&gt;=DATEVALUE(I20),"Yes","No"))</f>
+        <f>IF(I20="","",IFERROR(IF(TODAY()&gt;=DATEVALUE(I20),"Yes","No"),""))</f>
         <v/>
       </c>
       <c r="T20" s="14" t="n"/>
@@ -2839,7 +2863,7 @@
         </is>
       </c>
       <c r="S21" s="14">
-        <f>IF(I21="","",IF(TODAY()&gt;=DATEVALUE(I21),"Yes","No"))</f>
+        <f>IF(I21="","",IFERROR(IF(TODAY()&gt;=DATEVALUE(I21),"Yes","No"),""))</f>
         <v/>
       </c>
       <c r="T21" s="14" t="n"/>
@@ -2934,7 +2958,7 @@
         </is>
       </c>
       <c r="S22" s="14">
-        <f>IF(I22="","",IF(TODAY()&gt;=DATEVALUE(I22),"Yes","No"))</f>
+        <f>IF(I22="","",IFERROR(IF(TODAY()&gt;=DATEVALUE(I22),"Yes","No"),""))</f>
         <v/>
       </c>
       <c r="T22" s="14" t="n"/>
@@ -3029,7 +3053,7 @@
         </is>
       </c>
       <c r="S23" s="14">
-        <f>IF(I23="","",IF(TODAY()&gt;=DATEVALUE(I23),"Yes","No"))</f>
+        <f>IF(I23="","",IFERROR(IF(TODAY()&gt;=DATEVALUE(I23),"Yes","No"),""))</f>
         <v/>
       </c>
       <c r="T23" s="14" t="n"/>
@@ -3124,7 +3148,7 @@
         </is>
       </c>
       <c r="S24" s="14">
-        <f>IF(I24="","",IF(TODAY()&gt;=DATEVALUE(I24),"Yes","No"))</f>
+        <f>IF(I24="","",IFERROR(IF(TODAY()&gt;=DATEVALUE(I24),"Yes","No"),""))</f>
         <v/>
       </c>
       <c r="T24" s="14" t="n"/>
@@ -3219,7 +3243,7 @@
         </is>
       </c>
       <c r="S25" s="14">
-        <f>IF(I25="","",IF(TODAY()&gt;=DATEVALUE(I25),"Yes","No"))</f>
+        <f>IF(I25="","",IFERROR(IF(TODAY()&gt;=DATEVALUE(I25),"Yes","No"),""))</f>
         <v/>
       </c>
       <c r="T25" s="14" t="n"/>
@@ -3314,7 +3338,7 @@
         </is>
       </c>
       <c r="S26" s="14">
-        <f>IF(I26="","",IF(TODAY()&gt;=DATEVALUE(I26),"Yes","No"))</f>
+        <f>IF(I26="","",IFERROR(IF(TODAY()&gt;=DATEVALUE(I26),"Yes","No"),""))</f>
         <v/>
       </c>
       <c r="T26" s="14" t="n"/>
@@ -3409,7 +3433,7 @@
         </is>
       </c>
       <c r="S27" s="14">
-        <f>IF(I27="","",IF(TODAY()&gt;=DATEVALUE(I27),"Yes","No"))</f>
+        <f>IF(I27="","",IFERROR(IF(TODAY()&gt;=DATEVALUE(I27),"Yes","No"),""))</f>
         <v/>
       </c>
       <c r="T27" s="14" t="n"/>
@@ -3504,7 +3528,7 @@
         </is>
       </c>
       <c r="S28" s="14">
-        <f>IF(I28="","",IF(TODAY()&gt;=DATEVALUE(I28),"Yes","No"))</f>
+        <f>IF(I28="","",IFERROR(IF(TODAY()&gt;=DATEVALUE(I28),"Yes","No"),""))</f>
         <v/>
       </c>
       <c r="T28" s="14" t="n"/>
@@ -3599,7 +3623,7 @@
         </is>
       </c>
       <c r="S29" s="14">
-        <f>IF(I29="","",IF(TODAY()&gt;=DATEVALUE(I29),"Yes","No"))</f>
+        <f>IF(I29="","",IFERROR(IF(TODAY()&gt;=DATEVALUE(I29),"Yes","No"),""))</f>
         <v/>
       </c>
       <c r="T29" s="15" t="inlineStr">
@@ -3698,7 +3722,7 @@
         </is>
       </c>
       <c r="S30" s="14">
-        <f>IF(I30="","",IF(TODAY()&gt;=DATEVALUE(I30),"Yes","No"))</f>
+        <f>IF(I30="","",IFERROR(IF(TODAY()&gt;=DATEVALUE(I30),"Yes","No"),""))</f>
         <v/>
       </c>
       <c r="T30" s="14" t="n"/>
@@ -3793,7 +3817,7 @@
         </is>
       </c>
       <c r="S31" s="14">
-        <f>IF(I31="","",IF(TODAY()&gt;=DATEVALUE(I31),"Yes","No"))</f>
+        <f>IF(I31="","",IFERROR(IF(TODAY()&gt;=DATEVALUE(I31),"Yes","No"),""))</f>
         <v/>
       </c>
       <c r="T31" s="14" t="n"/>
@@ -3888,7 +3912,7 @@
         </is>
       </c>
       <c r="S32" s="14">
-        <f>IF(I32="","",IF(TODAY()&gt;=DATEVALUE(I32),"Yes","No"))</f>
+        <f>IF(I32="","",IFERROR(IF(TODAY()&gt;=DATEVALUE(I32),"Yes","No"),""))</f>
         <v/>
       </c>
       <c r="T32" s="14" t="n"/>
@@ -3983,7 +4007,7 @@
         </is>
       </c>
       <c r="S33" s="14">
-        <f>IF(I33="","",IF(TODAY()&gt;=DATEVALUE(I33),"Yes","No"))</f>
+        <f>IF(I33="","",IFERROR(IF(TODAY()&gt;=DATEVALUE(I33),"Yes","No"),""))</f>
         <v/>
       </c>
       <c r="T33" s="14" t="n"/>
@@ -4078,7 +4102,7 @@
         </is>
       </c>
       <c r="S34" s="14">
-        <f>IF(I34="","",IF(TODAY()&gt;=DATEVALUE(I34),"Yes","No"))</f>
+        <f>IF(I34="","",IFERROR(IF(TODAY()&gt;=DATEVALUE(I34),"Yes","No"),""))</f>
         <v/>
       </c>
       <c r="T34" s="14" t="n"/>
@@ -4173,7 +4197,7 @@
         </is>
       </c>
       <c r="S35" s="14">
-        <f>IF(I35="","",IF(TODAY()&gt;=DATEVALUE(I35),"Yes","No"))</f>
+        <f>IF(I35="","",IFERROR(IF(TODAY()&gt;=DATEVALUE(I35),"Yes","No"),""))</f>
         <v/>
       </c>
       <c r="T35" s="14" t="n"/>
@@ -4268,7 +4292,7 @@
         </is>
       </c>
       <c r="S36" s="14">
-        <f>IF(I36="","",IF(TODAY()&gt;=DATEVALUE(I36),"Yes","No"))</f>
+        <f>IF(I36="","",IFERROR(IF(TODAY()&gt;=DATEVALUE(I36),"Yes","No"),""))</f>
         <v/>
       </c>
       <c r="T36" s="14" t="n"/>
@@ -4363,7 +4387,7 @@
         </is>
       </c>
       <c r="S37" s="14">
-        <f>IF(I37="","",IF(TODAY()&gt;=DATEVALUE(I37),"Yes","No"))</f>
+        <f>IF(I37="","",IFERROR(IF(TODAY()&gt;=DATEVALUE(I37),"Yes","No"),""))</f>
         <v/>
       </c>
       <c r="T37" s="14" t="n"/>
@@ -4458,7 +4482,7 @@
         </is>
       </c>
       <c r="S38" s="14">
-        <f>IF(I38="","",IF(TODAY()&gt;=DATEVALUE(I38),"Yes","No"))</f>
+        <f>IF(I38="","",IFERROR(IF(TODAY()&gt;=DATEVALUE(I38),"Yes","No"),""))</f>
         <v/>
       </c>
       <c r="T38" s="14" t="n"/>
@@ -4553,7 +4577,7 @@
         </is>
       </c>
       <c r="S39" s="14">
-        <f>IF(I39="","",IF(TODAY()&gt;=DATEVALUE(I39),"Yes","No"))</f>
+        <f>IF(I39="","",IFERROR(IF(TODAY()&gt;=DATEVALUE(I39),"Yes","No"),""))</f>
         <v/>
       </c>
       <c r="T39" s="14" t="n"/>
@@ -4648,7 +4672,7 @@
         </is>
       </c>
       <c r="S40" s="14">
-        <f>IF(I40="","",IF(TODAY()&gt;=DATEVALUE(I40),"Yes","No"))</f>
+        <f>IF(I40="","",IFERROR(IF(TODAY()&gt;=DATEVALUE(I40),"Yes","No"),""))</f>
         <v/>
       </c>
       <c r="T40" s="14" t="n"/>
@@ -4743,7 +4767,7 @@
         </is>
       </c>
       <c r="S41" s="14">
-        <f>IF(I41="","",IF(TODAY()&gt;=DATEVALUE(I41),"Yes","No"))</f>
+        <f>IF(I41="","",IFERROR(IF(TODAY()&gt;=DATEVALUE(I41),"Yes","No"),""))</f>
         <v/>
       </c>
       <c r="T41" s="14" t="n"/>
@@ -4838,7 +4862,7 @@
         </is>
       </c>
       <c r="S42" s="14">
-        <f>IF(I42="","",IF(TODAY()&gt;=DATEVALUE(I42),"Yes","No"))</f>
+        <f>IF(I42="","",IFERROR(IF(TODAY()&gt;=DATEVALUE(I42),"Yes","No"),""))</f>
         <v/>
       </c>
       <c r="T42" s="14" t="n"/>
@@ -4933,7 +4957,7 @@
         </is>
       </c>
       <c r="S43" s="14">
-        <f>IF(I43="","",IF(TODAY()&gt;=DATEVALUE(I43),"Yes","No"))</f>
+        <f>IF(I43="","",IFERROR(IF(TODAY()&gt;=DATEVALUE(I43),"Yes","No"),""))</f>
         <v/>
       </c>
       <c r="T43" s="14" t="n"/>
@@ -5028,7 +5052,7 @@
         </is>
       </c>
       <c r="S44" s="14">
-        <f>IF(I44="","",IF(TODAY()&gt;=DATEVALUE(I44),"Yes","No"))</f>
+        <f>IF(I44="","",IFERROR(IF(TODAY()&gt;=DATEVALUE(I44),"Yes","No"),""))</f>
         <v/>
       </c>
       <c r="T44" s="14" t="n"/>
@@ -5123,7 +5147,7 @@
         </is>
       </c>
       <c r="S45" s="14">
-        <f>IF(I45="","",IF(TODAY()&gt;=DATEVALUE(I45),"Yes","No"))</f>
+        <f>IF(I45="","",IFERROR(IF(TODAY()&gt;=DATEVALUE(I45),"Yes","No"),""))</f>
         <v/>
       </c>
       <c r="T45" s="14" t="n"/>
@@ -5218,7 +5242,7 @@
         </is>
       </c>
       <c r="S46" s="14">
-        <f>IF(I46="","",IF(TODAY()&gt;=DATEVALUE(I46),"Yes","No"))</f>
+        <f>IF(I46="","",IFERROR(IF(TODAY()&gt;=DATEVALUE(I46),"Yes","No"),""))</f>
         <v/>
       </c>
       <c r="T46" s="14" t="n"/>
@@ -5313,7 +5337,7 @@
         </is>
       </c>
       <c r="S47" s="14">
-        <f>IF(I47="","",IF(TODAY()&gt;=DATEVALUE(I47),"Yes","No"))</f>
+        <f>IF(I47="","",IFERROR(IF(TODAY()&gt;=DATEVALUE(I47),"Yes","No"),""))</f>
         <v/>
       </c>
       <c r="T47" s="14" t="n"/>
@@ -5408,7 +5432,7 @@
         </is>
       </c>
       <c r="S48" s="14">
-        <f>IF(I48="","",IF(TODAY()&gt;=DATEVALUE(I48),"Yes","No"))</f>
+        <f>IF(I48="","",IFERROR(IF(TODAY()&gt;=DATEVALUE(I48),"Yes","No"),""))</f>
         <v/>
       </c>
       <c r="T48" s="14" t="n"/>
@@ -5503,7 +5527,7 @@
         </is>
       </c>
       <c r="S49" s="14">
-        <f>IF(I49="","",IF(TODAY()&gt;=DATEVALUE(I49),"Yes","No"))</f>
+        <f>IF(I49="","",IFERROR(IF(TODAY()&gt;=DATEVALUE(I49),"Yes","No"),""))</f>
         <v/>
       </c>
       <c r="T49" s="15" t="inlineStr">
@@ -5602,7 +5626,7 @@
         </is>
       </c>
       <c r="S50" s="14">
-        <f>IF(I50="","",IF(TODAY()&gt;=DATEVALUE(I50),"Yes","No"))</f>
+        <f>IF(I50="","",IFERROR(IF(TODAY()&gt;=DATEVALUE(I50),"Yes","No"),""))</f>
         <v/>
       </c>
       <c r="T50" s="14" t="n"/>
@@ -5697,10 +5721,14 @@
         </is>
       </c>
       <c r="S51" s="14">
-        <f>IF(I51="","",IF(TODAY()&gt;=DATEVALUE(I51),"Yes","No"))</f>
+        <f>IF(I51="","",IFERROR(IF(TODAY()&gt;=DATEVALUE(I51),"Yes","No"),""))</f>
         <v/>
       </c>
-      <c r="T51" s="14" t="n"/>
+      <c r="T51" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-30 (CHG-0100) (+1 earlier)</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="12" t="inlineStr">
@@ -5792,7 +5820,7 @@
         </is>
       </c>
       <c r="S52" s="14">
-        <f>IF(I52="","",IF(TODAY()&gt;=DATEVALUE(I52),"Yes","No"))</f>
+        <f>IF(I52="","",IFERROR(IF(TODAY()&gt;=DATEVALUE(I52),"Yes","No"),""))</f>
         <v/>
       </c>
       <c r="T52" s="14" t="n"/>
@@ -5887,7 +5915,7 @@
         </is>
       </c>
       <c r="S53" s="14">
-        <f>IF(I53="","",IF(TODAY()&gt;=DATEVALUE(I53),"Yes","No"))</f>
+        <f>IF(I53="","",IFERROR(IF(TODAY()&gt;=DATEVALUE(I53),"Yes","No"),""))</f>
         <v/>
       </c>
       <c r="T53" s="14" t="n"/>
@@ -5982,7 +6010,7 @@
         </is>
       </c>
       <c r="S54" s="14">
-        <f>IF(I54="","",IF(TODAY()&gt;=DATEVALUE(I54),"Yes","No"))</f>
+        <f>IF(I54="","",IFERROR(IF(TODAY()&gt;=DATEVALUE(I54),"Yes","No"),""))</f>
         <v/>
       </c>
       <c r="T54" s="14" t="n"/>
@@ -6077,7 +6105,7 @@
         </is>
       </c>
       <c r="S55" s="14">
-        <f>IF(I55="","",IF(TODAY()&gt;=DATEVALUE(I55),"Yes","No"))</f>
+        <f>IF(I55="","",IFERROR(IF(TODAY()&gt;=DATEVALUE(I55),"Yes","No"),""))</f>
         <v/>
       </c>
       <c r="T55" s="14" t="n"/>
@@ -6172,7 +6200,7 @@
         </is>
       </c>
       <c r="S56" s="14">
-        <f>IF(I56="","",IF(TODAY()&gt;=DATEVALUE(I56),"Yes","No"))</f>
+        <f>IF(I56="","",IFERROR(IF(TODAY()&gt;=DATEVALUE(I56),"Yes","No"),""))</f>
         <v/>
       </c>
       <c r="T56" s="14" t="n"/>
@@ -6267,10 +6295,14 @@
         </is>
       </c>
       <c r="S57" s="14">
-        <f>IF(I57="","",IF(TODAY()&gt;=DATEVALUE(I57),"Yes","No"))</f>
+        <f>IF(I57="","",IFERROR(IF(TODAY()&gt;=DATEVALUE(I57),"Yes","No"),""))</f>
         <v/>
       </c>
-      <c r="T57" s="14" t="n"/>
+      <c r="T57" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-30 (CHG-0102) (+1 earlier)</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="12" t="inlineStr">
@@ -6362,7 +6394,7 @@
         </is>
       </c>
       <c r="S58" s="14">
-        <f>IF(I58="","",IF(TODAY()&gt;=DATEVALUE(I58),"Yes","No"))</f>
+        <f>IF(I58="","",IFERROR(IF(TODAY()&gt;=DATEVALUE(I58),"Yes","No"),""))</f>
         <v/>
       </c>
       <c r="T58" s="14" t="n"/>
@@ -6415,7 +6447,7 @@
       </c>
       <c r="J59" s="12" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="K59" s="12" t="inlineStr">
@@ -6448,7 +6480,7 @@
       </c>
       <c r="Q59" s="12" t="inlineStr">
         <is>
-          <t>CHG-0030</t>
+          <t>CHG-0097</t>
         </is>
       </c>
       <c r="R59" s="12" t="inlineStr">
@@ -6457,7 +6489,7 @@
         </is>
       </c>
       <c r="S59" s="14">
-        <f>IF(I59="","",IF(TODAY()&gt;=DATEVALUE(I59),"Yes","No"))</f>
+        <f>IF(I59="","",IFERROR(IF(TODAY()&gt;=DATEVALUE(I59),"Yes","No"),""))</f>
         <v/>
       </c>
       <c r="T59" s="14" t="n"/>
@@ -6552,7 +6584,7 @@
         </is>
       </c>
       <c r="S60" s="14">
-        <f>IF(I60="","",IF(TODAY()&gt;=DATEVALUE(I60),"Yes","No"))</f>
+        <f>IF(I60="","",IFERROR(IF(TODAY()&gt;=DATEVALUE(I60),"Yes","No"),""))</f>
         <v/>
       </c>
       <c r="T60" s="14" t="n"/>
@@ -6605,7 +6637,7 @@
       </c>
       <c r="J61" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="K61" s="12" t="inlineStr">
@@ -6638,7 +6670,7 @@
       </c>
       <c r="Q61" s="12" t="inlineStr">
         <is>
-          <t>CHG-0031</t>
+          <t>CHG-0098</t>
         </is>
       </c>
       <c r="R61" s="12" t="inlineStr">
@@ -6647,7 +6679,7 @@
         </is>
       </c>
       <c r="S61" s="14">
-        <f>IF(I61="","",IF(TODAY()&gt;=DATEVALUE(I61),"Yes","No"))</f>
+        <f>IF(I61="","",IFERROR(IF(TODAY()&gt;=DATEVALUE(I61),"Yes","No"),""))</f>
         <v/>
       </c>
       <c r="T61" s="14" t="n"/>
@@ -6742,7 +6774,7 @@
         </is>
       </c>
       <c r="S62" s="14">
-        <f>IF(I62="","",IF(TODAY()&gt;=DATEVALUE(I62),"Yes","No"))</f>
+        <f>IF(I62="","",IFERROR(IF(TODAY()&gt;=DATEVALUE(I62),"Yes","No"),""))</f>
         <v/>
       </c>
       <c r="T62" s="14" t="n"/>
@@ -6795,7 +6827,7 @@
       </c>
       <c r="J63" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="K63" s="12" t="inlineStr">
@@ -6828,7 +6860,7 @@
       </c>
       <c r="Q63" s="12" t="inlineStr">
         <is>
-          <t>CHG-0032</t>
+          <t>CHG-0096</t>
         </is>
       </c>
       <c r="R63" s="12" t="inlineStr">
@@ -6837,7 +6869,7 @@
         </is>
       </c>
       <c r="S63" s="14">
-        <f>IF(I63="","",IF(TODAY()&gt;=DATEVALUE(I63),"Yes","No"))</f>
+        <f>IF(I63="","",IFERROR(IF(TODAY()&gt;=DATEVALUE(I63),"Yes","No"),""))</f>
         <v/>
       </c>
       <c r="T63" s="14" t="n"/>
@@ -6932,7 +6964,7 @@
         </is>
       </c>
       <c r="S64" s="14">
-        <f>IF(I64="","",IF(TODAY()&gt;=DATEVALUE(I64),"Yes","No"))</f>
+        <f>IF(I64="","",IFERROR(IF(TODAY()&gt;=DATEVALUE(I64),"Yes","No"),""))</f>
         <v/>
       </c>
       <c r="T64" s="14" t="n"/>
@@ -7027,7 +7059,7 @@
         </is>
       </c>
       <c r="S65" s="14">
-        <f>IF(I65="","",IF(TODAY()&gt;=DATEVALUE(I65),"Yes","No"))</f>
+        <f>IF(I65="","",IFERROR(IF(TODAY()&gt;=DATEVALUE(I65),"Yes","No"),""))</f>
         <v/>
       </c>
       <c r="T65" s="14" t="n"/>
@@ -7122,7 +7154,7 @@
         </is>
       </c>
       <c r="S66" s="14">
-        <f>IF(I66="","",IF(TODAY()&gt;=DATEVALUE(I66),"Yes","No"))</f>
+        <f>IF(I66="","",IFERROR(IF(TODAY()&gt;=DATEVALUE(I66),"Yes","No"),""))</f>
         <v/>
       </c>
       <c r="T66" s="14" t="n"/>
@@ -7217,7 +7249,7 @@
         </is>
       </c>
       <c r="S67" s="14">
-        <f>IF(I67="","",IF(TODAY()&gt;=DATEVALUE(I67),"Yes","No"))</f>
+        <f>IF(I67="","",IFERROR(IF(TODAY()&gt;=DATEVALUE(I67),"Yes","No"),""))</f>
         <v/>
       </c>
       <c r="T67" s="14" t="n"/>
@@ -7312,7 +7344,7 @@
         </is>
       </c>
       <c r="S68" s="14">
-        <f>IF(I68="","",IF(TODAY()&gt;=DATEVALUE(I68),"Yes","No"))</f>
+        <f>IF(I68="","",IFERROR(IF(TODAY()&gt;=DATEVALUE(I68),"Yes","No"),""))</f>
         <v/>
       </c>
       <c r="T68" s="14" t="n"/>
@@ -7407,7 +7439,7 @@
         </is>
       </c>
       <c r="S69" s="14">
-        <f>IF(I69="","",IF(TODAY()&gt;=DATEVALUE(I69),"Yes","No"))</f>
+        <f>IF(I69="","",IFERROR(IF(TODAY()&gt;=DATEVALUE(I69),"Yes","No"),""))</f>
         <v/>
       </c>
       <c r="T69" s="14" t="n"/>
@@ -7502,7 +7534,7 @@
         </is>
       </c>
       <c r="S70" s="14">
-        <f>IF(I70="","",IF(TODAY()&gt;=DATEVALUE(I70),"Yes","No"))</f>
+        <f>IF(I70="","",IFERROR(IF(TODAY()&gt;=DATEVALUE(I70),"Yes","No"),""))</f>
         <v/>
       </c>
       <c r="T70" s="14" t="n"/>
@@ -7597,7 +7629,7 @@
         </is>
       </c>
       <c r="S71" s="14">
-        <f>IF(I71="","",IF(TODAY()&gt;=DATEVALUE(I71),"Yes","No"))</f>
+        <f>IF(I71="","",IFERROR(IF(TODAY()&gt;=DATEVALUE(I71),"Yes","No"),""))</f>
         <v/>
       </c>
       <c r="T71" s="14" t="n"/>
@@ -7692,7 +7724,7 @@
         </is>
       </c>
       <c r="S72" s="14">
-        <f>IF(I72="","",IF(TODAY()&gt;=DATEVALUE(I72),"Yes","No"))</f>
+        <f>IF(I72="","",IFERROR(IF(TODAY()&gt;=DATEVALUE(I72),"Yes","No"),""))</f>
         <v/>
       </c>
       <c r="T72" s="14" t="n"/>
@@ -7787,7 +7819,7 @@
         </is>
       </c>
       <c r="S73" s="14">
-        <f>IF(I73="","",IF(TODAY()&gt;=DATEVALUE(I73),"Yes","No"))</f>
+        <f>IF(I73="","",IFERROR(IF(TODAY()&gt;=DATEVALUE(I73),"Yes","No"),""))</f>
         <v/>
       </c>
       <c r="T73" s="14" t="n"/>
@@ -7882,7 +7914,7 @@
         </is>
       </c>
       <c r="S74" s="14">
-        <f>IF(I74="","",IF(TODAY()&gt;=DATEVALUE(I74),"Yes","No"))</f>
+        <f>IF(I74="","",IFERROR(IF(TODAY()&gt;=DATEVALUE(I74),"Yes","No"),""))</f>
         <v/>
       </c>
       <c r="T74" s="14" t="n"/>
@@ -7977,7 +8009,7 @@
         </is>
       </c>
       <c r="S75" s="14">
-        <f>IF(I75="","",IF(TODAY()&gt;=DATEVALUE(I75),"Yes","No"))</f>
+        <f>IF(I75="","",IFERROR(IF(TODAY()&gt;=DATEVALUE(I75),"Yes","No"),""))</f>
         <v/>
       </c>
       <c r="T75" s="14" t="n"/>
@@ -8072,7 +8104,7 @@
         </is>
       </c>
       <c r="S76" s="14">
-        <f>IF(I76="","",IF(TODAY()&gt;=DATEVALUE(I76),"Yes","No"))</f>
+        <f>IF(I76="","",IFERROR(IF(TODAY()&gt;=DATEVALUE(I76),"Yes","No"),""))</f>
         <v/>
       </c>
       <c r="T76" s="14" t="n"/>
@@ -8167,7 +8199,7 @@
         </is>
       </c>
       <c r="S77" s="14">
-        <f>IF(I77="","",IF(TODAY()&gt;=DATEVALUE(I77),"Yes","No"))</f>
+        <f>IF(I77="","",IFERROR(IF(TODAY()&gt;=DATEVALUE(I77),"Yes","No"),""))</f>
         <v/>
       </c>
       <c r="T77" s="14" t="n"/>
@@ -8262,7 +8294,7 @@
         </is>
       </c>
       <c r="S78" s="14">
-        <f>IF(I78="","",IF(TODAY()&gt;=DATEVALUE(I78),"Yes","No"))</f>
+        <f>IF(I78="","",IFERROR(IF(TODAY()&gt;=DATEVALUE(I78),"Yes","No"),""))</f>
         <v/>
       </c>
       <c r="T78" s="14" t="n"/>
@@ -8357,7 +8389,7 @@
         </is>
       </c>
       <c r="S79" s="14">
-        <f>IF(I79="","",IF(TODAY()&gt;=DATEVALUE(I79),"Yes","No"))</f>
+        <f>IF(I79="","",IFERROR(IF(TODAY()&gt;=DATEVALUE(I79),"Yes","No"),""))</f>
         <v/>
       </c>
       <c r="T79" s="14" t="n"/>
@@ -8452,7 +8484,7 @@
         </is>
       </c>
       <c r="S80" s="14">
-        <f>IF(I80="","",IF(TODAY()&gt;=DATEVALUE(I80),"Yes","No"))</f>
+        <f>IF(I80="","",IFERROR(IF(TODAY()&gt;=DATEVALUE(I80),"Yes","No"),""))</f>
         <v/>
       </c>
       <c r="T80" s="14" t="n"/>
@@ -8563,7 +8595,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P143"/>
+  <dimension ref="A1:P150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -19603,6 +19635,510 @@
       <c r="P143" s="12" t="inlineStr">
         <is>
           <t>Summary-only data-quality fix (not a regulatory change; never highlighted). Basis: Rule 12(1),(2): 'The provisions of sub-sections (1) and (3) of section 9 of the Act shall not be applicable'</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="12" t="inlineStr">
+        <is>
+          <t>CHG-0096</t>
+        </is>
+      </c>
+      <c r="B144" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-30T16:24:09.544218+00:00</t>
+        </is>
+      </c>
+      <c r="C144" s="12" t="inlineStr">
+        <is>
+          <t>DPDPR-SCH7</t>
+        </is>
+      </c>
+      <c r="D144" s="12" t="inlineStr">
+        <is>
+          <t>Correction</t>
+        </is>
+      </c>
+      <c r="E144" s="12" t="inlineStr">
+        <is>
+          <t>data_correction</t>
+        </is>
+      </c>
+      <c r="F144" s="12" t="inlineStr">
+        <is>
+          <t>Text as this project stored it</t>
+        </is>
+      </c>
+      <c r="G144" s="12" t="inlineStr">
+        <is>
+          <t>Text as the official Gazette prints it</t>
+        </is>
+      </c>
+      <c r="H144" s="12" t="inlineStr">
+        <is>
+          <t>DPDP Rules 2025, official Gazette PDF (G.S.R. 846(E), 13 Nov 2025)</t>
+        </is>
+      </c>
+      <c r="I144" s="12" t="inlineStr">
+        <is>
+          <t>https://www.meity.gov.in/static/uploads/2025/11/53450e6e5dc0bfa85ebd78686cadad39.pdf</t>
+        </is>
+      </c>
+      <c r="J144" s="12" t="inlineStr">
+        <is>
+          <t>manual:audit-2026-09-30-verbatim-restore (wording read by code from the official PDF)</t>
+        </is>
+      </c>
+      <c r="K144" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L144" s="12" t="inlineStr">
+        <is>
+          <t>Pending Review</t>
+        </is>
+      </c>
+      <c r="M144" s="12" t="n"/>
+      <c r="N144" s="12" t="n"/>
+      <c r="O144" s="12" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P144" s="12" t="inlineStr">
+        <is>
+          <t>Our own paraphrase corrected: five words of enacted text ('for the following purposes, namely: —') had been replaced by a colon. Restored verbatim from the official Rules PDF, page 41. Audit finding H-7.</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="12" t="inlineStr">
+        <is>
+          <t>CHG-0097</t>
+        </is>
+      </c>
+      <c r="B145" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-30T16:24:09.544218+00:00</t>
+        </is>
+      </c>
+      <c r="C145" s="12" t="inlineStr">
+        <is>
+          <t>DPDPR-SCH5</t>
+        </is>
+      </c>
+      <c r="D145" s="12" t="inlineStr">
+        <is>
+          <t>Correction</t>
+        </is>
+      </c>
+      <c r="E145" s="12" t="inlineStr">
+        <is>
+          <t>data_correction</t>
+        </is>
+      </c>
+      <c r="F145" s="12" t="inlineStr">
+        <is>
+          <t>Text as this project stored it</t>
+        </is>
+      </c>
+      <c r="G145" s="12" t="inlineStr">
+        <is>
+          <t>Text as the official Gazette prints it</t>
+        </is>
+      </c>
+      <c r="H145" s="12" t="inlineStr">
+        <is>
+          <t>DPDP Rules 2025, official Gazette PDF (G.S.R. 846(E), 13 Nov 2025)</t>
+        </is>
+      </c>
+      <c r="I145" s="12" t="inlineStr">
+        <is>
+          <t>https://www.meity.gov.in/static/uploads/2025/11/53450e6e5dc0bfa85ebd78686cadad39.pdf</t>
+        </is>
+      </c>
+      <c r="J145" s="12" t="inlineStr">
+        <is>
+          <t>manual:audit-2026-09-30-verbatim-restore (wording read by code from the official PDF)</t>
+        </is>
+      </c>
+      <c r="K145" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L145" s="12" t="inlineStr">
+        <is>
+          <t>Pending Review</t>
+        </is>
+      </c>
+      <c r="M145" s="12" t="n"/>
+      <c r="N145" s="12" t="n"/>
+      <c r="O145" s="12" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P145" s="12" t="inlineStr">
+        <is>
+          <t>Our own omission corrected: the Gazette prints a separator dash after each of the 8 numbered paragraph headings in the Fifth Schedule ("1. Salary. — (1) ..."); the database dropped them. Pure insertion — no word was added, removed or changed. Restored from the official Rules PDF. Audit finding M-11.</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="12" t="inlineStr">
+        <is>
+          <t>CHG-0098</t>
+        </is>
+      </c>
+      <c r="B146" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-30T16:24:09.544218+00:00</t>
+        </is>
+      </c>
+      <c r="C146" s="12" t="inlineStr">
+        <is>
+          <t>DPDPR-SCH6</t>
+        </is>
+      </c>
+      <c r="D146" s="12" t="inlineStr">
+        <is>
+          <t>Correction</t>
+        </is>
+      </c>
+      <c r="E146" s="12" t="inlineStr">
+        <is>
+          <t>data_correction</t>
+        </is>
+      </c>
+      <c r="F146" s="12" t="inlineStr">
+        <is>
+          <t>Text as this project stored it</t>
+        </is>
+      </c>
+      <c r="G146" s="12" t="inlineStr">
+        <is>
+          <t>Text as the official Gazette prints it</t>
+        </is>
+      </c>
+      <c r="H146" s="12" t="inlineStr">
+        <is>
+          <t>DPDP Rules 2025, official Gazette PDF (G.S.R. 846(E), 13 Nov 2025)</t>
+        </is>
+      </c>
+      <c r="I146" s="12" t="inlineStr">
+        <is>
+          <t>https://www.meity.gov.in/static/uploads/2025/11/53450e6e5dc0bfa85ebd78686cadad39.pdf</t>
+        </is>
+      </c>
+      <c r="J146" s="12" t="inlineStr">
+        <is>
+          <t>manual:audit-2026-09-30-verbatim-restore (wording read by code from the official PDF)</t>
+        </is>
+      </c>
+      <c r="K146" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L146" s="12" t="inlineStr">
+        <is>
+          <t>Pending Review</t>
+        </is>
+      </c>
+      <c r="M146" s="12" t="n"/>
+      <c r="N146" s="12" t="n"/>
+      <c r="O146" s="12" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P146" s="12" t="inlineStr">
+        <is>
+          <t>Our own omission corrected: the Gazette prints a separator dash after each of the 7 numbered paragraph headings in the Sixth Schedule ("1. Salary. — (1) ..."); the database dropped them. Pure insertion — no word was added, removed or changed. Restored from the official Rules PDF. Audit finding M-11.</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="16" t="inlineStr">
+        <is>
+          <t>CHG-0099</t>
+        </is>
+      </c>
+      <c r="B147" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-30T16:24:18.512788+00:00</t>
+        </is>
+      </c>
+      <c r="C147" s="16" t="inlineStr">
+        <is>
+          <t>DPDPR-SCH1</t>
+        </is>
+      </c>
+      <c r="D147" s="16" t="inlineStr">
+        <is>
+          <t>Correction</t>
+        </is>
+      </c>
+      <c r="E147" s="16" t="inlineStr">
+        <is>
+          <t>regulatory</t>
+        </is>
+      </c>
+      <c r="F147" s="16" t="inlineStr">
+        <is>
+          <t>Text as originally gazetted in G.S.R. 846(E)</t>
+        </is>
+      </c>
+      <c r="G147" s="16" t="inlineStr">
+        <is>
+          <t>Text as corrected by G.S.R. 892(E)</t>
+        </is>
+      </c>
+      <c r="H147" s="16" t="inlineStr">
+        <is>
+          <t>Corrigenda G.S.R. 892(E), 10 Dec 2025 (Gazette Extraordinary No. 806, 11 Dec 2025)</t>
+        </is>
+      </c>
+      <c r="I147" s="16" t="inlineStr">
+        <is>
+          <t>https://www.meity.gov.in/static/uploads/2025/12/3c7ebbae0e5456f493f486e6845df86b.pdf</t>
+        </is>
+      </c>
+      <c r="J147" s="16" t="inlineStr">
+        <is>
+          <t>manual:audit-2026-09-30-corrigendum-schedules (phrase pairs extracted by code from the corrigendum PDF)</t>
+        </is>
+      </c>
+      <c r="K147" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L147" s="16" t="inlineStr">
+        <is>
+          <t>Pending Review</t>
+        </is>
+      </c>
+      <c r="M147" s="16" t="n"/>
+      <c r="N147" s="16" t="n"/>
+      <c r="O147" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P147" s="16" t="inlineStr">
+        <is>
+          <t>Government corrigendum (regulatory change), G.S.R. 892(E) item (iv)(a). Recorded on 30 Sep 2026 to correct audit finding H-5: this item was previously folded into a change_origin='data_correction' row, so a real act of government was never highlighted or reported. provisions.full_text is unchanged — it already carries the correction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="16" t="inlineStr">
+        <is>
+          <t>CHG-0100</t>
+        </is>
+      </c>
+      <c r="B148" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-30T16:24:18.512788+00:00</t>
+        </is>
+      </c>
+      <c r="C148" s="16" t="inlineStr">
+        <is>
+          <t>DPDPR-SCH1</t>
+        </is>
+      </c>
+      <c r="D148" s="16" t="inlineStr">
+        <is>
+          <t>Correction</t>
+        </is>
+      </c>
+      <c r="E148" s="16" t="inlineStr">
+        <is>
+          <t>regulatory</t>
+        </is>
+      </c>
+      <c r="F148" s="16" t="inlineStr">
+        <is>
+          <t>Text as originally gazetted in G.S.R. 846(E)</t>
+        </is>
+      </c>
+      <c r="G148" s="16" t="inlineStr">
+        <is>
+          <t>Text as corrected by G.S.R. 892(E)</t>
+        </is>
+      </c>
+      <c r="H148" s="16" t="inlineStr">
+        <is>
+          <t>Corrigenda G.S.R. 892(E), 10 Dec 2025 (Gazette Extraordinary No. 806, 11 Dec 2025)</t>
+        </is>
+      </c>
+      <c r="I148" s="16" t="inlineStr">
+        <is>
+          <t>https://www.meity.gov.in/static/uploads/2025/12/3c7ebbae0e5456f493f486e6845df86b.pdf</t>
+        </is>
+      </c>
+      <c r="J148" s="16" t="inlineStr">
+        <is>
+          <t>manual:audit-2026-09-30-corrigendum-schedules (phrase pairs extracted by code from the corrigendum PDF)</t>
+        </is>
+      </c>
+      <c r="K148" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L148" s="16" t="inlineStr">
+        <is>
+          <t>Pending Review</t>
+        </is>
+      </c>
+      <c r="M148" s="16" t="n"/>
+      <c r="N148" s="16" t="n"/>
+      <c r="O148" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P148" s="16" t="inlineStr">
+        <is>
+          <t>Government corrigendum (regulatory change), G.S.R. 892(E) item (iv)(b). Recorded on 30 Sep 2026 to correct audit finding H-5: this item was previously folded into a change_origin='data_correction' row, so a real act of government was never highlighted or reported. provisions.full_text is unchanged — it already carries the correction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="16" t="inlineStr">
+        <is>
+          <t>CHG-0101</t>
+        </is>
+      </c>
+      <c r="B149" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-30T16:24:18.512788+00:00</t>
+        </is>
+      </c>
+      <c r="C149" s="16" t="inlineStr">
+        <is>
+          <t>DPDPR-SCH4</t>
+        </is>
+      </c>
+      <c r="D149" s="16" t="inlineStr">
+        <is>
+          <t>Correction</t>
+        </is>
+      </c>
+      <c r="E149" s="16" t="inlineStr">
+        <is>
+          <t>regulatory</t>
+        </is>
+      </c>
+      <c r="F149" s="16" t="inlineStr">
+        <is>
+          <t>Text as originally gazetted in G.S.R. 846(E)</t>
+        </is>
+      </c>
+      <c r="G149" s="16" t="inlineStr">
+        <is>
+          <t>Text as corrected by G.S.R. 892(E)</t>
+        </is>
+      </c>
+      <c r="H149" s="16" t="inlineStr">
+        <is>
+          <t>Corrigenda G.S.R. 892(E), 10 Dec 2025 (Gazette Extraordinary No. 806, 11 Dec 2025)</t>
+        </is>
+      </c>
+      <c r="I149" s="16" t="inlineStr">
+        <is>
+          <t>https://www.meity.gov.in/static/uploads/2025/12/3c7ebbae0e5456f493f486e6845df86b.pdf</t>
+        </is>
+      </c>
+      <c r="J149" s="16" t="inlineStr">
+        <is>
+          <t>manual:audit-2026-09-30-corrigendum-schedules (phrase pairs extracted by code from the corrigendum PDF)</t>
+        </is>
+      </c>
+      <c r="K149" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L149" s="16" t="inlineStr">
+        <is>
+          <t>Pending Review</t>
+        </is>
+      </c>
+      <c r="M149" s="16" t="n"/>
+      <c r="N149" s="16" t="n"/>
+      <c r="O149" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P149" s="16" t="inlineStr">
+        <is>
+          <t>Government corrigendum (regulatory change), G.S.R. 892(E) item (v)(a). Recorded on 30 Sep 2026 to correct audit finding H-5: this item was previously folded into a change_origin='data_correction' row, so a real act of government was never highlighted or reported. provisions.full_text is unchanged — it already carries the correction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="16" t="inlineStr">
+        <is>
+          <t>CHG-0102</t>
+        </is>
+      </c>
+      <c r="B150" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-30T16:24:18.512788+00:00</t>
+        </is>
+      </c>
+      <c r="C150" s="16" t="inlineStr">
+        <is>
+          <t>DPDPR-SCH4</t>
+        </is>
+      </c>
+      <c r="D150" s="16" t="inlineStr">
+        <is>
+          <t>Correction</t>
+        </is>
+      </c>
+      <c r="E150" s="16" t="inlineStr">
+        <is>
+          <t>regulatory</t>
+        </is>
+      </c>
+      <c r="F150" s="16" t="inlineStr">
+        <is>
+          <t>Text as originally gazetted in G.S.R. 846(E)</t>
+        </is>
+      </c>
+      <c r="G150" s="16" t="inlineStr">
+        <is>
+          <t>Text as corrected by G.S.R. 892(E)</t>
+        </is>
+      </c>
+      <c r="H150" s="16" t="inlineStr">
+        <is>
+          <t>Corrigenda G.S.R. 892(E), 10 Dec 2025 (Gazette Extraordinary No. 806, 11 Dec 2025)</t>
+        </is>
+      </c>
+      <c r="I150" s="16" t="inlineStr">
+        <is>
+          <t>https://www.meity.gov.in/static/uploads/2025/12/3c7ebbae0e5456f493f486e6845df86b.pdf</t>
+        </is>
+      </c>
+      <c r="J150" s="16" t="inlineStr">
+        <is>
+          <t>manual:audit-2026-09-30-corrigendum-schedules (phrase pairs extracted by code from the corrigendum PDF)</t>
+        </is>
+      </c>
+      <c r="K150" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L150" s="16" t="inlineStr">
+        <is>
+          <t>Pending Review</t>
+        </is>
+      </c>
+      <c r="M150" s="16" t="n"/>
+      <c r="N150" s="16" t="n"/>
+      <c r="O150" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P150" s="16" t="inlineStr">
+        <is>
+          <t>Government corrigendum (regulatory change), G.S.R. 892(E) item (v)(b). Recorded on 30 Sep 2026 to correct audit finding H-5: this item was previously folded into a change_origin='data_correction' row, so a real act of government was never highlighted or reported. provisions.full_text is unchanged — it already carries the correction.</t>
         </is>
       </c>
     </row>
@@ -19631,7 +20167,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -19695,80 +20231,76 @@
     <row r="2">
       <c r="A2" s="12" t="inlineStr">
         <is>
-          <t>SRC-0003</t>
+          <t>SRC-0001</t>
         </is>
       </c>
       <c r="B2" s="12" t="inlineStr">
         <is>
-          <t>eGazette</t>
+          <t>MeitY</t>
         </is>
       </c>
       <c r="C2" s="12" t="inlineStr">
         <is>
-          <t>Gazette Notification G.S.R. 843(E), 13 Nov 2025 (Act commencement schedule)</t>
+          <t>DPDP Rules, 2025 — MeitY PDF (G.S.R. 846(E))</t>
         </is>
       </c>
       <c r="D2" s="12" t="inlineStr">
         <is>
-          <t>https://www.meity.gov.in/static/uploads/2025/11/c56ceae6c383460ca69577428d36828b.pdf</t>
-        </is>
-      </c>
-      <c r="E2" s="12" t="inlineStr">
-        <is>
-          <t>2025-11-13</t>
-        </is>
-      </c>
+          <t>https://www.meity.gov.in/static/uploads/2025/11/53450e6e5dc0bfa85ebd78686cadad39.pdf</t>
+        </is>
+      </c>
+      <c r="E2" s="12" t="n"/>
       <c r="F2" s="12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G2" s="12" t="inlineStr">
         <is>
-          <t>manual-seed-not-hashed</t>
+          <t>76094c7228c8dbff357281552fa2b052fe363303eb8b2c33ee5361d38883070d</t>
         </is>
       </c>
       <c r="H2" s="12" t="inlineStr">
         <is>
-          <t>Processed</t>
+          <t>No Change Detected</t>
         </is>
       </c>
       <c r="I2" s="12" t="inlineStr">
         <is>
-          <t>CHG-A0001,CHG-A0002,CHG-A0003,CHG-A0004,CHG-A0005,CHG-A0006,CHG-A0007,CHG-A0008,CHG-A0009,CHG-A0010,CHG-A0011,CHG-A0012,CHG-A0013,CHG-A0014,CHG-A0015,CHG-A0016,CHG-A0017,CHG-A0018,CHG-A0019,CHG-A0020,CHG-A0021,CHG-A0022,CHG-A0023,CHG-A0024,CHG-A0025,CHG-A0026,CHG-A0027,CHG-A0028,CHG-A0029,CHG-A0030,CHG-A0031,CHG-A0032,CHG-A0033,CHG-A0034,CHG-A0035,CHG-A0036,CHG-A0037,CHG-A0038,CHG-A0039,CHG-A0040,CHG-A0041,CHG-A0042,CHG-A0043,CHG-A0044,CHG-A0045,CHG-A0046,CHG-A0047,CHG-A0048</t>
+          <t>CHG-0002,CHG-0003,CHG-0004,CHG-0005,CHG-0006,CHG-0007,CHG-0008,CHG-0009,CHG-0010,CHG-0011,CHG-0012,CHG-0013,CHG-0014,CHG-0015,CHG-0016,CHG-0017,CHG-0018,CHG-0019,CHG-0020,CHG-0021,CHG-0022,CHG-0023,CHG-0024,CHG-0025,CHG-0026,CHG-0027,CHG-0028,CHG-0029,CHG-0030,CHG-0031,CHG-0032</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="12" t="inlineStr">
         <is>
-          <t>SRC-0004</t>
+          <t>SRC-0002</t>
         </is>
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>PIB</t>
+          <t>MeitY</t>
         </is>
       </c>
       <c r="C3" s="12" t="inlineStr">
         <is>
-          <t>PIB — All Press Releases (English)</t>
+          <t>DPDP Act, 2023 — MeitY PDF</t>
         </is>
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/allRel.aspx</t>
+          <t>https://www.meity.gov.in/static/uploads/2024/06/2bf1f0e9f04e6fb4f8fef35e82c42aa5.pdf</t>
         </is>
       </c>
       <c r="E3" s="12" t="n"/>
       <c r="F3" s="12" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G3" s="12" t="inlineStr">
         <is>
-          <t>d38842055f43a4f6ee39929156a2c93772a0b128ba3ab14f887a64fcf1c77e89</t>
+          <t>f15bda1ff8065c68f8e1cc57c50616264afeb49d72cfc48d1e92a2a3c473c1d2</t>
         </is>
       </c>
       <c r="H3" s="12" t="inlineStr">
@@ -19776,218 +20308,50 @@
           <t>No Change Detected</t>
         </is>
       </c>
-      <c r="I3" s="12" t="n"/>
+      <c r="I3" s="12" t="inlineStr">
+        <is>
+          <t>CHG-A0001,CHG-A0002,CHG-A0003,CHG-A0004,CHG-A0005,CHG-A0006,CHG-A0007,CHG-A0008,CHG-A0009,CHG-A0010,CHG-A0011,CHG-A0012,CHG-A0013,CHG-A0014,CHG-A0015,CHG-A0016,CHG-A0017,CHG-A0018,CHG-A0019,CHG-A0020,CHG-A0021,CHG-A0022,CHG-A0023,CHG-A0024,CHG-A0025,CHG-A0026,CHG-A0027,CHG-A0028,CHG-A0029,CHG-A0030,CHG-A0031,CHG-A0032,CHG-A0033,CHG-A0034,CHG-A0035,CHG-A0036,CHG-A0037,CHG-A0038,CHG-A0039,CHG-A0040,CHG-A0041,CHG-A0042,CHG-A0043,CHG-A0044,CHG-A0045,CHG-A0046,CHG-A0047,CHG-A0048</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="12" t="inlineStr">
         <is>
-          <t>SRC-0006</t>
+          <t>SRC-0007</t>
         </is>
       </c>
       <c r="B4" s="12" t="inlineStr">
         <is>
-          <t>MeitY</t>
+          <t>PIB</t>
         </is>
       </c>
       <c r="C4" s="12" t="inlineStr">
         <is>
-          <t>Corrigenda G.S.R. 892(E), 10 Dec 2025 (Gazette Extraordinary No. 806, 11 Dec 2025)</t>
+          <t>PIB — All Press Releases RSS (English, national)</t>
         </is>
       </c>
       <c r="D4" s="12" t="inlineStr">
         <is>
-          <t>https://www.meity.gov.in/static/uploads/2025/12/3c7ebbae0e5456f493f486e6845df86b.pdf</t>
-        </is>
-      </c>
-      <c r="E4" s="12" t="inlineStr">
-        <is>
-          <t>2025-12-11</t>
-        </is>
-      </c>
+          <t>https://www.pib.gov.in/RssMain.aspx?ModId=6&amp;Mid=0&amp;reg=3&amp;lang=1</t>
+        </is>
+      </c>
+      <c r="E4" s="12" t="n"/>
       <c r="F4" s="12" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G4" s="12" t="inlineStr">
         <is>
-          <t>597d69e0d16cc9eeb72d1799195fe4a1b5fe4e2f3cb063310864736b39d3c244</t>
+          <t>7f21b9fb049520cfc9c843e19656e076159b542bbc931a5850920e7e89b81eae</t>
         </is>
       </c>
       <c r="H4" s="12" t="inlineStr">
         <is>
-          <t>Processed</t>
-        </is>
-      </c>
-      <c r="I4" s="12" t="inlineStr">
-        <is>
-          <t>CHG-0086,CHG-0087,CHG-0088</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="12" t="inlineStr">
-        <is>
-          <t>SRC-0001</t>
-        </is>
-      </c>
-      <c r="B5" s="12" t="inlineStr">
-        <is>
-          <t>MeitY</t>
-        </is>
-      </c>
-      <c r="C5" s="12" t="inlineStr">
-        <is>
-          <t>DPDP Rules, 2025 — MeitY PDF (G.S.R. 846(E))</t>
-        </is>
-      </c>
-      <c r="D5" s="12" t="inlineStr">
-        <is>
-          <t>https://www.meity.gov.in/static/uploads/2025/11/53450e6e5dc0bfa85ebd78686cadad39.pdf</t>
-        </is>
-      </c>
-      <c r="E5" s="12" t="n"/>
-      <c r="F5" s="12" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="G5" s="12" t="inlineStr">
-        <is>
-          <t>76094c7228c8dbff357281552fa2b052fe363303eb8b2c33ee5361d38883070d</t>
-        </is>
-      </c>
-      <c r="H5" s="12" t="inlineStr">
-        <is>
           <t>No Change Detected</t>
         </is>
       </c>
-      <c r="I5" s="12" t="inlineStr">
-        <is>
-          <t>CHG-0002,CHG-0003,CHG-0004,CHG-0005,CHG-0006,CHG-0007,CHG-0008,CHG-0009,CHG-0010,CHG-0011,CHG-0012,CHG-0013,CHG-0014,CHG-0015,CHG-0016,CHG-0017,CHG-0018,CHG-0019,CHG-0020,CHG-0021,CHG-0022,CHG-0023,CHG-0024,CHG-0025,CHG-0026,CHG-0027,CHG-0028,CHG-0029,CHG-0030,CHG-0031,CHG-0032</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="12" t="inlineStr">
-        <is>
-          <t>SRC-0005</t>
-        </is>
-      </c>
-      <c r="B6" s="12" t="inlineStr">
-        <is>
-          <t>eGazette</t>
-        </is>
-      </c>
-      <c r="C6" s="12" t="inlineStr">
-        <is>
-          <t>eGazette — Home (best-effort; no stable search endpoint confirmed)</t>
-        </is>
-      </c>
-      <c r="D6" s="12" t="inlineStr">
-        <is>
-          <t>https://egazette.gov.in/</t>
-        </is>
-      </c>
-      <c r="E6" s="12" t="n"/>
-      <c r="F6" s="12" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="G6" s="12" t="inlineStr">
-        <is>
-          <t>0263e67d63e88fa4ad218b927a6cf82dbeeca9065635dc9c16464a94f9c2392c</t>
-        </is>
-      </c>
-      <c r="H6" s="12" t="inlineStr">
-        <is>
-          <t>No Change Detected</t>
-        </is>
-      </c>
-      <c r="I6" s="12" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>SRC-0002</t>
-        </is>
-      </c>
-      <c r="B7" s="12" t="inlineStr">
-        <is>
-          <t>MeitY</t>
-        </is>
-      </c>
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>DPDP Act, 2023 — MeitY PDF</t>
-        </is>
-      </c>
-      <c r="D7" s="12" t="inlineStr">
-        <is>
-          <t>https://www.meity.gov.in/static/uploads/2024/06/2bf1f0e9f04e6fb4f8fef35e82c42aa5.pdf</t>
-        </is>
-      </c>
-      <c r="E7" s="12" t="n"/>
-      <c r="F7" s="12" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="G7" s="12" t="inlineStr">
-        <is>
-          <t>f15bda1ff8065c68f8e1cc57c50616264afeb49d72cfc48d1e92a2a3c473c1d2</t>
-        </is>
-      </c>
-      <c r="H7" s="12" t="inlineStr">
-        <is>
-          <t>No Change Detected</t>
-        </is>
-      </c>
-      <c r="I7" s="12" t="inlineStr">
-        <is>
-          <t>CHG-A0001,CHG-A0002,CHG-A0003,CHG-A0004,CHG-A0005,CHG-A0006,CHG-A0007,CHG-A0008,CHG-A0009,CHG-A0010,CHG-A0011,CHG-A0012,CHG-A0013,CHG-A0014,CHG-A0015,CHG-A0016,CHG-A0017,CHG-A0018,CHG-A0019,CHG-A0020,CHG-A0021,CHG-A0022,CHG-A0023,CHG-A0024,CHG-A0025,CHG-A0026,CHG-A0027,CHG-A0028,CHG-A0029,CHG-A0030,CHG-A0031,CHG-A0032,CHG-A0033,CHG-A0034,CHG-A0035,CHG-A0036,CHG-A0037,CHG-A0038,CHG-A0039,CHG-A0040,CHG-A0041,CHG-A0042,CHG-A0043,CHG-A0044,CHG-A0045,CHG-A0046,CHG-A0047,CHG-A0048</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t>SRC-0007</t>
-        </is>
-      </c>
-      <c r="B8" s="12" t="inlineStr">
-        <is>
-          <t>PIB</t>
-        </is>
-      </c>
-      <c r="C8" s="12" t="inlineStr">
-        <is>
-          <t>PIB — All Press Releases RSS (English, national)</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="inlineStr">
-        <is>
-          <t>https://www.pib.gov.in/RssMain.aspx?ModId=6&amp;Mid=0&amp;reg=3&amp;lang=1</t>
-        </is>
-      </c>
-      <c r="E8" s="12" t="n"/>
-      <c r="F8" s="12" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="G8" s="12" t="inlineStr">
-        <is>
-          <t>999b9fcb656461e59cfefe3a33ff05d77e449b7e6da0dbb7ff692c3c1ba46334</t>
-        </is>
-      </c>
-      <c r="H8" s="12" t="inlineStr">
-        <is>
-          <t>No Change Detected</t>
-        </is>
-      </c>
-      <c r="I8" s="12" t="n"/>
+      <c r="I4" s="12" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="2">
